--- a/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
@@ -556,7 +556,7 @@
         <v>0.4481559725105925</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9243267853069075</v>
+        <v>2.763479807123514</v>
       </c>
     </row>
     <row r="6">
@@ -581,7 +581,7 @@
         <v>-0.2280902140263398</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4279270434436434</v>
+        <v>-0.2280902140263398</v>
       </c>
     </row>
     <row r="7">
@@ -606,7 +606,7 @@
         <v>-0.1098273345114712</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8404195797588516</v>
+        <v>2.27731399542493</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         <v>0.3156354404163368</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9533573171392666</v>
+        <v>3.975472939029722</v>
       </c>
     </row>
     <row r="9">
@@ -656,7 +656,7 @@
         <v>0.2011033877524098</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9115225033341499</v>
+        <v>2.689290658553455</v>
       </c>
     </row>
     <row r="10">
@@ -681,7 +681,7 @@
         <v>0.7232573657160433</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7451698833102089</v>
+        <v>1.72542878264095</v>
       </c>
     </row>
     <row r="11">
@@ -706,7 +706,7 @@
         <v>-0.4446788403161421</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4499061108660709</v>
+        <v>-0.1685092747940378</v>
       </c>
     </row>
     <row r="12">
@@ -731,7 +731,7 @@
         <v>0.02202355758647872</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4645219119572452</v>
+        <v>0.02202355758647872</v>
       </c>
     </row>
     <row r="13">
@@ -756,7 +756,7 @@
         <v>0.3765148355833932</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7891204243184647</v>
+        <v>1.980082126228146</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +781,7 @@
         <v>0.0150657937917144</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8219680459459473</v>
+        <v>2.170404167423368</v>
       </c>
     </row>
     <row r="15">
@@ -806,7 +806,7 @@
         <v>-0.04037724894114841</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7704970058097398</v>
+        <v>1.872176383011477</v>
       </c>
     </row>
     <row r="16">
@@ -831,7 +831,7 @@
         <v>-1.30216719642931</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8479939113629964</v>
+        <v>3.660881940237104</v>
       </c>
     </row>
     <row r="17">
@@ -856,7 +856,7 @@
         <v>0.298223176955328</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7549672201377287</v>
+        <v>1.782195423600141</v>
       </c>
     </row>
     <row r="18">
@@ -881,7 +881,7 @@
         <v>0.05340069262867814</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8498365014758507</v>
+        <v>2.331876477399435</v>
       </c>
     </row>
     <row r="19">
@@ -906,7 +906,7 @@
         <v>-1.483859035078137</v>
       </c>
       <c r="G19" t="n">
-        <v>0.646864932675818</v>
+        <v>1.949847872202055</v>
       </c>
     </row>
     <row r="20">
@@ -931,7 +931,7 @@
         <v>0.1599334242983557</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5217034781906107</v>
+        <v>0.7465135631616248</v>
       </c>
     </row>
     <row r="21">
@@ -956,7 +956,7 @@
         <v>0.5151875717321431</v>
       </c>
       <c r="G21" t="n">
-        <v>0.834081369310496</v>
+        <v>2.240589840363225</v>
       </c>
     </row>
     <row r="22">
@@ -981,7 +981,7 @@
         <v>-0.2458269768227078</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8170967647078101</v>
+        <v>2.14217953067516</v>
       </c>
     </row>
     <row r="23">
@@ -1006,7 +1006,7 @@
         <v>0.3890834931741244</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8010756606369889</v>
+        <v>2.049351828762988</v>
       </c>
     </row>
     <row r="24">
@@ -1031,7 +1031,7 @@
         <v>-0.263110520300714</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6004826529035383</v>
+        <v>1.750516170830915</v>
       </c>
     </row>
     <row r="25">
@@ -1056,7 +1056,7 @@
         <v>-0.6091386422503443</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5649295156080353</v>
+        <v>1.297408573733281</v>
       </c>
     </row>
     <row r="26">
@@ -1081,7 +1081,7 @@
         <v>-0.487085405320118</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4566228460312882</v>
+        <v>-0.1262227552824805</v>
       </c>
     </row>
     <row r="27">
@@ -1106,7 +1106,7 @@
         <v>0.191087196148281</v>
       </c>
       <c r="G27" t="n">
-        <v>0.923814068391583</v>
+        <v>2.760509079714799</v>
       </c>
     </row>
     <row r="28">
@@ -1131,7 +1131,7 @@
         <v>-0.5607045290296652</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6899527436386715</v>
+        <v>2.890769349844495</v>
       </c>
     </row>
     <row r="29">
@@ -1156,7 +1156,7 @@
         <v>-0.187861406564276</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6178038292714395</v>
+        <v>1.396823502055015</v>
       </c>
     </row>
     <row r="30">
@@ -1181,7 +1181,7 @@
         <v>0.478674549516585</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7651163916690356</v>
+        <v>2.114576865878735</v>
       </c>
     </row>
     <row r="31">
@@ -1206,7 +1206,7 @@
         <v>-0.633238882931122</v>
       </c>
       <c r="G31" t="n">
-        <v>0.467512626807579</v>
+        <v>0.05587728398447637</v>
       </c>
     </row>
     <row r="32">
@@ -1231,7 +1231,7 @@
         <v>-0.7697715287667245</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7177302982953639</v>
+        <v>2.981908648169002</v>
       </c>
     </row>
     <row r="33">
@@ -1256,7 +1256,7 @@
         <v>0.2864756987871691</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5032146687493856</v>
+        <v>0.2864756987871691</v>
       </c>
     </row>
     <row r="34">
@@ -1281,7 +1281,7 @@
         <v>-0.8229604609119283</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5011199261156756</v>
+        <v>0.2843845156874721</v>
       </c>
     </row>
     <row r="35">
@@ -1306,7 +1306,7 @@
         <v>-0.3323228525645893</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7172240308022388</v>
+        <v>3.008968663813961</v>
       </c>
     </row>
     <row r="36">
@@ -1331,7 +1331,7 @@
         <v>0.6083797869825953</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5503133858873539</v>
+        <v>1.096144918039989</v>
       </c>
     </row>
     <row r="37">
@@ -1356,7 +1356,7 @@
         <v>-1.128089700601403</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5722068049985606</v>
+        <v>1.390154119132507</v>
       </c>
     </row>
     <row r="38">
@@ -1381,7 +1381,7 @@
         <v>-0.06100077834916965</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8493559187984098</v>
+        <v>2.329091938623054</v>
       </c>
     </row>
     <row r="39">
@@ -1406,7 +1406,7 @@
         <v>0.05663323021793536</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7374807311980002</v>
+        <v>3.496490641299062</v>
       </c>
     </row>
     <row r="40">
@@ -1431,7 +1431,7 @@
         <v>0.6018438449320197</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7518632452480585</v>
+        <v>1.764210717020153</v>
       </c>
     </row>
     <row r="41">
@@ -1456,7 +1456,7 @@
         <v>0.43835146177413</v>
       </c>
       <c r="G41" t="n">
-        <v>0.903183418158147</v>
+        <v>2.640973257360858</v>
       </c>
     </row>
     <row r="42">
@@ -1481,7 +1481,7 @@
         <v>-0.1327326221235222</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7637891954072916</v>
+        <v>3.831779336136942</v>
       </c>
     </row>
     <row r="43">
@@ -1506,7 +1506,7 @@
         <v>0.2526557449325313</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9775067813330917</v>
+        <v>6.555506950144018</v>
       </c>
     </row>
     <row r="44">
@@ -1531,7 +1531,7 @@
         <v>-0.5990870643821545</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7422970234339675</v>
+        <v>3.557871964241698</v>
       </c>
     </row>
     <row r="45">
@@ -1556,7 +1556,7 @@
         <v>3.681838434817529</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3.681838434817529</v>
       </c>
     </row>
     <row r="46">
@@ -1581,7 +1581,7 @@
         <v>-0.6400317145522038</v>
       </c>
       <c r="G46" t="n">
-        <v>0.56806693376109</v>
+        <v>1.337393455759457</v>
       </c>
     </row>
     <row r="47">
@@ -1606,7 +1606,7 @@
         <v>0.4202137105699785</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5227822636279221</v>
+        <v>0.4202137105699785</v>
       </c>
     </row>
     <row r="48">
@@ -1631,7 +1631,7 @@
         <v>0.661193444829144</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9034678722125055</v>
+        <v>2.917489125100054</v>
       </c>
     </row>
     <row r="49">
@@ -1656,7 +1656,7 @@
         <v>-0.536947676587389</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4315652138063645</v>
+        <v>-0.4022551669291249</v>
       </c>
     </row>
     <row r="50">
@@ -1681,7 +1681,7 @@
         <v>-1.986107704915156</v>
       </c>
       <c r="G50" t="n">
-        <v>0.5966073432996783</v>
+        <v>1.701127217951179</v>
       </c>
     </row>
     <row r="51">
@@ -1706,7 +1706,7 @@
         <v>-2.559989688843802</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6478839196008841</v>
+        <v>2.354622465982963</v>
       </c>
     </row>
     <row r="52">
@@ -1731,7 +1731,7 @@
         <v>-1.990840503368205</v>
       </c>
       <c r="G52" t="n">
-        <v>0.6009062358026265</v>
+        <v>1.755914530699477</v>
       </c>
     </row>
     <row r="53">
@@ -1756,7 +1756,7 @@
         <v>0.08171329404120221</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6853216505185022</v>
+        <v>2.831748300360889</v>
       </c>
     </row>
     <row r="54">
@@ -1781,7 +1781,7 @@
         <v>-0.1511661431674419</v>
       </c>
       <c r="G54" t="n">
-        <v>0.482292423318319</v>
+        <v>0.2442386661857714</v>
       </c>
     </row>
     <row r="55">
@@ -1806,7 +1806,7 @@
         <v>-1.016166214201748</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7659301314080673</v>
+        <v>3.859064533468148</v>
       </c>
     </row>
     <row r="56">
@@ -1831,7 +1831,7 @@
         <v>0.2041376924456348</v>
       </c>
       <c r="G56" t="n">
-        <v>0.7008729885720086</v>
+        <v>3.029942607617384</v>
       </c>
     </row>
     <row r="57">
@@ -1856,7 +1856,7 @@
         <v>1.114846676565727</v>
       </c>
       <c r="G57" t="n">
-        <v>0.62441601970585</v>
+        <v>1.114846676565727</v>
       </c>
     </row>
     <row r="58">
@@ -1881,7 +1881,7 @@
         <v>0.005734034642913454</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5601444483024109</v>
+        <v>1.236425197476465</v>
       </c>
     </row>
     <row r="59">
@@ -1906,7 +1906,7 @@
         <v>0.2620814423873599</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4996454746195236</v>
+        <v>0.2620814423873599</v>
       </c>
     </row>
     <row r="60">
@@ -1931,7 +1931,7 @@
         <v>-0.06090283215241446</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7968850694695153</v>
+        <v>4.253570297804814</v>
       </c>
     </row>
     <row r="61">
@@ -1956,7 +1956,7 @@
         <v>-1.378067637022015</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9779984231567342</v>
+        <v>4.292117288815221</v>
       </c>
     </row>
     <row r="62">
@@ -1981,7 +1981,7 @@
         <v>0.2688249326222985</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9905182490356108</v>
+        <v>6.721331834074801</v>
       </c>
     </row>
     <row r="63">
@@ -2006,7 +2006,7 @@
         <v>-0.7043113833963557</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5899256148787306</v>
+        <v>1.172734572661247</v>
       </c>
     </row>
     <row r="64">
@@ -2031,7 +2031,7 @@
         <v>-0.8410704702600007</v>
       </c>
       <c r="G64" t="n">
-        <v>0.600526352422122</v>
+        <v>1.751073100130719</v>
       </c>
     </row>
     <row r="65">
@@ -2056,7 +2056,7 @@
         <v>0.1323380202061264</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8684307388725729</v>
+        <v>5.165385367077522</v>
       </c>
     </row>
     <row r="66">
@@ -2081,7 +2081,7 @@
         <v>-1.094260807743402</v>
       </c>
       <c r="G66" t="n">
-        <v>0.77131020120551</v>
+        <v>3.927630929673222</v>
       </c>
     </row>
     <row r="67">
@@ -2106,7 +2106,7 @@
         <v>0.5420714604346089</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8693874790905177</v>
+        <v>4.391681541309022</v>
       </c>
     </row>
     <row r="68">
@@ -2131,7 +2131,7 @@
         <v>-0.8188432413649119</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9585577371642899</v>
+        <v>2.96181698670493</v>
       </c>
     </row>
     <row r="69">
@@ -2156,7 +2156,7 @@
         <v>0.5884704727570466</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8822790391143867</v>
+        <v>2.519851425934307</v>
       </c>
     </row>
     <row r="70">
@@ -2181,7 +2181,7 @@
         <v>0.6313690995957126</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8696275423735416</v>
+        <v>3.882269467735987</v>
       </c>
     </row>
     <row r="71">
@@ -2206,7 +2206,7 @@
         <v>1.119488047643306</v>
       </c>
       <c r="G71" t="n">
-        <v>0.7927824614648837</v>
+        <v>2.259695112876489</v>
       </c>
     </row>
     <row r="72">
@@ -2231,7 +2231,7 @@
         <v>3.441225940226508</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9647952907770359</v>
+        <v>3.441225940226508</v>
       </c>
     </row>
     <row r="73">
@@ -2256,7 +2256,7 @@
         <v>3.354816259848985</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9521524407998946</v>
+        <v>5.600905185773277</v>
       </c>
     </row>
     <row r="74">
@@ -2281,7 +2281,7 @@
         <v>0.413036395460917</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9215996131933117</v>
+        <v>4.641127841209785</v>
       </c>
     </row>
     <row r="75">
@@ -2306,7 +2306,7 @@
         <v>0.4008740656604979</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9423048753384816</v>
+        <v>2.867646459747699</v>
       </c>
     </row>
     <row r="76">
@@ -2331,7 +2331,7 @@
         <v>-1.38265272173316</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>3.201937143472751</v>
       </c>
     </row>
     <row r="77">
@@ -2356,7 +2356,7 @@
         <v>0.8733700831459458</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8253991727079085</v>
+        <v>2.190284421048478</v>
       </c>
     </row>
     <row r="78">
@@ -2381,7 +2381,7 @@
         <v>0.7387695177326324</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8371829803608046</v>
+        <v>2.74901437268143</v>
       </c>
     </row>
     <row r="79">
@@ -2406,7 +2406,7 @@
         <v>0.675456641873503</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5601275943142237</v>
+        <v>0.675456641873503</v>
       </c>
     </row>
     <row r="80">
@@ -2431,7 +2431,7 @@
         <v>0.6142898632900973</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8330840616624919</v>
+        <v>2.234811351149597</v>
       </c>
     </row>
     <row r="81">
@@ -2456,7 +2456,7 @@
         <v>-0.4858923464044823</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9558323625751309</v>
+        <v>3.67803512406718</v>
       </c>
     </row>
     <row r="82">
@@ -2481,7 +2481,7 @@
         <v>-2.679523865859168</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6280847762652918</v>
+        <v>2.102291927982409</v>
       </c>
     </row>
     <row r="83">
@@ -2506,7 +2506,7 @@
         <v>-0.6009409013509414</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5710751553023293</v>
+        <v>1.375731789244887</v>
       </c>
     </row>
     <row r="84">
@@ -2531,7 +2531,7 @@
         <v>0.6387877130265049</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7693003371589151</v>
+        <v>3.650971145561097</v>
       </c>
     </row>
     <row r="85">
@@ -2556,7 +2556,7 @@
         <v>0.6836269438271769</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8402115464951354</v>
+        <v>2.993905594326431</v>
       </c>
     </row>
     <row r="86">
@@ -2581,7 +2581,7 @@
         <v>0.9021676857652036</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9334990011324412</v>
+        <v>5.994649004624828</v>
       </c>
     </row>
     <row r="87">
@@ -2606,7 +2606,7 @@
         <v>-0.6111783377618998</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8068000919688815</v>
+        <v>2.082519693034055</v>
       </c>
     </row>
     <row r="88">
@@ -2631,7 +2631,7 @@
         <v>0.3393065010980859</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7358294520311127</v>
+        <v>1.671309493066756</v>
       </c>
     </row>
     <row r="89">
@@ -2656,7 +2656,7 @@
         <v>1.177133058657776</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6335293202176466</v>
+        <v>1.177133058657776</v>
       </c>
     </row>
     <row r="90">
@@ -2681,7 +2681,7 @@
         <v>0.1852093443319505</v>
       </c>
       <c r="G90" t="n">
-        <v>0.7065930542623292</v>
+        <v>3.102842087588441</v>
       </c>
     </row>
     <row r="91">
@@ -2706,7 +2706,7 @@
         <v>-0.1005942475604853</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9521888956593905</v>
+        <v>2.924915352577265</v>
       </c>
     </row>
     <row r="92">
@@ -2731,7 +2731,7 @@
         <v>0.3788151064100657</v>
       </c>
       <c r="G92" t="n">
-        <v>0.7270061444809685</v>
+        <v>3.362997082671668</v>
       </c>
     </row>
     <row r="93">
@@ -2756,7 +2756,7 @@
         <v>0.7650340129331171</v>
       </c>
       <c r="G93" t="n">
-        <v>0.8016283830315825</v>
+        <v>4.314021542726616</v>
       </c>
     </row>
     <row r="94">
@@ -2781,7 +2781,7 @@
         <v>0.28106403645769</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5024228727994454</v>
+        <v>0.28106403645769</v>
       </c>
     </row>
     <row r="95">
@@ -2806,7 +2806,7 @@
         <v>0.02433001605627384</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5001062400358601</v>
+        <v>0.4712671734293135</v>
       </c>
     </row>
     <row r="96">
@@ -2831,7 +2831,7 @@
         <v>0.316308908648707</v>
       </c>
       <c r="G96" t="n">
-        <v>0.7314660529615133</v>
+        <v>3.419836466439655</v>
       </c>
     </row>
     <row r="97">
@@ -2856,7 +2856,7 @@
         <v>-0.6274446345226417</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6590007243578806</v>
+        <v>2.496300783960359</v>
       </c>
     </row>
     <row r="98">
@@ -2881,7 +2881,7 @@
         <v>0.3577400192920832</v>
       </c>
       <c r="G98" t="n">
-        <v>0.625912350805265</v>
+        <v>2.07460541267196</v>
       </c>
     </row>
     <row r="99">
@@ -2906,7 +2906,7 @@
         <v>-0.6287489291991131</v>
       </c>
       <c r="G99" t="n">
-        <v>0.6200213455377179</v>
+        <v>1.999527390187418</v>
       </c>
     </row>
     <row r="100">
@@ -2931,7 +2931,7 @@
         <v>-0.5038878653218247</v>
       </c>
       <c r="G100" t="n">
-        <v>0.5871527405550957</v>
+        <v>1.580632863388202</v>
       </c>
     </row>
     <row r="101">
@@ -2956,7 +2956,7 @@
         <v>2.490543804887305</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8256982409959298</v>
+        <v>2.490543804887305</v>
       </c>
     </row>
     <row r="102">
@@ -2981,7 +2981,7 @@
         <v>2.259100056813676</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7918350375648093</v>
+        <v>2.259100056813676</v>
       </c>
     </row>
     <row r="103">
@@ -3006,7 +3006,7 @@
         <v>-0.6564639066398494</v>
       </c>
       <c r="G103" t="n">
-        <v>0.5234719288435601</v>
+        <v>0.7690516142844713</v>
       </c>
     </row>
     <row r="104">
@@ -3031,7 +3031,7 @@
         <v>0.2549825368686213</v>
       </c>
       <c r="G104" t="n">
-        <v>0.4986068132440482</v>
+        <v>0.2549825368686213</v>
       </c>
     </row>
     <row r="105">
@@ -3056,7 +3056,7 @@
         <v>0.06312144951122764</v>
       </c>
       <c r="G105" t="n">
-        <v>0.7419293129378134</v>
+        <v>3.55318567121627</v>
       </c>
     </row>
     <row r="106">
@@ -3081,7 +3081,7 @@
         <v>0.2092706182527805</v>
       </c>
       <c r="G106" t="n">
-        <v>0.7478199928277829</v>
+        <v>3.628259546920428</v>
       </c>
     </row>
     <row r="107">
@@ -3106,7 +3106,7 @@
         <v>0.02075406377236158</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4643361686496821</v>
+        <v>0.02075406377236158</v>
       </c>
     </row>
     <row r="108">
@@ -3131,7 +3131,7 @@
         <v>0.8438185853079608</v>
       </c>
       <c r="G108" t="n">
-        <v>0.7155209006446386</v>
+        <v>3.216623186227426</v>
       </c>
     </row>
     <row r="109">
@@ -3156,7 +3156,7 @@
         <v>0.5883443989180057</v>
       </c>
       <c r="G109" t="n">
-        <v>0.5744726564412542</v>
+        <v>1.419031303557776</v>
       </c>
     </row>
     <row r="110">
@@ -3181,7 +3181,7 @@
         <v>0.6067564661714181</v>
       </c>
       <c r="G110" t="n">
-        <v>0.8377669859084637</v>
+        <v>2.261944630732623</v>
       </c>
     </row>
     <row r="111">
@@ -3206,7 +3206,7 @@
         <v>-0.6728193002905415</v>
       </c>
       <c r="G111" t="n">
-        <v>0.8697147900844762</v>
+        <v>2.447053049583766</v>
       </c>
     </row>
     <row r="112">
@@ -3231,7 +3231,7 @@
         <v>0.2511448081360659</v>
       </c>
       <c r="G112" t="n">
-        <v>0.6969720372659843</v>
+        <v>2.980226863603674</v>
       </c>
     </row>
     <row r="113">
@@ -3256,7 +3256,7 @@
         <v>0.675246484669455</v>
       </c>
       <c r="G113" t="n">
-        <v>0.6956384936740742</v>
+        <v>2.963231493334849</v>
       </c>
     </row>
     <row r="114">
@@ -3281,7 +3281,7 @@
         <v>-0.03895816992636211</v>
       </c>
       <c r="G114" t="n">
-        <v>0.8095796148110737</v>
+        <v>2.098624495594011</v>
       </c>
     </row>
     <row r="115">
@@ -3306,7 +3306,7 @@
         <v>0.3357388722078157</v>
       </c>
       <c r="G115" t="n">
-        <v>0.5104225059758862</v>
+        <v>0.3357388722078157</v>
       </c>
     </row>
     <row r="116">
@@ -3331,7 +3331,7 @@
         <v>-0.2209402022920736</v>
       </c>
       <c r="G116" t="n">
-        <v>0.8723671399685544</v>
+        <v>2.462421000713577</v>
       </c>
     </row>
     <row r="117">
@@ -3356,7 +3356,7 @@
         <v>3.302504865988261</v>
       </c>
       <c r="G117" t="n">
-        <v>0.9444986096343727</v>
+        <v>3.302504865988261</v>
       </c>
     </row>
     <row r="118">
@@ -3381,7 +3381,7 @@
         <v>0.04755766728354271</v>
       </c>
       <c r="G118" t="n">
-        <v>0.8117628853166764</v>
+        <v>2.111274559084756</v>
       </c>
     </row>
     <row r="119">
@@ -3406,7 +3406,7 @@
         <v>-0.5547603924229295</v>
       </c>
       <c r="G119" t="n">
-        <v>0.7887574063130198</v>
+        <v>1.977978767617577</v>
       </c>
     </row>
     <row r="120">
@@ -3431,7 +3431,7 @@
         <v>-0.7183532923190646</v>
       </c>
       <c r="G120" t="n">
-        <v>0.819192150054835</v>
+        <v>4.537863287148288</v>
       </c>
     </row>
     <row r="121">
@@ -3456,7 +3456,7 @@
         <v>-0.6520054892059023</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4816008485980839</v>
+        <v>0.3020051722514078</v>
       </c>
     </row>
     <row r="122">
@@ -3481,7 +3481,7 @@
         <v>-0.5369440477986557</v>
       </c>
       <c r="G122" t="n">
-        <v>0.7953765230546896</v>
+        <v>4.234344600914814</v>
       </c>
     </row>
     <row r="123">
@@ -3506,7 +3506,7 @@
         <v>-0.5811836255615815</v>
       </c>
       <c r="G123" t="n">
-        <v>0.5814791967287359</v>
+        <v>1.50832628214832</v>
       </c>
     </row>
     <row r="124">
@@ -3531,7 +3531,7 @@
         <v>-0.3397256353204008</v>
       </c>
       <c r="G124" t="n">
-        <v>0.6503937151874452</v>
+        <v>2.386608600933051</v>
       </c>
     </row>
     <row r="125">
@@ -3556,7 +3556,7 @@
         <v>0.7358190626987998</v>
       </c>
       <c r="G125" t="n">
-        <v>0.5803593991080923</v>
+        <v>1.494055001250989</v>
       </c>
     </row>
     <row r="126">
@@ -3581,7 +3581,7 @@
         <v>-0.5107666564447587</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6469323701477642</v>
+        <v>2.342495426879799</v>
       </c>
     </row>
     <row r="127">
@@ -3606,7 +3606,7 @@
         <v>-0.176215346785682</v>
       </c>
       <c r="G127" t="n">
-        <v>0.7332544448199504</v>
+        <v>1.65638967226272</v>
       </c>
     </row>
     <row r="128">
@@ -3631,7 +3631,7 @@
         <v>-0.5460113970483075</v>
       </c>
       <c r="G128" t="n">
-        <v>0.6409648891583338</v>
+        <v>2.266442758183566</v>
       </c>
     </row>
     <row r="129">
@@ -3656,7 +3656,7 @@
         <v>-1.005038480131347</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>6.842172179612913</v>
       </c>
     </row>
     <row r="130">
@@ -3681,7 +3681,7 @@
         <v>-0.7210715540432888</v>
       </c>
       <c r="G130" t="n">
-        <v>0.6129199325717485</v>
+        <v>1.909023305041172</v>
       </c>
     </row>
     <row r="131">
@@ -3706,7 +3706,7 @@
         <v>-0.2218709043944195</v>
       </c>
       <c r="G131" t="n">
-        <v>0.6066125644216813</v>
+        <v>1.828638938318954</v>
       </c>
     </row>
     <row r="132">
@@ -3731,7 +3731,7 @@
         <v>-0.6004829770661529</v>
       </c>
       <c r="G132" t="n">
-        <v>0.6276808832828212</v>
+        <v>2.097144506609979</v>
       </c>
     </row>
     <row r="133">
@@ -3756,7 +3756,7 @@
         <v>-0.3016328255649398</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5561563520250102</v>
+        <v>0.6372310545687212</v>
       </c>
     </row>
     <row r="134">
@@ -3781,7 +3781,7 @@
         <v>-0.5128194317398215</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6374505489593454</v>
+        <v>1.159945263963395</v>
       </c>
     </row>
     <row r="135">
@@ -3806,7 +3806,7 @@
         <v>-0.7292843217125511</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8462082812769164</v>
+        <v>2.644770402642359</v>
       </c>
     </row>
     <row r="136">
@@ -3831,7 +3831,7 @@
         <v>-1.194091358866186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.7973251537487782</v>
+        <v>2.297080782692796</v>
       </c>
     </row>
     <row r="137">
@@ -3856,7 +3856,7 @@
         <v>-1.062452382198005</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>3.738640352011697</v>
       </c>
     </row>
     <row r="138">
@@ -3881,7 +3881,7 @@
         <v>0.4228692413244797</v>
       </c>
       <c r="G138" t="n">
-        <v>0.5579190477234698</v>
+        <v>0.5942638348690173</v>
       </c>
     </row>
     <row r="139">
@@ -3906,7 +3906,7 @@
         <v>-0.3862921824597976</v>
       </c>
       <c r="G139" t="n">
-        <v>0.7300656900907722</v>
+        <v>1.818686323504345</v>
       </c>
     </row>
     <row r="140">
@@ -3931,7 +3931,7 @@
         <v>0.2212047974901072</v>
       </c>
       <c r="G140" t="n">
-        <v>0.8719927416615398</v>
+        <v>2.828166794916441</v>
       </c>
     </row>
     <row r="141">
@@ -3956,7 +3956,7 @@
         <v>-1.200596191800883</v>
       </c>
       <c r="G141" t="n">
-        <v>0.8810332524590305</v>
+        <v>2.89246897692229</v>
       </c>
     </row>
     <row r="142">
@@ -3981,7 +3981,7 @@
         <v>-1.086205036776972</v>
       </c>
       <c r="G142" t="n">
-        <v>0.6176346785065769</v>
+        <v>1.019001490209825</v>
       </c>
     </row>
     <row r="143">
@@ -4006,7 +4006,7 @@
         <v>2.426258453264439</v>
       </c>
       <c r="G143" t="n">
-        <v>0.8162924654769743</v>
+        <v>2.426258453264439</v>
       </c>
     </row>
     <row r="144">
@@ -4031,7 +4031,7 @@
         <v>-1.775440584254941</v>
       </c>
       <c r="G144" t="n">
-        <v>0.5724960596840994</v>
+        <v>0.9159042099526967</v>
       </c>
     </row>
     <row r="145">
@@ -4056,7 +4056,7 @@
         <v>-0.2501102329732696</v>
       </c>
       <c r="G145" t="n">
-        <v>0.9684163502568556</v>
+        <v>3.513996231819244</v>
       </c>
     </row>
     <row r="146">
@@ -4081,7 +4081,7 @@
         <v>3.471640522215216</v>
       </c>
       <c r="G146" t="n">
-        <v>0.9692453361367768</v>
+        <v>3.471640522215216</v>
       </c>
     </row>
     <row r="147">
@@ -4106,7 +4106,7 @@
         <v>0.05674552872975166</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4696021838684143</v>
+        <v>0.05674552872975166</v>
       </c>
     </row>
     <row r="148">
@@ -4131,7 +4131,7 @@
         <v>2.460365518868009</v>
       </c>
       <c r="G148" t="n">
-        <v>0.836022752643399</v>
+        <v>2.572324085095787</v>
       </c>
     </row>
     <row r="149">
@@ -4156,7 +4156,7 @@
         <v>1.491828202025415</v>
       </c>
       <c r="G149" t="n">
-        <v>0.6795732758109243</v>
+        <v>1.491828202025415</v>
       </c>
     </row>
     <row r="150">
@@ -4181,7 +4181,7 @@
         <v>-0.060693496632741</v>
       </c>
       <c r="G150" t="n">
-        <v>0.5640676320858971</v>
+        <v>0.9648845432904982</v>
       </c>
     </row>
     <row r="151">
@@ -4206,7 +4206,7 @@
         <v>-0.6927317260028962</v>
       </c>
       <c r="G151" t="n">
-        <v>0.7357783871585788</v>
+        <v>2.345119257307775</v>
       </c>
     </row>
     <row r="152">
@@ -4231,7 +4231,7 @@
         <v>-0.04651621837521624</v>
       </c>
       <c r="G152" t="n">
-        <v>0.5513697836534377</v>
+        <v>0.8628174876049537</v>
       </c>
     </row>
     <row r="153">
@@ -4256,7 +4256,7 @@
         <v>-0.2811972299589065</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5926706541324308</v>
+        <v>0.8414405896299196</v>
       </c>
     </row>
     <row r="154">
@@ -4281,7 +4281,7 @@
         <v>0.406046713764525</v>
       </c>
       <c r="G154" t="n">
-        <v>0.5576156513591051</v>
+        <v>0.6387228815394025</v>
       </c>
     </row>
     <row r="155">
@@ -4306,7 +4306,7 @@
         <v>1.50995125235221</v>
       </c>
       <c r="G155" t="n">
-        <v>0.6822249116624723</v>
+        <v>1.50995125235221</v>
       </c>
     </row>
     <row r="156">
@@ -4331,7 +4331,7 @@
         <v>0.4875842149707524</v>
       </c>
       <c r="G156" t="n">
-        <v>0.6076986464554137</v>
+        <v>0.9483297598528198</v>
       </c>
     </row>
     <row r="157">
@@ -4356,7 +4356,7 @@
         <v>-0.02387642351555256</v>
       </c>
       <c r="G157" t="n">
-        <v>0.6504124138009956</v>
+        <v>1.25213874847473</v>
       </c>
     </row>
     <row r="158">
@@ -4381,7 +4381,7 @@
         <v>-0.4042775050966564</v>
       </c>
       <c r="G158" t="n">
-        <v>0.6705968300910684</v>
+        <v>1.395703867641043</v>
       </c>
     </row>
     <row r="159">
@@ -4406,7 +4406,7 @@
         <v>-0.1776683158246657</v>
       </c>
       <c r="G159" t="n">
-        <v>0.6373599866468866</v>
+        <v>1.159301123999511</v>
       </c>
     </row>
     <row r="160">
@@ -4431,7 +4431,7 @@
         <v>0.3289721812868349</v>
       </c>
       <c r="G160" t="n">
-        <v>0.5422080833277145</v>
+        <v>0.4825169087612939</v>
       </c>
     </row>
     <row r="161">
@@ -4456,7 +4456,7 @@
         <v>-0.02448702938226801</v>
       </c>
       <c r="G161" t="n">
-        <v>0.4817703950445548</v>
+        <v>0.3010141847338035</v>
       </c>
     </row>
     <row r="162">
@@ -4481,7 +4481,7 @@
         <v>-0.2525268163382256</v>
       </c>
       <c r="G162" t="n">
-        <v>0.5475103983506402</v>
+        <v>0.5202305328356266</v>
       </c>
     </row>
     <row r="163">
@@ -4506,7 +4506,7 @@
         <v>-0.7522664682617017</v>
       </c>
       <c r="G163" t="n">
-        <v>0.7037647680193277</v>
+        <v>1.631616508994628</v>
       </c>
     </row>
     <row r="164">
@@ -4531,7 +4531,7 @@
         <v>0.2080320203356396</v>
       </c>
       <c r="G164" t="n">
-        <v>0.4917373475281424</v>
+        <v>0.2080320203356396</v>
       </c>
     </row>
     <row r="165">
@@ -4556,7 +4556,7 @@
         <v>1.094157600689859</v>
       </c>
       <c r="G165" t="n">
-        <v>0.6213889412428641</v>
+        <v>1.094157600689859</v>
       </c>
     </row>
     <row r="166">
@@ -4581,7 +4581,7 @@
         <v>1.712434519322673</v>
       </c>
       <c r="G166" t="n">
-        <v>0.7118508234353724</v>
+        <v>1.712434519322673</v>
       </c>
     </row>
     <row r="167">
@@ -4606,7 +4606,7 @@
         <v>-0.1359963094813013</v>
       </c>
       <c r="G167" t="n">
-        <v>0.484952423083475</v>
+        <v>0.3289455898705217</v>
       </c>
     </row>
     <row r="168">
@@ -4631,7 +4631,7 @@
         <v>0.5081568813577235</v>
       </c>
       <c r="G168" t="n">
-        <v>0.5772518883305402</v>
+        <v>0.7317719760849947</v>
       </c>
     </row>
     <row r="169">
@@ -4656,7 +4656,7 @@
         <v>0.850042454471434</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5856717489409903</v>
+        <v>0.850042454471434</v>
       </c>
     </row>
     <row r="170">
@@ -4681,7 +4681,7 @@
         <v>-1.17165851049401</v>
       </c>
       <c r="G170" t="n">
-        <v>0.8123680146659075</v>
+        <v>2.404075708339076</v>
       </c>
     </row>
     <row r="171">
@@ -4706,7 +4706,7 @@
         <v>3.07319366785422</v>
       </c>
       <c r="G171" t="n">
-        <v>0.9165246489772899</v>
+        <v>3.144907615587742</v>
       </c>
     </row>
     <row r="172">
@@ -4731,7 +4731,7 @@
         <v>0.2570025709125904</v>
       </c>
       <c r="G172" t="n">
-        <v>0.5184533233839834</v>
+        <v>0.3135571086324083</v>
       </c>
     </row>
     <row r="173">
@@ -4756,7 +4756,7 @@
         <v>0.4552761016617888</v>
       </c>
       <c r="G173" t="n">
-        <v>0.5710865065096054</v>
+        <v>0.6879196415360052</v>
       </c>
     </row>
     <row r="174">
@@ -4781,7 +4781,7 @@
         <v>3.342005881826272</v>
       </c>
       <c r="G174" t="n">
-        <v>0.9502781173816847</v>
+        <v>3.342005881826272</v>
       </c>
     </row>
     <row r="175">
@@ -4806,7 +4806,7 @@
         <v>-0.02931360735713913</v>
       </c>
       <c r="G175" t="n">
-        <v>0.5424472754850664</v>
+        <v>0.7910971372700197</v>
       </c>
     </row>
     <row r="176">
@@ -4831,7 +4831,7 @@
         <v>0.4203976788765076</v>
       </c>
       <c r="G176" t="n">
-        <v>0.5228091805623424</v>
+        <v>0.4203976788765076</v>
       </c>
     </row>
     <row r="177">
@@ -4856,7 +4856,7 @@
         <v>0.9029263946437102</v>
       </c>
       <c r="G177" t="n">
-        <v>0.5934093510114653</v>
+        <v>0.9029263946437102</v>
       </c>
     </row>
     <row r="178">
@@ -4881,7 +4881,7 @@
         <v>-0.2681371305397149</v>
       </c>
       <c r="G178" t="n">
-        <v>0.4785962151959065</v>
+        <v>0.03006659771482753</v>
       </c>
     </row>
     <row r="179">
@@ -4906,7 +4906,7 @@
         <v>0.1891153940625758</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4977908434553533</v>
+        <v>0.2316925153583238</v>
       </c>
     </row>
     <row r="180">
@@ -4931,7 +4931,7 @@
         <v>1.231274817110714</v>
       </c>
       <c r="G180" t="n">
-        <v>0.6414509573146536</v>
+        <v>1.231274817110714</v>
       </c>
     </row>
     <row r="181">
@@ -4956,7 +4956,7 @@
         <v>0.5216125667239547</v>
       </c>
       <c r="G181" t="n">
-        <v>0.6084478435480961</v>
+        <v>0.9536585525384379</v>
       </c>
     </row>
     <row r="182">
@@ -4981,7 +4981,7 @@
         <v>-0.7056868162947558</v>
       </c>
       <c r="G182" t="n">
-        <v>0.6168109707877535</v>
+        <v>1.013142727929477</v>
       </c>
     </row>
     <row r="183">
@@ -5006,7 +5006,7 @@
         <v>-0.1000156031009907</v>
       </c>
       <c r="G183" t="n">
-        <v>0.6110652922305252</v>
+        <v>0.9722756047535895</v>
       </c>
     </row>
     <row r="184">
@@ -5031,7 +5031,7 @@
         <v>-0.4476214874188126</v>
       </c>
       <c r="G184" t="n">
-        <v>0.5775632142418805</v>
+        <v>0.7339863349705229</v>
       </c>
     </row>
     <row r="185">
@@ -5056,7 +5056,7 @@
         <v>-0.6588779620603112</v>
       </c>
       <c r="G185" t="n">
-        <v>0.6512301012218443</v>
+        <v>1.257954690354242</v>
       </c>
     </row>
     <row r="186">
@@ -5081,7 +5081,7 @@
         <v>-0.6395430371529254</v>
       </c>
       <c r="G186" t="n">
-        <v>0.7381203637182031</v>
+        <v>1.875976569729429</v>
       </c>
     </row>
     <row r="187">
@@ -5106,7 +5106,7 @@
         <v>-0.3350270227443484</v>
       </c>
       <c r="G187" t="n">
-        <v>0.6354777360989823</v>
+        <v>1.145913294481564</v>
       </c>
     </row>
     <row r="188">
@@ -5131,7 +5131,7 @@
         <v>1.238337014231035</v>
       </c>
       <c r="G188" t="n">
-        <v>0.6424842477783046</v>
+        <v>1.238337014231035</v>
       </c>
     </row>
     <row r="189">
@@ -5156,7 +5156,7 @@
         <v>-0.5830855910769702</v>
       </c>
       <c r="G189" t="n">
-        <v>0.6365566232118295</v>
+        <v>1.153587063923145</v>
       </c>
     </row>
     <row r="190">
@@ -5181,7 +5181,7 @@
         <v>-0.5340608389236194</v>
       </c>
       <c r="G190" t="n">
-        <v>0.712579390219759</v>
+        <v>1.6943120196512</v>
       </c>
     </row>
     <row r="191">
@@ -5206,7 +5206,7 @@
         <v>-0.6050807259304319</v>
       </c>
       <c r="G191" t="n">
-        <v>0.4920495726049761</v>
+        <v>0.3859934558355891</v>
       </c>
     </row>
     <row r="192">
@@ -5231,7 +5231,7 @@
         <v>0.2623200431468876</v>
       </c>
       <c r="G192" t="n">
-        <v>0.4996803849859776</v>
+        <v>0.2947578242478518</v>
       </c>
     </row>
     <row r="193">
@@ -5256,7 +5256,7 @@
         <v>-0.2133494205605597</v>
       </c>
       <c r="G193" t="n">
-        <v>0.4452953699698398</v>
+        <v>0.01017673150811147</v>
       </c>
     </row>
     <row r="194">
@@ -5281,7 +5281,7 @@
         <v>-0.1782187716001077</v>
       </c>
       <c r="G194" t="n">
-        <v>0.4854230154784182</v>
+        <v>0.3327282763969321</v>
       </c>
     </row>
     <row r="195">
@@ -5306,7 +5306,7 @@
         <v>-0.5846043798639832</v>
       </c>
       <c r="G195" t="n">
-        <v>0.4767018754778721</v>
+        <v>0.1906505373581875</v>
       </c>
     </row>
     <row r="196">
@@ -5331,7 +5331,7 @@
         <v>-0.7872752502013224</v>
       </c>
       <c r="G196" t="n">
-        <v>0.6146018592525765</v>
+        <v>0.9974300436367265</v>
       </c>
     </row>
     <row r="197">
@@ -5356,7 +5356,7 @@
         <v>-0.7265285935515164</v>
       </c>
       <c r="G197" t="n">
-        <v>0.7403528954991712</v>
+        <v>1.891855834533084</v>
       </c>
     </row>
     <row r="198">
@@ -5381,7 +5381,7 @@
         <v>-0.3131136432768201</v>
       </c>
       <c r="G198" t="n">
-        <v>0.5005856599216519</v>
+        <v>0.4546077021090476</v>
       </c>
     </row>
     <row r="199">
@@ -5406,7 +5406,7 @@
         <v>0.769345116326919</v>
       </c>
       <c r="G199" t="n">
-        <v>0.5804986749188547</v>
+        <v>0.769345116326919</v>
       </c>
     </row>
     <row r="200">
@@ -5431,7 +5431,7 @@
         <v>0.3475570768303943</v>
       </c>
       <c r="G200" t="n">
-        <v>0.603074929859872</v>
+        <v>0.9154427833611247</v>
       </c>
     </row>
     <row r="201">
@@ -5456,7 +5456,7 @@
         <v>-0.01083940968724928</v>
       </c>
       <c r="G201" t="n">
-        <v>0.6337650931900197</v>
+        <v>1.133731828355369</v>
       </c>
     </row>
     <row r="202">
@@ -5481,7 +5481,7 @@
         <v>-0.7423288107261099</v>
       </c>
       <c r="G202" t="n">
-        <v>0.830568356786174</v>
+        <v>2.533528760030684</v>
       </c>
     </row>
     <row r="203">
@@ -5506,7 +5506,7 @@
         <v>-0.1126670340673456</v>
       </c>
       <c r="G203" t="n">
-        <v>0.791652672702895</v>
+        <v>2.256734289357667</v>
       </c>
     </row>
     <row r="204">
@@ -5531,7 +5531,7 @@
         <v>-0.1304338789794753</v>
       </c>
       <c r="G204" t="n">
-        <v>0.6300470945975647</v>
+        <v>1.107286926342101</v>
       </c>
     </row>
     <row r="205">
@@ -5556,7 +5556,7 @@
         <v>0.2840115438054184</v>
       </c>
       <c r="G205" t="n">
-        <v>0.6185465476509819</v>
+        <v>1.025487315734785</v>
       </c>
     </row>
     <row r="206">
@@ -5581,7 +5581,7 @@
         <v>-1.108025431067092</v>
       </c>
       <c r="G206" t="n">
-        <v>0.5209571937133598</v>
+        <v>0.6183568982801889</v>
       </c>
     </row>
     <row r="207">
@@ -5606,7 +5606,7 @@
         <v>-0.5814012152830668</v>
       </c>
       <c r="G207" t="n">
-        <v>0.7001245106575487</v>
+        <v>1.60572455480436</v>
       </c>
     </row>
     <row r="208">
@@ -5631,7 +5631,7 @@
         <v>-0.7686110148688693</v>
       </c>
       <c r="G208" t="n">
-        <v>0.6154034604025812</v>
+        <v>1.003131569158714</v>
       </c>
     </row>
     <row r="209">
@@ -5656,7 +5656,7 @@
         <v>-0.2171915829150729</v>
       </c>
       <c r="G209" t="n">
-        <v>0.5254974249028412</v>
+        <v>0.3952472834481091</v>
       </c>
     </row>
     <row r="210">
@@ -5681,7 +5681,7 @@
         <v>-0.962525031586438</v>
       </c>
       <c r="G210" t="n">
-        <v>0.5163819878358257</v>
+        <v>0.3002658069252208</v>
       </c>
     </row>
     <row r="211">
@@ -5706,7 +5706,7 @@
         <v>-1.007269503210028</v>
       </c>
       <c r="G211" t="n">
-        <v>0.4852841580118419</v>
+        <v>0.3316121209436056</v>
       </c>
     </row>
     <row r="212">
@@ -5731,7 +5731,7 @@
         <v>-1.347985979776195</v>
       </c>
       <c r="G212" t="n">
-        <v>0.5127327830639198</v>
+        <v>0.5522479520124634</v>
       </c>
     </row>
     <row r="213">
@@ -5756,7 +5756,7 @@
         <v>-1.092419831206434</v>
       </c>
       <c r="G213" t="n">
-        <v>0.5186062015990544</v>
+        <v>0.599459299657599</v>
       </c>
     </row>
     <row r="214">
@@ -5781,7 +5781,7 @@
         <v>-0.3651524675200444</v>
       </c>
       <c r="G214" t="n">
-        <v>0.7052528390632292</v>
+        <v>1.642200669253487</v>
       </c>
     </row>
     <row r="215">
@@ -5806,7 +5806,7 @@
         <v>-0.813456109039279</v>
       </c>
       <c r="G215" t="n">
-        <v>0.5203593278017669</v>
+        <v>0.6135511696864331</v>
       </c>
     </row>
     <row r="216">
@@ -5831,7 +5831,7 @@
         <v>-0.3493082724922306</v>
       </c>
       <c r="G216" t="n">
-        <v>0.5115589970868325</v>
+        <v>0.3017315555677913</v>
       </c>
     </row>
     <row r="217">
@@ -5856,7 +5856,7 @@
         <v>-0.0362508375237905</v>
       </c>
       <c r="G217" t="n">
-        <v>0.7317580553485201</v>
+        <v>1.830723561361999</v>
       </c>
     </row>
     <row r="218">
@@ -5881,7 +5881,7 @@
         <v>-0.8479979797137639</v>
       </c>
       <c r="G218" t="n">
-        <v>0.4668088778224345</v>
+        <v>0.1831052725646437</v>
       </c>
     </row>
     <row r="219">
@@ -5906,7 +5906,7 @@
         <v>0.3593948198147103</v>
       </c>
       <c r="G219" t="n">
-        <v>0.5138836760132525</v>
+        <v>0.3593948198147103</v>
       </c>
     </row>
     <row r="220">
@@ -5931,7 +5931,7 @@
         <v>-0.4182646086026177</v>
       </c>
       <c r="G220" t="n">
-        <v>0.7992003819160949</v>
+        <v>2.310418664325629</v>
       </c>
     </row>
     <row r="221">
@@ -5956,7 +5956,7 @@
         <v>-1.043109723918329</v>
       </c>
       <c r="G221" t="n">
-        <v>0.9508253203478138</v>
+        <v>3.388877017626667</v>
       </c>
     </row>
     <row r="222">
@@ -5981,7 +5981,7 @@
         <v>-1.123559034952408</v>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>4.468968995683205</v>
       </c>
     </row>
     <row r="223">
@@ -6006,7 +6006,7 @@
         <v>-0.655906153036052</v>
       </c>
       <c r="G223" t="n">
-        <v>0.8082516259482172</v>
+        <v>2.374797188301778</v>
       </c>
     </row>
     <row r="224">
@@ -6031,7 +6031,7 @@
         <v>-0.9563978436214826</v>
       </c>
       <c r="G224" t="n">
-        <v>0.9272890782070158</v>
+        <v>3.221471462810959</v>
       </c>
     </row>
     <row r="225">
@@ -6056,7 +6056,7 @@
         <v>0.2270668756329048</v>
       </c>
       <c r="G225" t="n">
-        <v>0.5399745325352203</v>
+        <v>0.5325111195530996</v>
       </c>
     </row>
     <row r="226">
@@ -6081,7 +6081,7 @@
         <v>-1.404118833204703</v>
       </c>
       <c r="G226" t="n">
-        <v>0.9557272924072273</v>
+        <v>4.113098870499632</v>
       </c>
     </row>
     <row r="227">
@@ -6106,7 +6106,7 @@
         <v>-3.152829423596941</v>
       </c>
       <c r="G227" t="n">
-        <v>0.7553621744720782</v>
+        <v>1.998611902847312</v>
       </c>
     </row>
     <row r="228">
@@ -6131,7 +6131,7 @@
         <v>-1.289206038928812</v>
       </c>
       <c r="G228" t="n">
-        <v>0.9395089289547327</v>
+        <v>3.308387244945979</v>
       </c>
     </row>
     <row r="229">
@@ -6156,7 +6156,7 @@
         <v>-0.5365936222611427</v>
       </c>
       <c r="G229" t="n">
-        <v>0.6261505446070396</v>
+        <v>1.079572046917901</v>
       </c>
     </row>
     <row r="230">
@@ -6181,7 +6181,7 @@
         <v>-0.8310544205871934</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6129973684613884</v>
+        <v>0.986017827978479</v>
       </c>
     </row>
     <row r="231">
@@ -6206,7 +6206,7 @@
         <v>-0.6244238617727518</v>
       </c>
       <c r="G231" t="n">
-        <v>0.6462142951592343</v>
+        <v>1.625190742319843</v>
       </c>
     </row>
     <row r="232">
@@ -6231,7 +6231,7 @@
         <v>-1.088558453919593</v>
       </c>
       <c r="G232" t="n">
-        <v>0.889267526655467</v>
+        <v>2.951036662966345</v>
       </c>
     </row>
     <row r="233">
@@ -6256,7 +6256,7 @@
         <v>-1.032210765319538</v>
       </c>
       <c r="G233" t="n">
-        <v>0.5930481878495744</v>
+        <v>1.197834244546017</v>
       </c>
     </row>
     <row r="234">
@@ -6281,7 +6281,7 @@
         <v>2.84582826505566</v>
       </c>
       <c r="G234" t="n">
-        <v>0.8776809367945191</v>
+        <v>2.84582826505566</v>
       </c>
     </row>
     <row r="235">
@@ -6306,7 +6306,7 @@
         <v>1.616630960916539</v>
       </c>
       <c r="G235" t="n">
-        <v>0.7667095077809323</v>
+        <v>2.079321755205378</v>
       </c>
     </row>
     <row r="236">
@@ -6331,7 +6331,7 @@
         <v>0.6791785957572891</v>
       </c>
       <c r="G236" t="n">
-        <v>0.8229620343245406</v>
+        <v>2.479427488290719</v>
       </c>
     </row>
     <row r="237">
@@ -6356,7 +6356,7 @@
         <v>3.406731806065343</v>
       </c>
       <c r="G237" t="n">
-        <v>0.9597483543529494</v>
+        <v>3.406731806065343</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:F314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,6 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -488,7 +487,6 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -508,20 +506,15 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>PC3</t>
+          <t>PC4</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>PC4</t>
+          <t>PC5</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>PC5</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>MaxRel_Score</t>
         </is>
@@ -537,5832 +530,6827 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1461630171032758</v>
+        <v>-0.4195119344233529</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2830717709267092</v>
+        <v>-0.4660838440881593</v>
       </c>
       <c r="D5" t="n">
-        <v>2.763479807123514</v>
+        <v>2.570168971278334</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.159931038013033</v>
+        <v>0.8132021610558516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4481559725105925</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.763479807123514</v>
+        <v>0.875428368862209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.61842307096378</v>
+        <v>-3.556513934636973</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.166129328688029</v>
+        <v>-1.142125407770038</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.182851566076757</v>
+        <v>0.9510782337748471</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.21295224057067</v>
+        <v>-1.198947789636557</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2280902140263398</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.2280902140263398</v>
+        <v>0.6151889609011129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.94899418220281</v>
+        <v>-2.732642337467384</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.925284433762951</v>
+        <v>-0.6877577382785514</v>
       </c>
       <c r="D7" t="n">
-        <v>2.27731399542493</v>
+        <v>2.069306774552422</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8832640027353664</v>
+        <v>0.1360842443220136</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1098273345114712</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.27731399542493</v>
+        <v>0.7949238742549297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.975472939029722</v>
+        <v>3.418341128183126</v>
       </c>
       <c r="C8" t="n">
-        <v>1.160291485359084</v>
+        <v>-1.23199091104253</v>
       </c>
       <c r="D8" t="n">
-        <v>2.931685290551719</v>
+        <v>2.472625585453397</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8363597358625144</v>
+        <v>0.9783204915206499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3156354404163368</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.975472939029722</v>
+        <v>0.8597500425092688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.158486857018305</v>
+        <v>-1.759784704925722</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.517311159518486</v>
+        <v>-0.5624826880101348</v>
       </c>
       <c r="D9" t="n">
-        <v>2.689290658553455</v>
+        <v>2.640735320533334</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.289131891287967</v>
+        <v>0.5988278954596763</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2011033877524098</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.689290658553455</v>
+        <v>0.8867706269128066</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.01182994612998662</v>
+        <v>-1.482432951521547</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.684591911729092</v>
+        <v>-2.524199988445216</v>
       </c>
       <c r="D10" t="n">
-        <v>1.72542878264095</v>
+        <v>0.5371441692211534</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8106820869196382</v>
+        <v>0.9644139817590437</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7232573657160433</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.72542878264095</v>
+        <v>0.5486565835616674</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1685092747940378</v>
+        <v>-1.039128352592894</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2339992025810342</v>
+        <v>-1.172837682867973</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.414281141650042</v>
+        <v>1.449595613050803</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.259369393840901</v>
+        <v>-1.044284745282894</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4446788403161421</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.1685092747940378</v>
+        <v>0.6953165687219887</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.8481886362914927</v>
+        <v>-2.237290392937454</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.704637286806151</v>
+        <v>-2.10562608156653</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.721009913415572</v>
+        <v>-0.513447301400873</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8219106478881908</v>
+        <v>-0.8775541256613852</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02202355758647872</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.02202355758647872</v>
+        <v>0.3797930998848826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.7164653447894558</v>
+        <v>-1.622637005863542</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.944336984631359</v>
+        <v>-1.382550580495274</v>
       </c>
       <c r="D13" t="n">
-        <v>1.980082126228146</v>
+        <v>1.785937948829724</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6499989825683068</v>
+        <v>0.6121181299650731</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3765148355833932</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.980082126228146</v>
+        <v>0.749377485944159</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3562999044695216</v>
+        <v>-0.569677428608911</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.659126151170106</v>
+        <v>-1.554041296054391</v>
       </c>
       <c r="D14" t="n">
-        <v>2.170404167423368</v>
+        <v>1.622863985734888</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2646348156958178</v>
+        <v>0.4190516129546148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0150657937917144</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.170404167423368</v>
+        <v>0.7231663103585916</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7552322148557221</v>
+        <v>-0.2757343362195343</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.614456959361735</v>
+        <v>-1.588752749455761</v>
       </c>
       <c r="D15" t="n">
-        <v>1.872176383011477</v>
+        <v>0.5036554658556712</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9181584723730878</v>
+        <v>0.4711879349990474</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04037724894114841</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.872176383011477</v>
+        <v>0.543273883175983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.660881940237104</v>
+        <v>2.65948819039014</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.199794878257832</v>
+        <v>-1.829698219236582</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6150695869593756</v>
+        <v>-2.71699699845938</v>
       </c>
       <c r="E16" t="n">
-        <v>3.247123106123325</v>
+        <v>-0.5951823492917649</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.30216719642931</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.660881940237104</v>
+        <v>0.6759971933216478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-2.3649278791398</v>
+        <v>-3.263671802234064</v>
       </c>
       <c r="C17" t="n">
-        <v>-3.031381304667946</v>
+        <v>-1.18419344153105</v>
       </c>
       <c r="D17" t="n">
-        <v>1.782195423600141</v>
+        <v>1.692558989926904</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6723566193204957</v>
+        <v>0.411098263247451</v>
       </c>
       <c r="F17" t="n">
-        <v>0.298223176955328</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.782195423600141</v>
+        <v>0.7343685155276131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8368269871156375</v>
+        <v>-0.008930101492554281</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.076897913852441</v>
+        <v>-1.360558039340776</v>
       </c>
       <c r="D18" t="n">
-        <v>2.331876477399435</v>
+        <v>1.727457404946159</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3182199128360695</v>
+        <v>0.5444190453612425</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05340069262867814</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.331876477399435</v>
+        <v>0.7399778014391581</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.949847872202055</v>
+        <v>1.364264432413657</v>
       </c>
       <c r="C19" t="n">
-        <v>1.226906681163135</v>
+        <v>-0.9743060333187968</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0820872779230888</v>
+        <v>2.639056972328434</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.569168821793931</v>
+        <v>-2.034129648358749</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.483859035078137</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.949847872202055</v>
+        <v>0.8865008629440071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7465135631616248</v>
+        <v>-0.3624509392039922</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.4013403221579306</v>
+        <v>-1.921668233693249</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.228808898461442</v>
+        <v>0.1020434791323256</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.185963437294383</v>
+        <v>-0.4751829882288403</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1599334242983557</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.7465135631616248</v>
+        <v>0.4787220558854894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.253632497881782</v>
+        <v>-2.850572094728604</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.069920739796283</v>
+        <v>-0.5005500067808011</v>
       </c>
       <c r="D21" t="n">
-        <v>2.240589840363225</v>
+        <v>2.272851443191966</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.122935549455663</v>
+        <v>0.6728391145625736</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5151875717321431</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.240589840363225</v>
+        <v>0.8276399801737792</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.812069921391803</v>
+        <v>1.466952807984113</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3089824857697</v>
+        <v>-0.4503854881361565</v>
       </c>
       <c r="D22" t="n">
-        <v>2.14217953067516</v>
+        <v>3.345196764767052</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.707103258251648</v>
+        <v>-0.1226673444420872</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2458269768227078</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.14217953067516</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.031664809092879</v>
+        <v>-2.86230179987503</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.339730116487223</v>
+        <v>-0.956797660777561</v>
       </c>
       <c r="D23" t="n">
-        <v>2.049351828762988</v>
+        <v>2.039373360368817</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9593342209431666</v>
+        <v>0.5355743947452036</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3890834931741244</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.049351828762988</v>
+        <v>0.7901126219853953</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.750516170830915</v>
+        <v>0.729820643750467</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3855112466161313</v>
+        <v>-1.749009366378937</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8920854058379685</v>
+        <v>0.7239303781105761</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.644561760504088</v>
+        <v>-0.7088260566819197</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.263110520300714</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.750516170830915</v>
+        <v>0.5786790716722673</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.297408573733281</v>
+        <v>0.2015279032647203</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.5531380335439952</v>
+        <v>-1.981213329832568</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7098264489323145</v>
+        <v>0.6098661463287984</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.252159608114467</v>
+        <v>-1.159994691517118</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6091386422503443</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.297408573733281</v>
+        <v>0.5603453196095525</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1267166616629151</v>
+        <v>-0.9374741982360316</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1262227552824805</v>
+        <v>-1.132550981390873</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6530638644716826</v>
+        <v>1.780252340560303</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.879120418322136</v>
+        <v>-1.19173088925595</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.487085405320118</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.1262227552824805</v>
+        <v>0.7484636277547073</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2563066744296122</v>
+        <v>-0.2865032767134751</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.286603496790511</v>
+        <v>-0.5291481963763114</v>
       </c>
       <c r="D27" t="n">
-        <v>2.760509079714799</v>
+        <v>2.821589937623261</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.465575326243233</v>
+        <v>0.5272938642498802</v>
       </c>
       <c r="F27" t="n">
-        <v>0.191087196148281</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.760509079714799</v>
+        <v>0.915839719452416</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.890769349844495</v>
+        <v>1.648340365907385</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4176783503458927</v>
+        <v>-2.189366731619616</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.440996099631296</v>
+        <v>-2.082483341934498</v>
       </c>
       <c r="E28" t="n">
-        <v>1.528924025574536</v>
+        <v>-0.6770176248238374</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5607045290296652</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.890769349844495</v>
+        <v>0.599367293516583</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2963143150595054</v>
+        <v>-1.64636765269775</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.374030983295713</v>
+        <v>-3.532756859389116</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.592151797078886</v>
+        <v>-2.519146958162668</v>
       </c>
       <c r="E29" t="n">
-        <v>1.396823502055015</v>
+        <v>-0.9888165227779678</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.187861406564276</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.396823502055015</v>
+        <v>0.3496776445458151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.114576865878735</v>
+        <v>1.319267445799227</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4561645542585586</v>
+        <v>-1.244104780052123</v>
       </c>
       <c r="D30" t="n">
-        <v>1.841000626125448</v>
+        <v>0.05200216731138559</v>
       </c>
       <c r="E30" t="n">
-        <v>1.661775072365689</v>
+        <v>1.148490600395166</v>
       </c>
       <c r="F30" t="n">
-        <v>0.478674549516585</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.114576865878735</v>
+        <v>0.5744284821124763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.05587728398447637</v>
+        <v>-1.042184603004716</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.154686338107861</v>
+        <v>-1.663203144488622</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.208586529855833</v>
+        <v>-0.3358165794164945</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.528443406890065</v>
+        <v>-1.186269001309663</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.633238882931122</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.05587728398447637</v>
+        <v>0.4274371806522259</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.981908648169002</v>
+        <v>1.477617926089766</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.519456137488236</v>
+        <v>-2.827125725599659</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.586383492277014</v>
+        <v>-2.602136135131042</v>
       </c>
       <c r="E32" t="n">
-        <v>2.20004623168318</v>
+        <v>-0.8095610581868992</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7697715287667245</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.981908648169002</v>
+        <v>0.5864290829592963</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5272604864964361</v>
+        <v>-1.569498969483431</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.757565527648523</v>
+        <v>-1.765666324649121</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.293187217031307</v>
+        <v>0.1203560523721204</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.08021719865085</v>
+        <v>-0.3771918964833491</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2864756987871691</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.2864756987871691</v>
+        <v>0.4816654691901178</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2843845156874721</v>
+        <v>-0.3398922854668763</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1902703507386197</v>
+        <v>-0.9439326234644515</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3452403717077387</v>
+        <v>2.205474152118386</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.118111757274341</v>
+        <v>-1.429800315759094</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8229604609119283</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.2843845156874721</v>
+        <v>0.8168103052625093</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.008968663813961</v>
+        <v>2.349392472199256</v>
       </c>
       <c r="C35" t="n">
-        <v>1.72734782158501</v>
+        <v>-1.261789259385896</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1071423841781833</v>
+        <v>1.423108624692335</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.979194873782933</v>
+        <v>-0.5749998153035886</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3323228525645893</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.008968663813961</v>
+        <v>0.6910592667626752</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.096144918039989</v>
+        <v>-0.3689108405937345</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.012537915989258</v>
+        <v>-2.485814416446983</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.566229961667883</v>
+        <v>-0.7309684481686501</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.2111682135202834</v>
+        <v>-0.120757864846565</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6083797869825953</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.096144918039989</v>
+        <v>0.4464897872875588</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.390154119132507</v>
+        <v>0.4994969098945983</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3359104167086873</v>
+        <v>-1.52543208081428</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6986618072380764</v>
+        <v>1.711953152018167</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.747224801904364</v>
+        <v>-1.726618397743815</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.128089700601403</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1.390154119132507</v>
+        <v>0.7374857745814903</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4614431773001467</v>
+        <v>-0.3892448701501115</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.272841961854766</v>
+        <v>-1.225447376189067</v>
       </c>
       <c r="D38" t="n">
-        <v>2.329091938623054</v>
+        <v>1.520657980203532</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02000065937321023</v>
+        <v>0.4577514791389596</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.06100077834916965</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.329091938623054</v>
+        <v>0.7067385526341784</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.496490641299062</v>
+        <v>2.098864851231217</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3630888933851129</v>
+        <v>-2.878531891710405</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.684343026396639</v>
+        <v>0.02196145033098014</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.235971834270616</v>
+        <v>-0.6387953603671084</v>
       </c>
       <c r="F39" t="n">
-        <v>0.05663323021793536</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3.496490641299062</v>
+        <v>0.6335103192287275</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.004051977027507</v>
+        <v>0.2774167769873147</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01682419404342771</v>
+        <v>-1.160564652179614</v>
       </c>
       <c r="D40" t="n">
-        <v>1.764210717020153</v>
+        <v>2.345177643445632</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.597679228265277</v>
+        <v>0.6551223299533194</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6018438449320197</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1.764210717020153</v>
+        <v>0.839265102285905</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.02584519600344023</v>
+        <v>-0.767967540942014</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.492514202663214</v>
+        <v>-0.9230748920394523</v>
       </c>
       <c r="D41" t="n">
-        <v>2.640973257360858</v>
+        <v>1.488632715879264</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1702998710440349</v>
+        <v>1.074074022104394</v>
       </c>
       <c r="F41" t="n">
-        <v>0.43835146177413</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.640973257360858</v>
+        <v>0.701591073475354</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.831779336136942</v>
+        <v>2.70470005568864</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.2533712924685882</v>
+        <v>-1.991415591061618</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.209108675880971</v>
+        <v>-0.525172274011186</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5989791318749325</v>
+        <v>-0.03386872592200748</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1327326221235222</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3.831779336136942</v>
+        <v>0.6794235773022457</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6.555506950144018</v>
+        <v>4.870749143283886</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5305752111939868</v>
+        <v>-3.69875034010539</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.263601978316839</v>
+        <v>-1.653513751179224</v>
       </c>
       <c r="E43" t="n">
-        <v>1.22162492489978</v>
+        <v>-0.04482669724439057</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2526557449325313</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6.555506950144018</v>
+        <v>0.8435777400629513</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.557871964241698</v>
+        <v>2.486762166006088</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7957803428894118</v>
+        <v>-2.152828515825692</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.02208469318061384</v>
+        <v>1.472405412640346</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.670088070269003</v>
+        <v>-0.961908584890402</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.5990870643821545</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.557871964241698</v>
+        <v>0.6989828294221436</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.893366224598804</v>
+        <v>2.049190168862161</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8199709332536217</v>
+        <v>-1.825571651929314</v>
       </c>
       <c r="D45" t="n">
-        <v>1.177464176677081</v>
+        <v>-0.270942191062543</v>
       </c>
       <c r="E45" t="n">
-        <v>1.185782260096363</v>
+        <v>4.142707699025716</v>
       </c>
       <c r="F45" t="n">
-        <v>3.681838434817529</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.681838434817529</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.337393455759457</v>
+        <v>0.5127207977770396</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5331758392759078</v>
+        <v>-1.29256828071152</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6024635876501555</v>
+        <v>1.47989231598431</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.451075413770698</v>
+        <v>-1.150031731892318</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.6400317145522038</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.337393455759457</v>
+        <v>0.7001862130550459</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.8696228508612583</v>
+        <v>-1.792165211649194</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.6780040357184001</v>
+        <v>-1.251804313498287</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.8316796114408801</v>
+        <v>1.088345835389974</v>
       </c>
       <c r="E47" t="n">
-        <v>-2.11581238940162</v>
+        <v>-0.2403186975326974</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4202137105699785</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.4202137105699785</v>
+        <v>0.6372522329272635</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.917489125100054</v>
+        <v>2.200407866350103</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3013469030487012</v>
+        <v>-1.461401464134005</v>
       </c>
       <c r="D48" t="n">
-        <v>2.642621409451311</v>
+        <v>2.136895950816551</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.619292308046149</v>
+        <v>1.230451538415712</v>
       </c>
       <c r="F48" t="n">
-        <v>0.661193444829144</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.917489125100054</v>
+        <v>0.8057876058594206</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.4022551669291249</v>
+        <v>-1.45308171897122</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.554329369729555</v>
+        <v>-1.689117953600398</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9984175910096292</v>
+        <v>0.6555571206292281</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.521855557076872</v>
+        <v>-1.168569733602351</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.536947676587389</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.4022551669291249</v>
+        <v>0.5676893132633262</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.701127217951179</v>
+        <v>0.6001309708084492</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5255717405315506</v>
+        <v>-2.008947308995419</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.7490546763134789</v>
+        <v>0.9964327705277104</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.883228847554964</v>
+        <v>-2.324089542917013</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.986107704915156</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.701127217951179</v>
+        <v>0.6224788783341002</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.354622465982963</v>
+        <v>1.416071278997086</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2169522388396917</v>
+        <v>-1.826408208811362</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1462368872799416</v>
+        <v>1.378972274383189</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.850664987457779</v>
+        <v>-2.694584532907937</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.559989688843802</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.354622465982963</v>
+        <v>0.6839651506591352</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.755914530699477</v>
+        <v>0.606677987571263</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3932650110784013</v>
+        <v>-2.099490302949656</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.285858004246176</v>
+        <v>0.5015133020740463</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.801379598214613</v>
+        <v>-2.521588629224988</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.990840503368205</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.755914530699477</v>
+        <v>0.5429295692833933</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.831748300360889</v>
+        <v>1.63161689248705</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5698189879606708</v>
+        <v>-2.383506799095743</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.549240827464957</v>
+        <v>0.104495929545711</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.368068382791717</v>
+        <v>-0.5977029411227951</v>
       </c>
       <c r="F53" t="n">
-        <v>0.08171329404120221</v>
-      </c>
-      <c r="G53" t="n">
-        <v>2.831748300360889</v>
+        <v>0.5980999040592121</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2442386661857714</v>
+        <v>-1.043914860230793</v>
       </c>
       <c r="C54" t="n">
-        <v>-1.489400948004193</v>
+        <v>-2.177770986232654</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.452284749538686</v>
+        <v>-0.4407484402379381</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5588161764787654</v>
+        <v>-0.7449282240862437</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1511661431674419</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.2442386661857714</v>
+        <v>0.3953345663194837</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.859064533468148</v>
+        <v>2.674806279624932</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5949047331578832</v>
+        <v>-2.480076348523352</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.249725436149384</v>
+        <v>0.2076123653555517</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.164560056284858</v>
+        <v>-1.650000716804917</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.016166214201748</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3.859064533468148</v>
+        <v>0.677158075652446</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.029942607617384</v>
+        <v>1.737705392207292</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5056992805458262</v>
+        <v>-2.621169458897848</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.841305546190881</v>
+        <v>-0.07212510468772937</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.359147195369583</v>
+        <v>-0.5425870117080887</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2041376924456348</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3.029942607617384</v>
+        <v>0.6061398275077845</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7333748808754794</v>
+        <v>-1.806310219326617</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.29581634812179</v>
+        <v>-1.789523632560072</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.7028897843651414</v>
+        <v>1.003843933694974</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.752716859612337</v>
+        <v>0.5937294866092923</v>
       </c>
       <c r="F57" t="n">
-        <v>1.114846676565727</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1.114846676565727</v>
+        <v>0.6236700881102278</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.236425197476465</v>
+        <v>0.2065031424730624</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5229166707300932</v>
+        <v>-1.592302761568185</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9519113489681915</v>
+        <v>0.1530086738765252</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.050607832484112</v>
+        <v>-0.4761344319551133</v>
       </c>
       <c r="F58" t="n">
-        <v>0.005734034642913454</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1.236425197476465</v>
+        <v>0.4900975712348741</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.439541641446721</v>
+        <v>-2.739617175055792</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.461612245429088</v>
+        <v>-2.056938491948376</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.206520528247183</v>
+        <v>-0.202739161395296</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5504189769382474</v>
+        <v>-0.3421883179877853</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2620814423873599</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.2620814423873599</v>
+        <v>0.4297337860557036</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4.253570297804814</v>
+        <v>2.89889129164797</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4821206401543292</v>
+        <v>-3.018771259497401</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.101857824483052</v>
+        <v>0.0438493236574022</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.8592076220340685</v>
+        <v>-0.5796259757708677</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.06090283215241446</v>
-      </c>
-      <c r="G60" t="n">
-        <v>4.253570297804814</v>
+        <v>0.6941403720124526</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.720510760065293</v>
+        <v>-0.04790360619361342</v>
       </c>
       <c r="C61" t="n">
-        <v>-3.283531393661418</v>
+        <v>-2.681316535588999</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1777485130759779</v>
+        <v>-2.672846739256908</v>
       </c>
       <c r="E61" t="n">
-        <v>4.292117288815221</v>
+        <v>-0.2260011638787932</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.378067637022015</v>
-      </c>
-      <c r="G61" t="n">
-        <v>4.292117288815221</v>
+        <v>0.4708173402063078</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6.721331834074801</v>
+        <v>4.830789421663072</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.2378281737638503</v>
+        <v>-4.152460467451951</v>
       </c>
       <c r="D62" t="n">
-        <v>-1.482955547530763</v>
+        <v>-2.112170975953126</v>
       </c>
       <c r="E62" t="n">
-        <v>1.608521071413265</v>
+        <v>0.004141674272815476</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2688249326222985</v>
-      </c>
-      <c r="G62" t="n">
-        <v>6.721331834074801</v>
+        <v>0.8405493901126285</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.084890527059936</v>
+        <v>-0.5554439751975372</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.648009856997918</v>
+        <v>-2.708880323945292</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.104312921431662</v>
+        <v>-1.61758713599114</v>
       </c>
       <c r="E63" t="n">
-        <v>1.172734572661247</v>
+        <v>-1.032157388680614</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7043113833963557</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1.172734572661247</v>
+        <v>0.4323533622575924</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.751073100130719</v>
+        <v>0.4599297604412184</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.077547471185917</v>
+        <v>-2.314523064790556</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8186403210752722</v>
+        <v>-0.1074685637118097</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.4451878713022363</v>
+        <v>-1.247869588913733</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8410704702600007</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.751073100130719</v>
+        <v>0.509303522998426</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5.165385367077522</v>
+        <v>3.328955408487943</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.21244588903694</v>
+        <v>-3.82239209350755</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.698425369095952</v>
+        <v>-2.377672935212005</v>
       </c>
       <c r="E65" t="n">
-        <v>1.741456655909494</v>
+        <v>-0.1752967835909997</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1323380202061264</v>
-      </c>
-      <c r="G65" t="n">
-        <v>5.165385367077522</v>
+        <v>0.726732807445975</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3.927630929673222</v>
+        <v>2.733701641129556</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.8339453898192339</v>
+        <v>-2.210764700868111</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8000528662636212</v>
+        <v>-1.46874995320997</v>
       </c>
       <c r="E66" t="n">
-        <v>1.169320434116975</v>
+        <v>-1.022750956451444</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.094260807743402</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3.927630929673222</v>
+        <v>0.6816214642310559</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.391681541309022</v>
+        <v>3.584832268187704</v>
       </c>
       <c r="C67" t="n">
-        <v>0.588705010907279</v>
+        <v>-1.910437578091913</v>
       </c>
       <c r="D67" t="n">
-        <v>2.44515658057355</v>
+        <v>1.830752068785988</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2749326915845541</v>
+        <v>1.076691743862464</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5420714604346089</v>
-      </c>
-      <c r="G67" t="n">
-        <v>4.391681541309022</v>
+        <v>0.7565805411995415</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.625018578307704</v>
+        <v>1.248475483005489</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4208195679317051</v>
+        <v>-0.3886361581046381</v>
       </c>
       <c r="D68" t="n">
-        <v>2.96181698670493</v>
+        <v>2.850179147060191</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.369553483197379</v>
+        <v>-0.1657087368557366</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8188432413649119</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2.96181698670493</v>
+        <v>0.9204349152407724</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.439829056709893</v>
+        <v>0.7429435252388549</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5391272967615832</v>
+        <v>-1.146908267405378</v>
       </c>
       <c r="D69" t="n">
-        <v>2.519851425934307</v>
+        <v>1.762364219115379</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.2292652497648993</v>
+        <v>1.085597884938893</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5884704727570466</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2.519851425934307</v>
+        <v>0.7455884373613997</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3.882269467735987</v>
+        <v>3.036331682919657</v>
       </c>
       <c r="C70" t="n">
-        <v>0.3859021438073764</v>
+        <v>-1.853675488624245</v>
       </c>
       <c r="D70" t="n">
-        <v>2.446547528586752</v>
+        <v>1.791599559809583</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.2538932574431716</v>
+        <v>1.173364605950211</v>
       </c>
       <c r="F70" t="n">
-        <v>0.6313690995957126</v>
-      </c>
-      <c r="G70" t="n">
-        <v>3.882269467735987</v>
+        <v>0.7502874870054808</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.259695112876489</v>
+        <v>1.27762526182336</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4124096069512407</v>
+        <v>-1.846198692166786</v>
       </c>
       <c r="D71" t="n">
-        <v>2.001300295158102</v>
+        <v>1.220066211369678</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1016510303501927</v>
+        <v>1.547068002199737</v>
       </c>
       <c r="F71" t="n">
-        <v>1.119488047643306</v>
-      </c>
-      <c r="G71" t="n">
-        <v>2.259695112876489</v>
+        <v>0.6584238892571777</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.93171650680845</v>
+        <v>1.092470102492731</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.246861032558254</v>
+        <v>-3.867708509416376</v>
       </c>
       <c r="D72" t="n">
-        <v>1.015875801478323</v>
+        <v>-0.1220915521045159</v>
       </c>
       <c r="E72" t="n">
-        <v>1.113760588626013</v>
+        <v>3.559738344946461</v>
       </c>
       <c r="F72" t="n">
-        <v>3.441225940226508</v>
-      </c>
-      <c r="G72" t="n">
-        <v>3.441225940226508</v>
+        <v>0.914736808914428</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5.600905185773277</v>
+        <v>3.705598348981645</v>
       </c>
       <c r="C73" t="n">
-        <v>1.324891464506641</v>
+        <v>-4.490862550127679</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.54604777660728</v>
+        <v>-0.6508345786011948</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.3795126897460858</v>
+        <v>2.725698992931777</v>
       </c>
       <c r="F73" t="n">
-        <v>3.354816259848985</v>
-      </c>
-      <c r="G73" t="n">
-        <v>5.600905185773277</v>
+        <v>0.7927529410728149</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4.641127841209785</v>
+        <v>3.745044472885484</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6403242024800895</v>
+        <v>-2.075543807863185</v>
       </c>
       <c r="D74" t="n">
-        <v>2.747678329341149</v>
+        <v>2.134361991426617</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.4857227734505894</v>
+        <v>0.9659367975786811</v>
       </c>
       <c r="F74" t="n">
-        <v>0.413036395460917</v>
-      </c>
-      <c r="G74" t="n">
-        <v>4.641127841209785</v>
+        <v>0.8053803179439509</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.422931739155248</v>
+        <v>1.871156199446205</v>
       </c>
       <c r="C75" t="n">
-        <v>0.694603504653542</v>
+        <v>-0.8226642061787089</v>
       </c>
       <c r="D75" t="n">
-        <v>2.867646459747699</v>
+        <v>2.560765568963235</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9756382137286365</v>
+        <v>0.8482761382834464</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4008740656604979</v>
-      </c>
-      <c r="G75" t="n">
-        <v>2.867646459747699</v>
+        <v>0.8739169428533896</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.54754624141797</v>
+        <v>2.011543654362223</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.1420697621067095</v>
+        <v>-0.9313046021949455</v>
       </c>
       <c r="D76" t="n">
-        <v>3.201937143472751</v>
+        <v>2.672366247717456</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9066829971401626</v>
+        <v>-0.5171394983765513</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.38265272173316</v>
-      </c>
-      <c r="G76" t="n">
-        <v>3.201937143472751</v>
+        <v>0.8918547235437025</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.612800923759805</v>
+        <v>0.736207309485154</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3983365856625974</v>
+        <v>-1.584287211314497</v>
       </c>
       <c r="D77" t="n">
-        <v>2.190284421048478</v>
+        <v>1.762507876497283</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.4804905232448999</v>
+        <v>1.27200772905662</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8733700831459458</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2.190284421048478</v>
+        <v>0.7456115276744687</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.74901437268143</v>
+        <v>1.894474151095204</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.1084537780728595</v>
+        <v>-1.673483949526989</v>
       </c>
       <c r="D78" t="n">
-        <v>2.258560850647712</v>
+        <v>1.560472310888082</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.10915958426013</v>
+        <v>1.22605668469724</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7387695177326324</v>
-      </c>
-      <c r="G78" t="n">
-        <v>2.74901437268143</v>
+        <v>0.7131379826387567</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.4734431126533395</v>
+        <v>-1.439691721669145</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6465911402704233</v>
+        <v>-1.47217355078788</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.5377542214199683</v>
+        <v>1.273663409670169</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.960698538998704</v>
+        <v>0.08525776919637312</v>
       </c>
       <c r="F79" t="n">
-        <v>0.675456641873503</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.675456641873503</v>
+        <v>0.6670386647178785</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.306237217147264</v>
+        <v>0.1643757715452476</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.389894957891074</v>
+        <v>-1.89234987021767</v>
       </c>
       <c r="D80" t="n">
-        <v>2.234811351149597</v>
+        <v>1.210214481049945</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2682474220609176</v>
+        <v>1.004752836907743</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6142898632900973</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2.234811351149597</v>
+        <v>0.6568404026702845</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3.67803512406718</v>
+        <v>3.073875442608585</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5909833209329661</v>
+        <v>-1.28408703041189</v>
       </c>
       <c r="D81" t="n">
-        <v>2.946025923939023</v>
+        <v>2.489365025516056</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.733676393169858</v>
+        <v>0.1286140804379066</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.4858923464044823</v>
-      </c>
-      <c r="G81" t="n">
-        <v>3.67803512406718</v>
+        <v>0.8624406032484547</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.102291927982409</v>
+        <v>1.391602924069187</v>
       </c>
       <c r="C82" t="n">
-        <v>0.5240442890198951</v>
+        <v>-1.126449819645205</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1278549153132864</v>
+        <v>1.435112260634117</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.898611718858809</v>
+        <v>-2.650112491409349</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.679523865859168</v>
-      </c>
-      <c r="G82" t="n">
-        <v>2.102291927982409</v>
+        <v>0.6929886330659415</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.375731789244887</v>
+        <v>0.3282419540653854</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.2841528374220448</v>
+        <v>-1.878371981994969</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.9911566270194123</v>
+        <v>1.103081527051819</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.123036001117732</v>
+        <v>-1.350731652089521</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.6009409013509414</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.375731789244887</v>
+        <v>0.63962072753053</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3.650971145561097</v>
+        <v>2.152429474808053</v>
       </c>
       <c r="C84" t="n">
-        <v>-1.069193164904969</v>
+        <v>-2.996339265691621</v>
       </c>
       <c r="D84" t="n">
-        <v>1.86524277841623</v>
+        <v>0.5512713889690511</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9761304867284574</v>
+        <v>0.9840067066319583</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6387877130265049</v>
-      </c>
-      <c r="G84" t="n">
-        <v>3.650971145561097</v>
+        <v>0.6375697175070046</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.993905594326431</v>
+        <v>1.933645193288293</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.5754280415407723</v>
+        <v>-2.099876518330802</v>
       </c>
       <c r="D85" t="n">
-        <v>2.276108632192367</v>
+        <v>1.314316568909814</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2384530455286678</v>
+        <v>1.164950726828277</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6836269438271769</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2.993905594326431</v>
+        <v>0.6735729211664</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5.994649004624828</v>
+        <v>4.715428532332534</v>
       </c>
       <c r="C86" t="n">
-        <v>0.09379496059533921</v>
+        <v>-2.927320758078244</v>
       </c>
       <c r="D86" t="n">
-        <v>2.216906959638711</v>
+        <v>0.4997827217294047</v>
       </c>
       <c r="E86" t="n">
-        <v>1.297515288832765</v>
+        <v>1.565610871771081</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9021676857652036</v>
-      </c>
-      <c r="G86" t="n">
-        <v>5.994649004624828</v>
+        <v>0.8318067580495626</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.0716826007252645</v>
+        <v>-1.265767594382391</v>
       </c>
       <c r="C87" t="n">
-        <v>-2.259233990916757</v>
+        <v>-1.790068818395849</v>
       </c>
       <c r="D87" t="n">
-        <v>2.082519693034055</v>
+        <v>1.021095756696391</v>
       </c>
       <c r="E87" t="n">
-        <v>0.400440579422697</v>
+        <v>-0.1024833938394327</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.6111783377618998</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2.082519693034055</v>
+        <v>0.6264430050939052</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.455689547548723</v>
+        <v>0.1172208193228845</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.762811633415942</v>
+        <v>-2.313570666032542</v>
       </c>
       <c r="D88" t="n">
-        <v>1.671309493066756</v>
+        <v>0.3300007243006164</v>
       </c>
       <c r="E88" t="n">
-        <v>1.020791049551393</v>
+        <v>0.6927927818544081</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3393065010980859</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1.671309493066756</v>
+        <v>0.5153620397658929</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.6300563840674588</v>
+        <v>-1.838567936931126</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.061309204420766</v>
+        <v>-1.882669540313854</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.6069763381490443</v>
+        <v>0.6842793664450749</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.308009574396477</v>
+        <v>0.6233686544013575</v>
       </c>
       <c r="F89" t="n">
-        <v>1.177133058657776</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1.177133058657776</v>
+        <v>0.572305892231565</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3.102842087588441</v>
+        <v>1.967082091421543</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5962109768908158</v>
+        <v>-2.389383945358097</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.161948046679061</v>
+        <v>0.3220380550562172</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.280750594691914</v>
+        <v>-0.3144412415614247</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1852093443319505</v>
-      </c>
-      <c r="G90" t="n">
-        <v>3.102842087588441</v>
+        <v>0.6235231547056608</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.357077591889135</v>
+        <v>0.9405982695952468</v>
       </c>
       <c r="C91" t="n">
-        <v>0.3377884854966019</v>
+        <v>-0.5221363735236013</v>
       </c>
       <c r="D91" t="n">
-        <v>2.924915352577265</v>
+        <v>3.26284177802724</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.887001556146362</v>
+        <v>0.2598248194096635</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.1005942475604853</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2.924915352577265</v>
+        <v>0.9867629327403485</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3.362997082671668</v>
+        <v>2.092628900478926</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6114393606530381</v>
+        <v>-2.642928383626745</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.30109193151684</v>
+        <v>-0.1643021282428402</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.8730571517962926</v>
+        <v>-0.1155861251568424</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3788151064100657</v>
-      </c>
-      <c r="G92" t="n">
-        <v>3.362997082671668</v>
+        <v>0.6330377273190512</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4.314021542726616</v>
+        <v>3.084154141652329</v>
       </c>
       <c r="C93" t="n">
-        <v>1.667025264466083</v>
+        <v>-2.696647460029953</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.697165519117817</v>
+        <v>-0.09894899774449423</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.368536115273023</v>
+        <v>0.08172978685871347</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7650340129331171</v>
-      </c>
-      <c r="G93" t="n">
-        <v>4.314021542726616</v>
+        <v>0.708180528446253</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-1.479897126734461</v>
+        <v>-2.570936930083669</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.53235087981043</v>
+        <v>-1.472466567790199</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.9948873764699908</v>
+        <v>0.4551502338205633</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.353137802142319</v>
+        <v>-0.4237476399713649</v>
       </c>
       <c r="F94" t="n">
-        <v>0.28106403645769</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.28106403645769</v>
+        <v>0.535477548742438</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.4712671734293135</v>
+        <v>2.284979709087783</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.357928779475431</v>
+        <v>2.511081412547276</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.038370805348676</v>
+        <v>-0.7777448555776301</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.8362323636200973</v>
+        <v>0.2847132985678413</v>
       </c>
       <c r="F95" t="n">
-        <v>0.02433001605627384</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.4712671734293135</v>
+        <v>0.8925394350711079</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3.419836466439655</v>
+        <v>-0.9237323690284843</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.7046764791470588</v>
+        <v>-2.432706763882072</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.233668887015886</v>
+        <v>0.05742994940020209</v>
       </c>
       <c r="E96" t="n">
-        <v>0.5823711694053896</v>
+        <v>-0.5719594047518956</v>
       </c>
       <c r="F96" t="n">
-        <v>0.316308908648707</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3.419836466439655</v>
+        <v>0.4715512418627715</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2.496300783960359</v>
+        <v>1.989463893239453</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.772332189042571</v>
+        <v>-2.687358159191414</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.681330466262061</v>
+        <v>-1.24682270073916</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8913062809110552</v>
+        <v>0.1438945825467666</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.6274446345226417</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2.496300783960359</v>
+        <v>0.62521936092718</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.07460541267196</v>
+        <v>0.8725892451013545</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.049913595301275</v>
+        <v>-3.093980568815844</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.620220973066474</v>
+        <v>-1.636185564490966</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.2745125618607719</v>
+        <v>-1.10074742751748</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3577400192920832</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2.07460541267196</v>
+        <v>0.5405769473162717</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.999527390187418</v>
+        <v>0.3670336561595248</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.156679533706541</v>
+        <v>-3.197372112518885</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.6777949870155584</v>
+        <v>-0.73812679321852</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3974150841908107</v>
+        <v>-0.3861396179946792</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.6287489291991131</v>
-      </c>
-      <c r="G99" t="n">
-        <v>1.999527390187418</v>
+        <v>0.5022633860461179</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.580632863388202</v>
+        <v>0.6160652749145055</v>
       </c>
       <c r="C100" t="n">
-        <v>-2.150490192749234</v>
+        <v>-2.42449706171116</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.9298410963006669</v>
+        <v>-0.6510925612359466</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5158132170675322</v>
+        <v>-0.8231661594626066</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.5038878653218247</v>
-      </c>
-      <c r="G100" t="n">
-        <v>1.580632863388202</v>
+        <v>0.5211362625251322</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1.618941185585461</v>
+        <v>0.04038853156291139</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.54081422181885</v>
+        <v>-2.999890878298487</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.654842583243645</v>
+        <v>-0.7609780050244566</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5091560069959498</v>
+        <v>-0.8460506226987625</v>
       </c>
       <c r="F101" t="n">
-        <v>2.490543804887305</v>
-      </c>
-      <c r="G101" t="n">
-        <v>2.490543804887305</v>
+        <v>0.4775085652735411</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8985095536166571</v>
+        <v>-0.3009293547616623</v>
       </c>
       <c r="C102" t="n">
-        <v>-2.014381739605798</v>
+        <v>-3.844353800151849</v>
       </c>
       <c r="D102" t="n">
-        <v>-2.103920126488463</v>
+        <v>-1.370145024621824</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.6024043892282173</v>
+        <v>2.058255897092977</v>
       </c>
       <c r="F102" t="n">
-        <v>2.259100056813676</v>
-      </c>
-      <c r="G102" t="n">
-        <v>2.259100056813676</v>
+        <v>0.6951348967947746</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7690516142844713</v>
+        <v>-1.374066847992175</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.7793796419223545</v>
+        <v>-4.425495612905637</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.232270711403085</v>
+        <v>-0.7101735641601755</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.544345589737193</v>
+        <v>1.105498797802428</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.6564639066398494</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.7690516142844713</v>
+        <v>0.5557877595112918</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-2.696758330834611</v>
+        <v>-0.3544708743658319</v>
       </c>
       <c r="C104" t="n">
-        <v>-2.15624905610703</v>
+        <v>-1.972999745344633</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.5146928646770766</v>
+        <v>0.5125206606133792</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.958080545394549</v>
+        <v>-1.390577281576049</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2549825368686213</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0.2549825368686213</v>
+        <v>0.5446988021022459</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3.55318567121627</v>
+        <v>-3.611888463805845</v>
       </c>
       <c r="C105" t="n">
-        <v>1.002939503884801</v>
+        <v>-1.158418524093345</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.126254408870247</v>
+        <v>1.251614665824742</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.424677001963086</v>
+        <v>-0.4896488581579503</v>
       </c>
       <c r="F105" t="n">
-        <v>0.06312144951122764</v>
-      </c>
-      <c r="G105" t="n">
-        <v>3.55318567121627</v>
+        <v>0.6634947298958765</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3.628259546920428</v>
+        <v>2.412304344207625</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9121714838650443</v>
+        <v>-2.412549697018496</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.7933724643384455</v>
+        <v>0.3816881753645561</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.353976378872652</v>
+        <v>-0.4553232739853179</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2092706182527805</v>
-      </c>
-      <c r="G106" t="n">
-        <v>3.628259546920428</v>
+        <v>0.6572643504002024</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-1.360558816998082</v>
+        <v>2.518313469767968</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.910537857825419</v>
+        <v>-2.447841766956383</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.9456069335605172</v>
+        <v>0.5907842791285374</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.576440884683023</v>
+        <v>-0.1744022873879949</v>
       </c>
       <c r="F107" t="n">
-        <v>0.02075406377236158</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0.02075406377236158</v>
+        <v>0.6652982584732056</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.216623186227426</v>
+        <v>-2.287427825976956</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.4311546262664994</v>
+        <v>-1.107211390967485</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.572597589535271</v>
+        <v>0.4669853192864558</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1721000406428136</v>
+        <v>-0.7273135376168756</v>
       </c>
       <c r="F108" t="n">
-        <v>0.8438185853079608</v>
-      </c>
-      <c r="G108" t="n">
-        <v>3.216623186227426</v>
+        <v>0.5373798236202265</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.419031303557776</v>
+        <v>1.626583349923795</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.8835396072265423</v>
+        <v>-2.96405012569673</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.284493238932921</v>
+        <v>-1.121000504252525</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.727969133042968</v>
+        <v>0.2461595218515032</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5883443989180057</v>
-      </c>
-      <c r="G109" t="n">
-        <v>1.419031303557776</v>
+        <v>0.5977184367277821</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.539199842727658</v>
+        <v>-0.02008525269803771</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.9701855777780007</v>
+        <v>-2.670456672971286</v>
       </c>
       <c r="D110" t="n">
-        <v>2.261944630732623</v>
+        <v>-0.1578205727030041</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1806512213699573</v>
+        <v>-0.05391538529520693</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6067564661714181</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2.261944630732623</v>
+        <v>0.4729255558296746</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3320269878203992</v>
+        <v>0.568335251812549</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.724787621091628</v>
+        <v>-1.715551251727707</v>
       </c>
       <c r="D111" t="n">
-        <v>2.447053049583766</v>
+        <v>1.627695206359269</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.2093669085122475</v>
+        <v>1.015816764011211</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.6728193002905415</v>
-      </c>
-      <c r="G111" t="n">
-        <v>2.447053049583766</v>
+        <v>0.7239428412631888</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.980226863603674</v>
+        <v>-0.5642337205745971</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8733838460084996</v>
+        <v>-1.316607983800496</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.777464340316397</v>
+        <v>1.743033240005803</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.503915652549578</v>
+        <v>-0.1088944564556278</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2511448081360659</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2.980226863603674</v>
+        <v>0.7424813338234342</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.963231493334849</v>
+        <v>2.612272244114549</v>
       </c>
       <c r="C113" t="n">
-        <v>0.7798740514161859</v>
+        <v>2.799591102402836</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.8212092614068203</v>
+        <v>-1.142849575810555</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.153274073312916</v>
+        <v>0.1582066978971005</v>
       </c>
       <c r="F113" t="n">
-        <v>0.675246484669455</v>
-      </c>
-      <c r="G113" t="n">
-        <v>2.963231493334849</v>
+        <v>0.9246854244831948</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-2.264450097716577</v>
+        <v>1.757973208919863</v>
       </c>
       <c r="C114" t="n">
-        <v>-2.489352228448325</v>
+        <v>-2.485554707796243</v>
       </c>
       <c r="D114" t="n">
-        <v>2.098624495594011</v>
+        <v>0.00350199000334293</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.10938263130116</v>
+        <v>-0.4898153904926215</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.03895816992636211</v>
-      </c>
-      <c r="G114" t="n">
-        <v>2.098624495594011</v>
+        <v>0.6076758252386268</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.8125296561302462</v>
+        <v>1.83628310467928</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.472079099865078</v>
+        <v>-2.320082720361562</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.26212284092699</v>
+        <v>0.3679872403175844</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.110089546590431</v>
+        <v>0.2647373364198807</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3357388722078157</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0.3357388722078157</v>
+        <v>0.6136105454847579</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.1716471532704986</v>
+        <v>-3.094442042941208</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.55113774161119</v>
+        <v>-0.8338551306692454</v>
       </c>
       <c r="D116" t="n">
-        <v>2.462421000713577</v>
+        <v>1.398500437703607</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4665958781700509</v>
+        <v>0.3190408778381391</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.2209402022920736</v>
-      </c>
-      <c r="G116" t="n">
-        <v>2.462421000713577</v>
+        <v>0.6871039479750344</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.97371023896531</v>
+        <v>-2.17072214222851</v>
       </c>
       <c r="C117" t="n">
-        <v>-2.349064598510147</v>
+        <v>-2.028077509095643</v>
       </c>
       <c r="D117" t="n">
-        <v>-2.351082737354753</v>
+        <v>-0.02594791136429362</v>
       </c>
       <c r="E117" t="n">
-        <v>1.535461665498797</v>
+        <v>-0.4259918930239834</v>
       </c>
       <c r="F117" t="n">
-        <v>3.302504865988261</v>
-      </c>
-      <c r="G117" t="n">
-        <v>3.302504865988261</v>
+        <v>0.458149766195094</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.8957563220736062</v>
+        <v>-0.8146890703616763</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.976206269847286</v>
+        <v>-1.244580918161565</v>
       </c>
       <c r="D118" t="n">
-        <v>2.111274559084756</v>
+        <v>1.14489867226429</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9105602947064138</v>
+        <v>0.4392153987280918</v>
       </c>
       <c r="F118" t="n">
-        <v>0.04755766728354271</v>
-      </c>
-      <c r="G118" t="n">
-        <v>2.111274559084756</v>
+        <v>0.6463420735679341</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.7489969610075358</v>
+        <v>0.3249196808717336</v>
       </c>
       <c r="C119" t="n">
-        <v>-2.963415679810057</v>
+        <v>-5.49944432661073</v>
       </c>
       <c r="D119" t="n">
-        <v>1.977978767617577</v>
+        <v>-2.564264249443796</v>
       </c>
       <c r="E119" t="n">
-        <v>1.030358584314974</v>
+        <v>2.533468059868231</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.5547603924229295</v>
-      </c>
-      <c r="G119" t="n">
-        <v>1.977978767617577</v>
+        <v>0.7646378735076567</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4.537863287148288</v>
+        <v>-0.1869266136253336</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3470965291217281</v>
+        <v>-1.72267651210624</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.030554795386875</v>
+        <v>0.6698290421679168</v>
       </c>
       <c r="E120" t="n">
-        <v>1.355402209977573</v>
+        <v>0.7115818402334427</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.7183532923190646</v>
-      </c>
-      <c r="G120" t="n">
-        <v>4.537863287148288</v>
+        <v>0.5699832652486376</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1095685099940603</v>
+        <v>-1.85751415156914</v>
       </c>
       <c r="C121" t="n">
-        <v>-2.987962334392148</v>
+        <v>-1.46919433137313</v>
       </c>
       <c r="D121" t="n">
-        <v>-2.325141000201505</v>
+        <v>0.4853921496558878</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3020051722514078</v>
+        <v>0.07142550117139783</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.6520054892059023</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.3020051722514078</v>
+        <v>0.5403383870452557</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4.234344600914814</v>
+        <v>3.162393074465823</v>
       </c>
       <c r="C122" t="n">
-        <v>0.03521772307458364</v>
+        <v>-2.42879318035731</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.6104984980629383</v>
+        <v>-1.819048214450467</v>
       </c>
       <c r="E122" t="n">
-        <v>0.9729631694070708</v>
+        <v>-0.8352537646165008</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.5369440477986557</v>
-      </c>
-      <c r="G122" t="n">
-        <v>4.234344600914814</v>
+        <v>0.7141098707611813</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.50832628214832</v>
+        <v>-1.69137917575485</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.227205801614457</v>
+        <v>-3.046869892793073</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.349372266011108</v>
+        <v>-1.709189540419653</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8439177330835586</v>
+        <v>-1.447734266538161</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.5811836255615815</v>
-      </c>
-      <c r="G123" t="n">
-        <v>1.50832628214832</v>
+        <v>0.3462664435142515</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2.386608600933051</v>
+        <v>1.860555662726946</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.24093159544928</v>
+        <v>2.572513797044856</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.058117413721145</v>
+        <v>-1.129086933050164</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.1573995152551072</v>
+        <v>0.09846601584310688</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.3397256353204008</v>
-      </c>
-      <c r="G124" t="n">
-        <v>2.386608600933051</v>
+        <v>0.8993842824057231</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.494055001250989</v>
+        <v>3.043832811435978</v>
       </c>
       <c r="C125" t="n">
-        <v>-1.936790041658746</v>
+        <v>-2.054541112179094</v>
       </c>
       <c r="D125" t="n">
-        <v>-1.977392743005802</v>
+        <v>-1.261376331873786</v>
       </c>
       <c r="E125" t="n">
-        <v>1.038588448218466</v>
+        <v>-0.4200676642560363</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7358190626987998</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1.494055001250989</v>
+        <v>0.7051247739663712</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2.342495426879799</v>
+        <v>-0.06813021593373952</v>
       </c>
       <c r="C126" t="n">
-        <v>-2.498028696597507</v>
+        <v>-2.78504312624066</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.306008079135043</v>
+        <v>-1.436000481841276</v>
       </c>
       <c r="E126" t="n">
-        <v>1.527722179071396</v>
+        <v>-0.9590837729682981</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.5107666564447587</v>
-      </c>
-      <c r="G126" t="n">
-        <v>2.342495426879799</v>
+        <v>0.4692844653483959</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.032975630603418</v>
+        <v>0.8667294561955123</v>
       </c>
       <c r="C127" t="n">
-        <v>-2.908700277339375</v>
+        <v>-2.932118757654166</v>
       </c>
       <c r="D127" t="n">
-        <v>1.65638967226272</v>
+        <v>-0.4395625108529136</v>
       </c>
       <c r="E127" t="n">
-        <v>1.636271245077607</v>
+        <v>-0.7277644491706599</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.176215346785682</v>
-      </c>
-      <c r="G127" t="n">
-        <v>1.65638967226272</v>
+        <v>0.5401328628551662</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2.266442758183566</v>
+        <v>-0.2212105731050684</v>
       </c>
       <c r="C128" t="n">
-        <v>-2.024981386432087</v>
+        <v>-3.106975434091657</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.839037290403609</v>
+        <v>-2.09391833801232</v>
       </c>
       <c r="E128" t="n">
-        <v>1.384432759523746</v>
+        <v>0.3280903199514703</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.5460113970483075</v>
-      </c>
-      <c r="G128" t="n">
-        <v>2.266442758183566</v>
+        <v>0.4576832611049282</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>6.842172179612913</v>
+        <v>0.5734693285889111</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.7695964628965734</v>
+        <v>-3.320623003423421</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.806888049298418</v>
+        <v>-1.870709170254469</v>
       </c>
       <c r="E129" t="n">
-        <v>2.219377802842296</v>
+        <v>-0.812942210374507</v>
       </c>
       <c r="F129" t="n">
-        <v>-1.005038480131347</v>
-      </c>
-      <c r="G129" t="n">
-        <v>6.842172179612913</v>
+        <v>0.5179081261241051</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.909023305041172</v>
+        <v>-0.4602812204788576</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.363011598568051</v>
+        <v>-2.61217302905935</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.8475377465410968</v>
+        <v>-0.1112349728812696</v>
       </c>
       <c r="E130" t="n">
-        <v>0.8012954533772055</v>
+        <v>0.2721779570806881</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.7210715540432888</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1.909023305041172</v>
+        <v>0.4444414212074977</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.828638938318954</v>
+        <v>0.5359752687405257</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.4263038113098841</v>
+        <v>-3.185406715854489</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.195595935613467</v>
+        <v>-2.116674896553371</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.192476054964748</v>
+        <v>-1.013229550173015</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.2218709043944195</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1.828638938318954</v>
+        <v>0.5150666365022126</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.097144506609979</v>
+        <v>4.868821418263976</v>
       </c>
       <c r="C132" t="n">
-        <v>-2.016794480502424</v>
+        <v>-4.016242946678913</v>
       </c>
       <c r="D132" t="n">
-        <v>-2.171853412966033</v>
+        <v>-2.845422237559242</v>
       </c>
       <c r="E132" t="n">
-        <v>1.140372710368378</v>
+        <v>-1.340938535067367</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.6004829770661529</v>
-      </c>
-      <c r="G132" t="n">
-        <v>2.097144506609979</v>
+        <v>0.8434316473042559</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-2.659880920205858</v>
+        <v>0.5282783558540581</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5817263597017146</v>
+        <v>-2.343833099918592</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2261077391060719</v>
+        <v>-1.161257142749651</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6372310545687212</v>
+        <v>-0.9400935666908858</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.3016328255649398</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.6372310545687212</v>
+        <v>0.5144833254877228</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-1.55324796683983</v>
+        <v>0.6573566343683632</v>
       </c>
       <c r="C134" t="n">
-        <v>1.159945263963395</v>
+        <v>-2.092105423259358</v>
       </c>
       <c r="D134" t="n">
-        <v>0.0661018916304101</v>
+        <v>0.256652865980201</v>
       </c>
       <c r="E134" t="n">
-        <v>0.436775633386527</v>
+        <v>-0.8310923326401757</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.5128194317398215</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1.159945263963395</v>
+        <v>0.5242655307301869</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.05102240646716513</v>
+        <v>0.3923990480813608</v>
       </c>
       <c r="C135" t="n">
-        <v>2.644770402642359</v>
+        <v>2.294747739116143</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.3367399296441296</v>
+        <v>0.1769129605768491</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1628477315154365</v>
+        <v>-0.01412501929469576</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.7292843217125511</v>
-      </c>
-      <c r="G135" t="n">
-        <v>2.644770402642359</v>
+        <v>0.8684353573915103</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.4114118853150632</v>
+        <v>0.3967773856940759</v>
       </c>
       <c r="C136" t="n">
-        <v>2.297080782692796</v>
+        <v>-3.190549330577665</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.3209299233824855</v>
+        <v>-2.049764596580563</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1226021542103289</v>
+        <v>-1.142460725990391</v>
       </c>
       <c r="F136" t="n">
-        <v>-1.194091358866186</v>
-      </c>
-      <c r="G136" t="n">
-        <v>2.297080782692796</v>
+        <v>0.5045175164105158</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.574155328554725</v>
+        <v>4.466954486095105</v>
       </c>
       <c r="C137" t="n">
-        <v>3.738640352011697</v>
+        <v>2.772922230099908</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3357418814520001</v>
+        <v>-0.3613046278859822</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4245549055398301</v>
+        <v>0.3484389482483349</v>
       </c>
       <c r="F137" t="n">
-        <v>-1.062452382198005</v>
-      </c>
-      <c r="G137" t="n">
-        <v>3.738640352011697</v>
+        <v>0.9217139565678142</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-2.86691774796456</v>
+        <v>1.759752247077424</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5942638348690173</v>
+        <v>2.191947319774002</v>
       </c>
       <c r="D138" t="n">
-        <v>0.07705447803092877</v>
+        <v>0.3645177515441511</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.004694666039584187</v>
+        <v>-0.5669990897510353</v>
       </c>
       <c r="F138" t="n">
-        <v>0.4228692413244797</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.5942638348690173</v>
+        <v>0.8569812492352644</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-1.624655840193646</v>
+        <v>3.610813181974859</v>
       </c>
       <c r="C139" t="n">
-        <v>1.818686323504345</v>
+        <v>2.599073334185725</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.09510515480824508</v>
+        <v>-1.262441850872404</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.1421802995513126</v>
+        <v>-0.1440506053088907</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.3862921824597976</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1.818686323504345</v>
+        <v>0.9023435681064832</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.09022932653583574</v>
+        <v>1.029607059546068</v>
       </c>
       <c r="C140" t="n">
-        <v>2.828166794916441</v>
+        <v>1.849235847767818</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1195295161581694</v>
+        <v>0.8382491459832028</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5119995260044338</v>
+        <v>-0.393587434572495</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2212047974901072</v>
-      </c>
-      <c r="G140" t="n">
-        <v>2.828166794916441</v>
+        <v>0.8187960522111127</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3856285630281259</v>
+        <v>6.705044799072948</v>
       </c>
       <c r="C141" t="n">
-        <v>2.89246897692229</v>
+        <v>2.83517446060035</v>
       </c>
       <c r="D141" t="n">
-        <v>0.5350162300503305</v>
+        <v>-0.5162309809313866</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4148264374011926</v>
+        <v>0.6999708482849797</v>
       </c>
       <c r="F141" t="n">
-        <v>-1.200596191800883</v>
-      </c>
-      <c r="G141" t="n">
-        <v>2.89246897692229</v>
+        <v>0.9825899486763504</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.992975354535908</v>
+        <v>2.527872834945208</v>
       </c>
       <c r="C142" t="n">
-        <v>1.019001490209825</v>
+        <v>2.369398243763741</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.08630783099461956</v>
+        <v>0.494407454870707</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2690099107124406</v>
+        <v>-0.5548649694881509</v>
       </c>
       <c r="F142" t="n">
-        <v>-1.086205036776972</v>
-      </c>
-      <c r="G142" t="n">
-        <v>1.019001490209825</v>
+        <v>0.8767529786582693</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0.4556813296037188</v>
+        <v>3.193335256101532</v>
       </c>
       <c r="C143" t="n">
-        <v>2.281399646184818</v>
+        <v>2.387332859721196</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.3409016791991754</v>
+        <v>-0.7746324909663875</v>
       </c>
       <c r="E143" t="n">
-        <v>0.6713802523539808</v>
+        <v>0.2163359828988708</v>
       </c>
       <c r="F143" t="n">
-        <v>2.426258453264439</v>
-      </c>
-      <c r="G143" t="n">
-        <v>2.426258453264439</v>
+        <v>0.8787512684729608</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-1.861428435646548</v>
+        <v>2.320827921740788</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6979453299958206</v>
+        <v>2.130831713149962</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.6057022915659784</v>
+        <v>0.4402586561738887</v>
       </c>
       <c r="E144" t="n">
-        <v>0.9159042099526967</v>
+        <v>-0.3803596578165541</v>
       </c>
       <c r="F144" t="n">
-        <v>-1.775440584254941</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.9159042099526967</v>
+        <v>0.8501716975545801</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1.28112292462921</v>
+        <v>2.391003312717928</v>
       </c>
       <c r="C145" t="n">
-        <v>3.513996231819244</v>
+        <v>2.181556563040062</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.434357927027624</v>
+        <v>0.2647071634972191</v>
       </c>
       <c r="E145" t="n">
-        <v>0.4116549744018875</v>
+        <v>-0.3233712843418087</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.2501102329732696</v>
-      </c>
-      <c r="G145" t="n">
-        <v>3.513996231819244</v>
+        <v>0.8558235024846439</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.8032310309116535</v>
+        <v>4.672241003302276</v>
       </c>
       <c r="C146" t="n">
-        <v>2.088387627045643</v>
+        <v>3.305489328958255</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.7218320420275312</v>
+        <v>0.310094370417473</v>
       </c>
       <c r="E146" t="n">
-        <v>0.7084664352816403</v>
+        <v>0.4357358464920209</v>
       </c>
       <c r="F146" t="n">
-        <v>3.471640522215216</v>
-      </c>
-      <c r="G146" t="n">
-        <v>3.471640522215216</v>
+        <v>0.9810530253169335</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-4.141317086697408</v>
+        <v>-1.064640378167739</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.1844323770344575</v>
+        <v>1.836684902166523</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.4803394424950003</v>
+        <v>0.07923179141070701</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.01186528899884616</v>
+        <v>-0.2297033441510425</v>
       </c>
       <c r="F147" t="n">
-        <v>0.05674552872975166</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.05674552872975166</v>
+        <v>0.8173976154216486</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.0009168402738896204</v>
+        <v>2.540274000460837</v>
       </c>
       <c r="C148" t="n">
-        <v>2.572324085095787</v>
+        <v>2.22024475676963</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.2482837194917268</v>
+        <v>0.5871950152945987</v>
       </c>
       <c r="E148" t="n">
-        <v>0.6709174410343501</v>
+        <v>-0.1696983890937031</v>
       </c>
       <c r="F148" t="n">
-        <v>2.460365518868009</v>
-      </c>
-      <c r="G148" t="n">
-        <v>2.572324085095787</v>
+        <v>0.860134173182138</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-4.513345977991692</v>
+        <v>3.992613529635443</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.2278467920222016</v>
+        <v>2.99582075077735</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3631259557317028</v>
+        <v>0.2916188268366853</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.5045693462221438</v>
+        <v>-0.03881487592186738</v>
       </c>
       <c r="F149" t="n">
-        <v>1.491828202025415</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1.491828202025415</v>
+        <v>0.9465494949833665</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-3.242025698135956</v>
+        <v>0.8538953124063497</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.7304111800598454</v>
+        <v>1.977640443969452</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.03693724919662139</v>
+        <v>0.3978389181292276</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9648845432904982</v>
+        <v>-0.4582048006031265</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.060693496632741</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.9648845432904982</v>
+        <v>0.8331029990316078</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-1.151176389202471</v>
+        <v>1.623152341074236</v>
       </c>
       <c r="C151" t="n">
-        <v>0.2497670883415908</v>
+        <v>2.095808501360983</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.4138642296663495</v>
+        <v>0.7415405930544633</v>
       </c>
       <c r="E151" t="n">
-        <v>2.345119257307775</v>
+        <v>-0.3034757007126972</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.6927317260028962</v>
-      </c>
-      <c r="G151" t="n">
-        <v>2.345119257307775</v>
+        <v>0.8462693821907202</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-2.439700839201843</v>
+        <v>2.305767495483289</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1425519674914449</v>
+        <v>2.04546024545887</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.03201976511787162</v>
+        <v>0.1128843439028534</v>
       </c>
       <c r="E152" t="n">
-        <v>0.8628174876049537</v>
+        <v>-0.3108084797525963</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.04651621837521624</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.8628174876049537</v>
+        <v>0.8406595376757695</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-2.578897144950596</v>
+        <v>1.423401747995108</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8414405896299196</v>
+        <v>2.168655179620119</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.1511940825355887</v>
+        <v>0.6609509048372327</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.1924244229482608</v>
+        <v>0.04427746122811687</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.2811972299589065</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.8414405896299196</v>
+        <v>0.8543860196221917</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>-3.43626133609625</v>
+        <v>3.144660249086152</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.2446775521077678</v>
+        <v>2.154238169350703</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6387228815394025</v>
+        <v>0.655674740486154</v>
       </c>
       <c r="E154" t="n">
-        <v>0.551844211236988</v>
+        <v>-0.2538141216882162</v>
       </c>
       <c r="F154" t="n">
-        <v>0.406046713764525</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.6387228815394025</v>
+        <v>0.852779664356597</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-2.760373686353978</v>
+        <v>5.891795819249972</v>
       </c>
       <c r="C155" t="n">
-        <v>0.9528045877563314</v>
+        <v>3.144666864262067</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.5934382489122353</v>
+        <v>0.06936867702634336</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2779495342621806</v>
+        <v>0.4265257556518525</v>
       </c>
       <c r="F155" t="n">
-        <v>1.50995125235221</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1.50995125235221</v>
+        <v>0.9631340526476359</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-1.411231724688604</v>
+        <v>4.837629479491945</v>
       </c>
       <c r="C156" t="n">
-        <v>0.9483297598528198</v>
+        <v>3.031015045974167</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5574692344484831</v>
+        <v>-0.5044166969220915</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3062228976495382</v>
+        <v>0.3919865178132687</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4875842149707524</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.9483297598528198</v>
+        <v>0.950470872602708</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-2.581173744467304</v>
+        <v>2.746603678568132</v>
       </c>
       <c r="C157" t="n">
-        <v>1.25213874847473</v>
+        <v>2.497435852612682</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.5216023525975783</v>
+        <v>-0.2102454353907318</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.07736697576897676</v>
+        <v>-0.3249454655215883</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.02387642351555256</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1.25213874847473</v>
+        <v>0.8910190354429394</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-1.373047849338763</v>
+        <v>-0.2786205447688595</v>
       </c>
       <c r="C158" t="n">
-        <v>1.395703867641043</v>
+        <v>2.094929716279219</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2457503571397776</v>
+        <v>0.3278774840360043</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2759666513892742</v>
+        <v>-0.1175389296257816</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.4042775050966564</v>
-      </c>
-      <c r="G158" t="n">
-        <v>1.395703867641043</v>
+        <v>0.8461714672265884</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>-1.106447438167609</v>
+        <v>6.262908248800912</v>
       </c>
       <c r="C159" t="n">
-        <v>1.159301123999511</v>
+        <v>2.687584274590168</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1506203614877049</v>
+        <v>-1.162762878044976</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5551811156139007</v>
+        <v>0.7509864004991916</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.1776683158246657</v>
-      </c>
-      <c r="G159" t="n">
-        <v>1.159301123999511</v>
+        <v>0.949082603135816</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-3.195690729618029</v>
+        <v>-0.3959797932077877</v>
       </c>
       <c r="C160" t="n">
-        <v>0.4825169087612939</v>
+        <v>2.028969473543796</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3744859909660251</v>
+        <v>-0.3278530187329633</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0555784626785556</v>
+        <v>-0.7815029893366046</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3289721812868349</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.4825169087612939</v>
+        <v>0.8388221221641986</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-3.510178099878564</v>
+        <v>0.9288274222814916</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.06305290565901274</v>
+        <v>2.150641775719913</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1992687207339622</v>
+        <v>0.05972269380776481</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3010141847338035</v>
+        <v>-0.586219512561146</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.02448702938226801</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.3010141847338035</v>
+        <v>0.8523789511894414</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-2.802382558568401</v>
+        <v>-0.680079215652909</v>
       </c>
       <c r="C162" t="n">
-        <v>0.5202305328356266</v>
+        <v>1.833916788524341</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3364094618074827</v>
+        <v>0.7738803137629753</v>
       </c>
       <c r="E162" t="n">
-        <v>0.4188136406937694</v>
+        <v>-0.1186559436716445</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.2525268163382256</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0.5202305328356266</v>
+        <v>0.8170891898991728</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-1.987064329278024</v>
+        <v>1.557884831341269</v>
       </c>
       <c r="C163" t="n">
-        <v>1.631616508994628</v>
+        <v>1.971492561076107</v>
       </c>
       <c r="D163" t="n">
-        <v>-1.068978085685103</v>
+        <v>0.6377512256327126</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.2755671803498808</v>
+        <v>-0.2179147506147645</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.7522664682617017</v>
-      </c>
-      <c r="G163" t="n">
-        <v>1.631616508994628</v>
+        <v>0.832417996810382</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-3.758612310991614</v>
+        <v>2.706509912349437</v>
       </c>
       <c r="C164" t="n">
-        <v>0.09935429824762962</v>
+        <v>2.717135798737733</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.4743599055680986</v>
+        <v>-0.5863931944106784</v>
       </c>
       <c r="E164" t="n">
-        <v>0.03575774137811578</v>
+        <v>-0.1474110978030476</v>
       </c>
       <c r="F164" t="n">
-        <v>0.2080320203356396</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.2080320203356396</v>
+        <v>0.9154981860236623</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-3.074779840474537</v>
+        <v>1.523412351883168</v>
       </c>
       <c r="C165" t="n">
-        <v>0.6453997802115087</v>
+        <v>2.107512072663106</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.8434162717686631</v>
+        <v>0.5567500465580024</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3639135508736945</v>
+        <v>-0.4542489148332218</v>
       </c>
       <c r="F165" t="n">
-        <v>1.094157600689859</v>
-      </c>
-      <c r="G165" t="n">
-        <v>1.094157600689859</v>
+        <v>0.8475734038315531</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-4.68886119658462</v>
+        <v>3.114433934198862</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.8075047608284311</v>
+        <v>2.804736669184483</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.6543597642288085</v>
+        <v>-0.3389013464071102</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2707578771571686</v>
+        <v>0.1086289467868011</v>
       </c>
       <c r="F166" t="n">
-        <v>1.712434519322673</v>
-      </c>
-      <c r="G166" t="n">
-        <v>1.712434519322673</v>
+        <v>0.9252587478102722</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-4.185837621709718</v>
+        <v>1.346007077664504</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.8235847569029561</v>
+        <v>2.106094025657893</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.6836513076621652</v>
+        <v>0.4207442616681898</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3289455898705217</v>
+        <v>-0.3471672076927065</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.1359963094813013</v>
-      </c>
-      <c r="G167" t="n">
-        <v>0.3289455898705217</v>
+        <v>0.8474154038557525</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-3.190250970880944</v>
+        <v>-1.703290794607403</v>
       </c>
       <c r="C168" t="n">
-        <v>0.7317719760849947</v>
+        <v>1.747698762300437</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.6438057482755478</v>
+        <v>-0.3465692072587775</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.1315481080118148</v>
+        <v>-0.4442643105651246</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5081568813577235</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0.7317719760849947</v>
+        <v>0.8074827057650966</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-4.810413324261017</v>
+        <v>0.05877604299848433</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.4820904001367389</v>
+        <v>1.911443771384944</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.6211647391765079</v>
+        <v>0.381880180027533</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.1735720320163709</v>
+        <v>-0.313039415079129</v>
       </c>
       <c r="F169" t="n">
-        <v>0.850042454471434</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.850042454471434</v>
+        <v>0.8257273107589458</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-0.469918918221544</v>
+        <v>0.0706919988695723</v>
       </c>
       <c r="C170" t="n">
-        <v>2.404075708339076</v>
+        <v>2.143584590872986</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.470213259509207</v>
+        <v>0.2861052500682971</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4385462480233608</v>
+        <v>0.1418663903759065</v>
       </c>
       <c r="F170" t="n">
-        <v>-1.17165851049401</v>
-      </c>
-      <c r="G170" t="n">
-        <v>2.404075708339076</v>
+        <v>0.8515926337888647</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.5639311574533636</v>
+        <v>0.9703751746601426</v>
       </c>
       <c r="C171" t="n">
-        <v>3.144907615587742</v>
+        <v>2.051817059408971</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.4650455086744995</v>
+        <v>0.4283235040734252</v>
       </c>
       <c r="E171" t="n">
-        <v>0.697344672657509</v>
+        <v>-0.2770308155087401</v>
       </c>
       <c r="F171" t="n">
-        <v>3.07319366785422</v>
-      </c>
-      <c r="G171" t="n">
-        <v>3.144907615587742</v>
+        <v>0.841367819168973</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-3.520703057690538</v>
+        <v>2.642700658044948</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3135571086324083</v>
+        <v>2.174233066290751</v>
       </c>
       <c r="D172" t="n">
-        <v>-1.230057082428342</v>
+        <v>0.09534968905832764</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.5572789064304755</v>
+        <v>-0.1726054382607719</v>
       </c>
       <c r="F172" t="n">
-        <v>0.2570025709125904</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.3135571086324083</v>
+        <v>0.8550075123905827</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-3.00677568202972</v>
+        <v>0.3833118315668738</v>
       </c>
       <c r="C173" t="n">
-        <v>0.6879196415360052</v>
+        <v>2.011028459455372</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.9984289821318733</v>
+        <v>0.4165288275310011</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.07511486816851831</v>
+        <v>-0.1572075633017678</v>
       </c>
       <c r="F173" t="n">
-        <v>0.4552761016617888</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.6879196415360052</v>
+        <v>0.8368231194644373</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-2.51419258925013</v>
+        <v>1.745429763975064</v>
       </c>
       <c r="C174" t="n">
-        <v>1.721196139976914</v>
+        <v>2.057149653987751</v>
       </c>
       <c r="D174" t="n">
-        <v>-1.245441852743973</v>
+        <v>0.5669773849340657</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.2187613768492899</v>
+        <v>-0.3280672511396407</v>
       </c>
       <c r="F174" t="n">
-        <v>3.342005881826272</v>
-      </c>
-      <c r="G174" t="n">
-        <v>3.342005881826272</v>
+        <v>0.8419619812886378</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-3.54708639464208</v>
+        <v>2.069453437259415</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.3679391199235528</v>
+        <v>2.542834354046599</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.5645995936718938</v>
+        <v>-0.3116213714751275</v>
       </c>
       <c r="E175" t="n">
-        <v>0.7910971372700197</v>
+        <v>0.1783884550063741</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.02931360735713913</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.7910971372700197</v>
+        <v>0.896077374201509</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-4.108049826135982</v>
+        <v>-4.134150650036776</v>
       </c>
       <c r="C176" t="n">
-        <v>0.009180138479683136</v>
+        <v>1.466816095529297</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.5500708506679908</v>
+        <v>-0.01977075951793842</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.1144720813057002</v>
+        <v>-0.3354079690299642</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4203976788765076</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0.4203976788765076</v>
+        <v>0.7761865256035769</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-5.902345788846264</v>
+        <v>0.6002668769538846</v>
       </c>
       <c r="C177" t="n">
-        <v>-1.52049748079914</v>
+        <v>2.177672945611776</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.3232936172527501</v>
+        <v>0.03238714473311769</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0649993372270171</v>
+        <v>0.1265172645502498</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9029263946437102</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0.9029263946437102</v>
+        <v>0.8553907866032717</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>-3.960616696665573</v>
+        <v>1.512569380566717</v>
       </c>
       <c r="C178" t="n">
-        <v>0.03006659771482753</v>
+        <v>2.153311821891128</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.4711193811620099</v>
+        <v>0.1551951291960705</v>
       </c>
       <c r="E178" t="n">
-        <v>0.01136404650554766</v>
+        <v>-0.1282706776032193</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.2681371305397149</v>
-      </c>
-      <c r="G178" t="n">
-        <v>0.03006659771482753</v>
+        <v>0.8526764499528023</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-2.936918600390152</v>
+        <v>3.195414376350735</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1665916799276767</v>
+        <v>2.596839432777065</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2316925153583238</v>
+        <v>-0.3314033441575999</v>
       </c>
       <c r="E179" t="n">
-        <v>0.04650945874169456</v>
+        <v>0.4816914002537471</v>
       </c>
       <c r="F179" t="n">
-        <v>0.1891153940625758</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0.2316925153583238</v>
+        <v>0.902094664955028</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-2.983722098231791</v>
+        <v>1.242734203282908</v>
       </c>
       <c r="C180" t="n">
-        <v>0.3699778028954989</v>
+        <v>2.072608493729737</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.1606453834415504</v>
+        <v>0.1989719010091702</v>
       </c>
       <c r="E180" t="n">
-        <v>0.2947857833110621</v>
+        <v>-0.2806696153487288</v>
       </c>
       <c r="F180" t="n">
-        <v>1.231274817110714</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1.231274817110714</v>
+        <v>0.8436844180598873</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-2.524291739508804</v>
+        <v>0.01497458891878667</v>
       </c>
       <c r="C181" t="n">
-        <v>0.9536585525384379</v>
+        <v>1.89139406936564</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.03807721227876779</v>
+        <v>-0.1711276948841827</v>
       </c>
       <c r="E181" t="n">
-        <v>0.08817596612237134</v>
+        <v>-0.2731598790362465</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5216125667239547</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0.9536585525384379</v>
+        <v>0.8234933562974832</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-2.013017868520377</v>
+        <v>-0.6618426110308104</v>
       </c>
       <c r="C182" t="n">
-        <v>1.013142727929477</v>
+        <v>2.214807101136349</v>
       </c>
       <c r="D182" t="n">
-        <v>0.07368187339158484</v>
+        <v>-0.7672038763675828</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5288516589971349</v>
+        <v>-0.001471695125544279</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.7056868162947558</v>
-      </c>
-      <c r="G182" t="n">
-        <v>1.013142727929477</v>
+        <v>0.8595283050724688</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-2.324733581296837</v>
+        <v>6.934774128810085</v>
       </c>
       <c r="C183" t="n">
-        <v>0.9722756047535895</v>
+        <v>2.716911014011337</v>
       </c>
       <c r="D183" t="n">
-        <v>0.0725763802093511</v>
+        <v>-0.8670332158306864</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3320104059494367</v>
+        <v>0.4823145827049648</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.1000156031009907</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.9722756047535895</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-2.187752253661311</v>
+        <v>0.5579253576383147</v>
       </c>
       <c r="C184" t="n">
-        <v>0.7339863349705229</v>
+        <v>1.988178012958278</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1042823855986838</v>
+        <v>0.4197768769253154</v>
       </c>
       <c r="E184" t="n">
-        <v>0.456616141058968</v>
+        <v>-0.483831520194286</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.4476214874188126</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0.7339863349705229</v>
+        <v>0.8342771037256772</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-1.330882486634583</v>
+        <v>1.402018679196382</v>
       </c>
       <c r="C185" t="n">
-        <v>1.257954690354242</v>
+        <v>2.527479860397676</v>
       </c>
       <c r="D185" t="n">
-        <v>0.07673594645472889</v>
+        <v>-0.6150902584400506</v>
       </c>
       <c r="E185" t="n">
-        <v>0.6046416302846215</v>
+        <v>0.01399425120717305</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.6588779620603112</v>
-      </c>
-      <c r="G185" t="n">
-        <v>1.257954690354242</v>
+        <v>0.8943665637586663</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-0.8218360378718387</v>
+        <v>3.805661986881031</v>
       </c>
       <c r="C186" t="n">
-        <v>1.875976569729429</v>
+        <v>2.851794279303387</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2959118269430437</v>
+        <v>-0.7755085516336524</v>
       </c>
       <c r="E186" t="n">
-        <v>0.5342310612743216</v>
+        <v>0.1173893791890206</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.6395430371529254</v>
-      </c>
-      <c r="G186" t="n">
-        <v>1.875976569729429</v>
+        <v>0.9305019458373391</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-2.00387448101298</v>
+        <v>4.590134738798424</v>
       </c>
       <c r="C187" t="n">
-        <v>1.145913294481564</v>
+        <v>2.435086535521586</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2123490308111696</v>
+        <v>-0.04619462602617604</v>
       </c>
       <c r="E187" t="n">
-        <v>0.4117629353417954</v>
+        <v>-0.05216740394860648</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.3350270227443484</v>
-      </c>
-      <c r="G187" t="n">
-        <v>1.145913294481564</v>
+        <v>0.8840720227167302</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-2.455206264957245</v>
+        <v>3.347906994878258</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1755632645769141</v>
+        <v>2.453695078608576</v>
       </c>
       <c r="D188" t="n">
-        <v>0.2197974878143911</v>
+        <v>-0.4578540032993383</v>
       </c>
       <c r="E188" t="n">
-        <v>0.8897147236621819</v>
+        <v>-0.2058575322921883</v>
       </c>
       <c r="F188" t="n">
-        <v>1.238337014231035</v>
-      </c>
-      <c r="G188" t="n">
-        <v>1.238337014231035</v>
+        <v>0.8861454020522673</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-2.340303423626747</v>
+        <v>2.914028236455228</v>
       </c>
       <c r="C189" t="n">
-        <v>1.153587063923145</v>
+        <v>2.381973348794318</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3118922555744778</v>
+        <v>0.05191672056925545</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4364205492945742</v>
+        <v>-0.2884716161122591</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.5830855910769702</v>
-      </c>
-      <c r="G189" t="n">
-        <v>1.153587063923145</v>
+        <v>0.878154107311422</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-0.5171609633397494</v>
+        <v>2.671951524277782</v>
       </c>
       <c r="C190" t="n">
-        <v>1.6943120196512</v>
+        <v>3.475538093656015</v>
       </c>
       <c r="D190" t="n">
-        <v>1.000870237260326</v>
+        <v>-0.3131682748472714</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6522929198930111</v>
+        <v>0.6594019217176065</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.5340608389236194</v>
-      </c>
-      <c r="G190" t="n">
-        <v>1.6943120196512</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-2.940155623136333</v>
+        <v>5.137263054440779</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.1080974265040334</v>
+        <v>2.515574825724495</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.2214655288718388</v>
+        <v>-0.1446279012196382</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3859934558355891</v>
+        <v>0.2068430705247172</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.6050807259304319</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.3859934558355891</v>
+        <v>0.8930400949016023</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-4.105839313524629</v>
+        <v>1.196430978987119</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.8686905438922697</v>
+        <v>1.8757809347033</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.1911591883863978</v>
+        <v>0.2893868814174262</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2947578242478518</v>
+        <v>-0.4981153595792332</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2623200431468876</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.2947578242478518</v>
+        <v>0.8217537278579796</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-4.756711921702698</v>
+        <v>4.641213954405176</v>
       </c>
       <c r="C193" t="n">
-        <v>-1.17736905892881</v>
+        <v>2.637299281177488</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.2255743639278613</v>
+        <v>-1.231603000414515</v>
       </c>
       <c r="E193" t="n">
-        <v>0.01017673150811147</v>
+        <v>0.2156400849661303</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.2133494205605597</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0.01017673150811147</v>
+        <v>0.9066027348882969</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-4.983158489062824</v>
+        <v>-1.321172998435992</v>
       </c>
       <c r="C194" t="n">
-        <v>-1.489073936010241</v>
+        <v>1.753426603682613</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1429728031931556</v>
+        <v>0.4753620707486512</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3327282763969321</v>
+        <v>-0.2135348579071244</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.1782187716001077</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0.3327282763969321</v>
+        <v>0.808120906612069</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-5.053988926513258</v>
+        <v>-2.497349659304359</v>
       </c>
       <c r="C195" t="n">
-        <v>-1.463747012355636</v>
+        <v>1.20080974616672</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1699012675676762</v>
+        <v>-0.407215571389522</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1906505373581875</v>
+        <v>0.132895997735734</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.5846043798639832</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0.1906505373581875</v>
+        <v>0.7465478770908068</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-2.486303803133826</v>
+        <v>-1.37249687616999</v>
       </c>
       <c r="C196" t="n">
-        <v>0.9974300436367265</v>
+        <v>1.009735740727663</v>
       </c>
       <c r="D196" t="n">
-        <v>0.08484399723816416</v>
+        <v>-0.2499377901379202</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.1826213398967675</v>
+        <v>-0.1933224304484075</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.7872752502013224</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0.9974300436367265</v>
+        <v>0.7252582526111437</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-1.604782727595732</v>
+        <v>0.4010055884956483</v>
       </c>
       <c r="C197" t="n">
-        <v>1.891855834533084</v>
+        <v>0.9720603568411339</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.3887998443300119</v>
+        <v>-0.254898725569834</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.4644985259845586</v>
+        <v>-0.3814019766992158</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.7265285935515164</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1.891855834533084</v>
+        <v>0.7210604300280651</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-2.809650654383938</v>
+        <v>-0.02542198983260159</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1363566327375006</v>
+        <v>1.082634134144745</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.1830625996734525</v>
+        <v>-0.2148921298598123</v>
       </c>
       <c r="E198" t="n">
-        <v>0.4546077021090476</v>
+        <v>-0.8511704914220783</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.3131136432768201</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.4546077021090476</v>
+        <v>0.733380652188492</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-2.690555846556655</v>
+        <v>2.138344799522687</v>
       </c>
       <c r="C199" t="n">
-        <v>0.7548653019835587</v>
+        <v>1.045059327646767</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.3023446639026404</v>
+        <v>-0.4465749628114145</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1421800071269152</v>
+        <v>-0.4587051535869041</v>
       </c>
       <c r="F199" t="n">
-        <v>0.769345116326919</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0.769345116326919</v>
+        <v>0.7291940360216314</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-2.63200340774512</v>
+        <v>-2.793570692276749</v>
       </c>
       <c r="C200" t="n">
-        <v>0.9154427833611247</v>
+        <v>1.058952409465378</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.3384751131370404</v>
+        <v>-0.02984849517197548</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.1165489718296747</v>
+        <v>0.6257902674023643</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3475570768303943</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0.9154427833611247</v>
+        <v>0.7307420147438223</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-2.427139790704279</v>
+        <v>-1.242252395786728</v>
       </c>
       <c r="C201" t="n">
-        <v>1.133731828355369</v>
+        <v>1.424810722039239</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.1736878050238442</v>
+        <v>0.0341132362140615</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.1317246647795638</v>
+        <v>-0.173405503681356</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.01083940968724928</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1.133731828355369</v>
+        <v>0.7715062519803992</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>-0.492158973968328</v>
+        <v>0.4256896079965353</v>
       </c>
       <c r="C202" t="n">
-        <v>2.533528760030684</v>
+        <v>1.026120825852422</v>
       </c>
       <c r="D202" t="n">
-        <v>0.06532341884622925</v>
+        <v>-0.406920649836397</v>
       </c>
       <c r="E202" t="n">
-        <v>0.1975350566441591</v>
+        <v>0.7006576574337134</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.7423288107261099</v>
-      </c>
-      <c r="G202" t="n">
-        <v>2.533528760030684</v>
+        <v>0.7270838924127058</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-1.094691571851184</v>
+        <v>0.9256385037998293</v>
       </c>
       <c r="C203" t="n">
-        <v>2.256734289357667</v>
+        <v>1.343125782091253</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.01490333644465504</v>
+        <v>0.1054793782042085</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1681639460635104</v>
+        <v>-0.5129420790854685</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.1126670340673456</v>
-      </c>
-      <c r="G203" t="n">
-        <v>2.256734289357667</v>
+        <v>0.762404848086445</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-1.884481385449269</v>
+        <v>-1.795429563278699</v>
       </c>
       <c r="C204" t="n">
-        <v>1.107286926342101</v>
+        <v>1.018722966952137</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.006178164676951891</v>
+        <v>-0.2678594156722152</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2318200203316245</v>
+        <v>-0.6912345598695996</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.1304338789794753</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1.107286926342101</v>
+        <v>0.7262596168259837</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-1.905685478647686</v>
+        <v>2.288569679761744</v>
       </c>
       <c r="C205" t="n">
-        <v>1.025487315734785</v>
+        <v>2.068873543865478</v>
       </c>
       <c r="D205" t="n">
-        <v>0.172545156723566</v>
+        <v>0.7360886624228994</v>
       </c>
       <c r="E205" t="n">
-        <v>0.009979361821890246</v>
+        <v>-0.4402347598603693</v>
       </c>
       <c r="F205" t="n">
-        <v>0.2840115438054184</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1.025487315734785</v>
+        <v>0.8432682668420505</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-5.026561017200922</v>
+        <v>-1.373797255002219</v>
       </c>
       <c r="C206" t="n">
-        <v>-2.147196108988696</v>
+        <v>2.35376038926401</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.0622102276949129</v>
+        <v>-0.6165440101354112</v>
       </c>
       <c r="E206" t="n">
-        <v>0.6183568982801889</v>
+        <v>0.2837184927123618</v>
       </c>
       <c r="F206" t="n">
-        <v>-1.108025431067092</v>
-      </c>
-      <c r="G206" t="n">
-        <v>0.6183568982801889</v>
+        <v>0.87501059591394</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-1.462538687813318</v>
+        <v>0.8042107434048156</v>
       </c>
       <c r="C207" t="n">
-        <v>1.60572455480436</v>
+        <v>1.950632431270586</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.2824524602333997</v>
+        <v>0.4424123216155718</v>
       </c>
       <c r="E207" t="n">
-        <v>0.1091544520300793</v>
+        <v>-0.4727164506997944</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.5814012152830668</v>
-      </c>
-      <c r="G207" t="n">
-        <v>1.60572455480436</v>
+        <v>0.8300937438114662</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-2.308302018755982</v>
+        <v>-0.5238094406156939</v>
       </c>
       <c r="C208" t="n">
-        <v>1.003131569158714</v>
+        <v>0.2235348655568003</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.0354731579512202</v>
+        <v>-0.8425639518176057</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3149888514582518</v>
+        <v>2.827067480503376</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.7686110148688693</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1.003131569158714</v>
+        <v>0.8075787645323061</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-2.685456175718473</v>
+        <v>-1.728658389714809</v>
       </c>
       <c r="C209" t="n">
-        <v>0.3636594875885844</v>
+        <v>0.9490975321057979</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.3716301381617754</v>
+        <v>-1.173285335547513</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3952472834481091</v>
+        <v>-1.564489915844035</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.2171915829150729</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0.3952472834481091</v>
+        <v>0.7185018930126073</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-2.924800481997058</v>
+        <v>1.619415340982925</v>
       </c>
       <c r="C210" t="n">
-        <v>0.298824379653224</v>
+        <v>0.7927268307384119</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.2047355414983923</v>
+        <v>-0.5772493284351672</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3002658069252208</v>
+        <v>0.1306570451974187</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.962525031586438</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0.3002658069252208</v>
+        <v>0.7010789395130795</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-3.98006376611318</v>
+        <v>-1.100233044972608</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.9547041114529285</v>
+        <v>-0.194572545092109</v>
       </c>
       <c r="D211" t="n">
-        <v>0.07028394015126727</v>
+        <v>-1.135642022231007</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3316121209436056</v>
+        <v>3.745434098763418</v>
       </c>
       <c r="F211" t="n">
-        <v>-1.007269503210028</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0.3316121209436056</v>
+        <v>0.9418960625367413</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-3.332509643481063</v>
+        <v>-0.8651211302765552</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.6085943996875534</v>
+        <v>2.010063459478491</v>
       </c>
       <c r="D212" t="n">
-        <v>0.05227739231763506</v>
+        <v>0.313132595743127</v>
       </c>
       <c r="E212" t="n">
-        <v>0.5522479520124634</v>
+        <v>-0.07390446894019619</v>
       </c>
       <c r="F212" t="n">
-        <v>-1.347985979776195</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0.5522479520124634</v>
+        <v>0.8367155983650418</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-2.905955682620839</v>
+        <v>1.561834928169894</v>
       </c>
       <c r="C213" t="n">
-        <v>0.05195595063372497</v>
+        <v>2.310468884010151</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.0561934943982489</v>
+        <v>-1.286154524385542</v>
       </c>
       <c r="E213" t="n">
-        <v>0.599459299657599</v>
+        <v>0.02735820283237086</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.092419831206434</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.599459299657599</v>
+        <v>0.8701870204207891</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-1.087059558354548</v>
+        <v>-0.5965785653544365</v>
       </c>
       <c r="C214" t="n">
-        <v>1.642200669253487</v>
+        <v>1.970516883898101</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.01684311406886916</v>
+        <v>-0.1298118985115479</v>
       </c>
       <c r="E214" t="n">
-        <v>0.5938706305115669</v>
+        <v>-0.426760472139066</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.3651524675200444</v>
-      </c>
-      <c r="G214" t="n">
-        <v>1.642200669253487</v>
+        <v>0.8323092860483637</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-3.167019429454647</v>
+        <v>-4.272173279655311</v>
       </c>
       <c r="C215" t="n">
-        <v>0.1151098320646766</v>
+        <v>0.9368453254536168</v>
       </c>
       <c r="D215" t="n">
-        <v>0.05448763164076208</v>
+        <v>-0.4223685574719133</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6135511696864331</v>
+        <v>-0.2228277128488418</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.813456109039279</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0.6135511696864331</v>
+        <v>0.7171367419651229</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-3.520805659205713</v>
+        <v>-1.001203671482393</v>
       </c>
       <c r="C216" t="n">
-        <v>0.2645200316024076</v>
+        <v>1.757588718730816</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.2080105014395562</v>
+        <v>0.3130261522029673</v>
       </c>
       <c r="E216" t="n">
-        <v>0.3017315555677913</v>
+        <v>-0.3375510055770795</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.3493082724922306</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.3017315555677913</v>
+        <v>0.8085846529297001</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-1.377585306309448</v>
+        <v>0.5155219187005281</v>
       </c>
       <c r="C217" t="n">
-        <v>1.830723561361999</v>
+        <v>2.228255267975646</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.02729145861227524</v>
+        <v>-0.2903149098720041</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3108684152473591</v>
+        <v>-0.1241178024608694</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.0362508375237905</v>
-      </c>
-      <c r="G217" t="n">
-        <v>1.830723561361999</v>
+        <v>0.8610267109979143</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-3.634574371021774</v>
+        <v>0.4761041419912843</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.6137739184869415</v>
+        <v>1.907112585752316</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.5698464389872923</v>
+        <v>0.4889230778379531</v>
       </c>
       <c r="E218" t="n">
-        <v>0.1831052725646437</v>
+        <v>-0.5499616584515694</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.8479979797137639</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0.1831052725646437</v>
+        <v>0.8252447264562904</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-2.893179026663169</v>
+        <v>1.399988345318702</v>
       </c>
       <c r="C219" t="n">
-        <v>0.1958124319641756</v>
+        <v>2.382275583713096</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.3719641693732126</v>
+        <v>0.5215630857705381</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1144120845010132</v>
+        <v>0.1224624605966539</v>
       </c>
       <c r="F219" t="n">
-        <v>0.3593948198147103</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0.3593948198147103</v>
+        <v>0.8781877825772471</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-0.5723721788977614</v>
+        <v>2.762526208594306</v>
       </c>
       <c r="C220" t="n">
-        <v>2.310418664325629</v>
+        <v>2.129952812863038</v>
       </c>
       <c r="D220" t="n">
-        <v>1.323934235404981</v>
+        <v>0.4545377396987005</v>
       </c>
       <c r="E220" t="n">
-        <v>1.458864710425384</v>
+        <v>-0.5361526955741374</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.4182646086026177</v>
-      </c>
-      <c r="G220" t="n">
-        <v>2.310418664325629</v>
+        <v>0.8500737697541936</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1.347995606169807</v>
+        <v>-0.2448917066495336</v>
       </c>
       <c r="C221" t="n">
-        <v>3.388877017626667</v>
+        <v>1.819866193307692</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2429979180469656</v>
+        <v>0.3272835725311088</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7711667521548982</v>
+        <v>-0.3670851889945473</v>
       </c>
       <c r="F221" t="n">
-        <v>-1.043109723918329</v>
-      </c>
-      <c r="G221" t="n">
-        <v>3.388877017626667</v>
+        <v>0.8155236609032696</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1.989305500953223</v>
+        <v>-0.03818378238094754</v>
       </c>
       <c r="C222" t="n">
-        <v>0.115870678731585</v>
+        <v>0.1804812703942668</v>
       </c>
       <c r="D222" t="n">
-        <v>1.048412512795384</v>
+        <v>-0.7307428509570452</v>
       </c>
       <c r="E222" t="n">
-        <v>4.468968995683205</v>
+        <v>2.891723284214408</v>
       </c>
       <c r="F222" t="n">
-        <v>-1.123559034952408</v>
-      </c>
-      <c r="G222" t="n">
-        <v>4.468968995683205</v>
+        <v>0.8170351109217519</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>-0.4882460954810556</v>
+        <v>0.785400527962362</v>
       </c>
       <c r="C223" t="n">
-        <v>2.374797188301778</v>
+        <v>1.943027157901007</v>
       </c>
       <c r="D223" t="n">
-        <v>0.8779409908967105</v>
+        <v>0.4081432920805671</v>
       </c>
       <c r="E223" t="n">
-        <v>1.147475270001562</v>
+        <v>-0.4194181990033153</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.655906153036052</v>
-      </c>
-      <c r="G223" t="n">
-        <v>2.374797188301778</v>
+        <v>0.8292463579322019</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2.057868053974148</v>
+        <v>6.214654429254098</v>
       </c>
       <c r="C224" t="n">
-        <v>3.221471462810959</v>
+        <v>3.102526714819122</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.1259454038483644</v>
+        <v>0.09260330494193242</v>
       </c>
       <c r="E224" t="n">
-        <v>1.090730534510535</v>
+        <v>1.004280788845287</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.9563978436214826</v>
-      </c>
-      <c r="G224" t="n">
-        <v>3.221471462810959</v>
+        <v>0.9584387621757808</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-2.700726194009252</v>
+        <v>0.5836018663114404</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4666303960635669</v>
+        <v>2.07170779449316</v>
       </c>
       <c r="D225" t="n">
-        <v>0.08928545947322115</v>
+        <v>-0.3846225652775951</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5325111195530996</v>
+        <v>-0.2778006925765642</v>
       </c>
       <c r="F225" t="n">
-        <v>0.2270668756329048</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0.5325111195530996</v>
+        <v>0.8435840614024143</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1.382740899199727</v>
+        <v>-4.62970263688642</v>
       </c>
       <c r="C226" t="n">
-        <v>2.053863240304131</v>
+        <v>0.9130228461524095</v>
       </c>
       <c r="D226" t="n">
-        <v>0.7591641837488152</v>
+        <v>0.5677236114911943</v>
       </c>
       <c r="E226" t="n">
-        <v>4.113098870499632</v>
+        <v>1.269098981903384</v>
       </c>
       <c r="F226" t="n">
-        <v>-1.404118833204703</v>
-      </c>
-      <c r="G226" t="n">
-        <v>4.113098870499632</v>
+        <v>0.7144824215235126</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.751675426695204</v>
+        <v>-3.511323147844879</v>
       </c>
       <c r="C227" t="n">
-        <v>1.998611902847312</v>
+        <v>0.3327499592054908</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.2335393061603699</v>
+        <v>-0.7646666128075877</v>
       </c>
       <c r="E227" t="n">
-        <v>0.8253298855365894</v>
+        <v>0.07284406674901177</v>
       </c>
       <c r="F227" t="n">
-        <v>-3.152829423596941</v>
-      </c>
-      <c r="G227" t="n">
-        <v>1.998611902847312</v>
+        <v>0.649827934219272</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.9902672592687232</v>
+        <v>-1.363013261462109</v>
       </c>
       <c r="C228" t="n">
-        <v>3.308387244945979</v>
+        <v>0.1729607762768831</v>
       </c>
       <c r="D228" t="n">
-        <v>0.2974085071261394</v>
+        <v>-2.096142058195585</v>
       </c>
       <c r="E228" t="n">
-        <v>0.5306014996253184</v>
+        <v>-0.1316150341039241</v>
       </c>
       <c r="F228" t="n">
-        <v>-1.289206038928812</v>
-      </c>
-      <c r="G228" t="n">
-        <v>3.308387244945979</v>
+        <v>0.6320240906632355</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-1.254597735038583</v>
+        <v>-2.599345918602109</v>
       </c>
       <c r="C229" t="n">
-        <v>1.079572046917901</v>
+        <v>0.4625101275213075</v>
       </c>
       <c r="D229" t="n">
-        <v>0.129311712543852</v>
+        <v>-0.7131744976547961</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8709479510792628</v>
+        <v>0.2344065205281276</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.5365936222611427</v>
-      </c>
-      <c r="G229" t="n">
-        <v>1.079572046917901</v>
+        <v>0.6642859200112887</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>-2.15395775152092</v>
+        <v>-2.431637495021056</v>
       </c>
       <c r="C230" t="n">
-        <v>0.986017827978479</v>
+        <v>1.149698848589898</v>
       </c>
       <c r="D230" t="n">
-        <v>0.2510763820294841</v>
+        <v>0.04304386877035915</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3341016007175349</v>
+        <v>-0.1021827641960479</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.8310544205871934</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0.986017827978479</v>
+        <v>0.7408530584066604</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>-1.908629355805097</v>
+        <v>-3.498869981471585</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.6214269819713759</v>
+        <v>0.7613921370584313</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.3057913285063547</v>
+        <v>-0.07164656983382318</v>
       </c>
       <c r="E231" t="n">
-        <v>1.625190742319843</v>
+        <v>0.6796536207027805</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.6244238617727518</v>
-      </c>
-      <c r="G231" t="n">
-        <v>1.625190742319843</v>
+        <v>0.6975876019022981</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2.373676677657147</v>
+        <v>-2.95191542329541</v>
       </c>
       <c r="C232" t="n">
-        <v>2.951036662966345</v>
+        <v>0.5745626118381321</v>
       </c>
       <c r="D232" t="n">
-        <v>0.8142295897230301</v>
+        <v>-0.7861221101326953</v>
       </c>
       <c r="E232" t="n">
-        <v>2.328822834442656</v>
+        <v>1.330964691886719</v>
       </c>
       <c r="F232" t="n">
-        <v>-1.088558453919593</v>
-      </c>
-      <c r="G232" t="n">
-        <v>2.951036662966345</v>
+        <v>0.6767709009360195</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>-2.348239086235433</v>
+        <v>-1.659790965105263</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1245785958627225</v>
+        <v>0.04478927850557137</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.1384871333603442</v>
+        <v>-0.5155970450434163</v>
       </c>
       <c r="E233" t="n">
-        <v>1.197834244546017</v>
+        <v>0.298769175508363</v>
       </c>
       <c r="F233" t="n">
-        <v>-1.032210765319538</v>
-      </c>
-      <c r="G233" t="n">
-        <v>1.197834244546017</v>
+        <v>0.6177431158635652</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-0.6228585062216963</v>
+        <v>-2.455215751762288</v>
       </c>
       <c r="C234" t="n">
-        <v>2.242782855618303</v>
+        <v>1.198369066644868</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.6845690959091115</v>
+        <v>-0.4134298649352377</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5781798598878798</v>
+        <v>-0.1726234199697174</v>
       </c>
       <c r="F234" t="n">
-        <v>2.84582826505566</v>
-      </c>
-      <c r="G234" t="n">
-        <v>2.84582826505566</v>
+        <v>0.7462759345501352</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>-0.755418575570471</v>
+        <v>-1.13930285466547</v>
       </c>
       <c r="C235" t="n">
-        <v>2.079321755205378</v>
+        <v>1.067510245682325</v>
       </c>
       <c r="D235" t="n">
-        <v>-0.2851649737549776</v>
+        <v>0.0003715130068328458</v>
       </c>
       <c r="E235" t="n">
-        <v>0.4070445479863124</v>
+        <v>-0.1098422007640584</v>
       </c>
       <c r="F235" t="n">
-        <v>1.616630960916539</v>
-      </c>
-      <c r="G235" t="n">
-        <v>2.079321755205378</v>
+        <v>0.7316955359671756</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>-0.6138826781011105</v>
+        <v>-1.020767802966034</v>
       </c>
       <c r="C236" t="n">
-        <v>2.479427488290719</v>
+        <v>0.5919937630444926</v>
       </c>
       <c r="D236" t="n">
-        <v>0.536416067160533</v>
+        <v>-0.2247798772029514</v>
       </c>
       <c r="E236" t="n">
-        <v>0.2842301872575205</v>
+        <v>0.09473279725185561</v>
       </c>
       <c r="F236" t="n">
-        <v>0.6791785957572891</v>
-      </c>
-      <c r="G236" t="n">
-        <v>2.479427488290719</v>
+        <v>0.6787130942897357</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>-0.6214681054670167</v>
+        <v>-3.02195733714497</v>
       </c>
       <c r="C237" t="n">
-        <v>2.158542928526597</v>
+        <v>1.237509314623267</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.5103957843135772</v>
+        <v>0.1622867661311894</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7858505077704507</v>
+        <v>0.543266823467789</v>
       </c>
       <c r="F237" t="n">
-        <v>3.406731806065343</v>
-      </c>
-      <c r="G237" t="n">
-        <v>3.406731806065343</v>
+        <v>0.7506369735077173</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>-3.467056296848696</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1.038676545065589</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.1308930960665224</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.07115557514056967</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.728482861081972</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>-2.649492888465336</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1.147432979532142</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.1085582862324054</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-0.02669172301913275</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.7406005933931757</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>-1.805857109642677</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1.173870204039078</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-0.517921526320681</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-0.9741729448246979</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.7435462509186141</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>-3.854058490804474</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.9354009934145838</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-0.4629884658667399</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-0.06965189608832852</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.7169758132890097</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-3.23987682778871</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.6854493388898131</v>
+      </c>
+      <c r="D242" t="n">
+        <v>-0.9915304076965075</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.998207389660082</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.6891259922174557</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>-5.173894209295031</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.2264565923323711</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-0.8249250890772976</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1.459352958989468</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.6379846389462813</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>-4.465852180009911</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.5873728734484994</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-0.7682289550827323</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-0.4135340671560574</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.6781982309307213</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>-3.249722486182395</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.9139976913189309</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-0.4488018384884581</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.1982762708236258</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.7145910395821197</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>-5.039056712941724</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.8270846046628783</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-0.3705167967033559</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.4580806219370792</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0.7049071112370577</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.05981270169661775</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1.45488801763666</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.7893763256172698</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-0.9964049292567002</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.7748574892518508</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.5645019904788555</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.1287596160138144</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.9099729134324883</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3.511448199642524</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.9076740501985733</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-3.730390409471035</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.6944673243543357</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.37260602900962</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-0.2423165054203742</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.6901307836523848</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>-3.154733127482138</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.7549962118703405</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-0.673830188715586</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.2100363714999769</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.6968749626024541</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>-2.70909465881337</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.1134190811904869</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-0.9141796705347159</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2.897901802236343</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.8179387607603645</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-3.808790122225191</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.5382462123667301</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-1.048626453559671</v>
+      </c>
+      <c r="E252" t="n">
+        <v>-0.1905604561715231</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0.6727244975258698</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>-4.230024531836465</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.9250078293642245</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-0.3947097165667597</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.1463230578926363</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.7158177983131931</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-6.260438536937455</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.7048338685797162</v>
+      </c>
+      <c r="D254" t="n">
+        <v>-0.4155570868964452</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.6124014749285084</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.6912858326251796</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-3.950649874981666</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1.127546528977918</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-0.4304863513732734</v>
+      </c>
+      <c r="E255" t="n">
+        <v>-0.4481666143483198</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0.7383848285456238</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-2.975888596583809</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.8079862796088143</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.1495224775476858</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.2163518433612984</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.7027791599877119</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-3.18356973263882</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.4493831963097559</v>
+      </c>
+      <c r="D257" t="n">
+        <v>-0.408731559216727</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.260417380339256</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0.6628233064264522</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-2.461362252371716</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.9432191495343691</v>
+      </c>
+      <c r="D258" t="n">
+        <v>-0.139911463910389</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.7476117636804875</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0.7178469187412199</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-1.784180081746878</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1.186930712569526</v>
+      </c>
+      <c r="D259" t="n">
+        <v>-0.3453752080183399</v>
+      </c>
+      <c r="E259" t="n">
+        <v>-0.339209161842105</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0.7450014636331211</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-2.125213412370318</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1.190143176885641</v>
+      </c>
+      <c r="D260" t="n">
+        <v>-0.2364293504140548</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.2164140620376151</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.7453593990769678</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-2.058128911010413</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1.015748107038029</v>
+      </c>
+      <c r="D261" t="n">
+        <v>-0.2541673004485992</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-0.1090523010645774</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.7259281554620718</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>-1.127532941266129</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1.02866376433917</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-0.3514613644611166</v>
+      </c>
+      <c r="E262" t="n">
+        <v>-0.2718510500015714</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.7273672287322295</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.447260896912589</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1.245254867704089</v>
+      </c>
+      <c r="D263" t="n">
+        <v>-0.1952078689527682</v>
+      </c>
+      <c r="E263" t="n">
+        <v>-0.1167616963765829</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0.7514999894689889</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>-1.770782663607636</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1.207203803177111</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-0.1756161438308365</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.08274667247076961</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0.7472603082367389</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-2.675606028488324</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.2314871418994844</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.5113232952127529</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1.62083478993023</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0.6385451469597292</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-1.962282326404922</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1.448744140744714</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-0.09904214762497064</v>
+      </c>
+      <c r="E266" t="n">
+        <v>-0.1369481568067895</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0.7741729333826303</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>-0.1354394200912833</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1.144021326616527</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.1680438245842788</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.02241000453859363</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0.7402204641900354</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-2.977715732610144</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.6597834750548953</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-0.3876578444097494</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-0.4157619678678652</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.6862662803391393</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>-4.34219636769542</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.4333401667917701</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.3455108566334074</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.4604935699409975</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.6610357787448649</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-4.983089446402844</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.7330681202228442</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.1836236023255893</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-0.188213314355524</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.6944317164075668</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-5.255192683341892</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.678512488283892</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-0.2005508693523821</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-0.04639112507425582</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.6883530825580165</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-5.258557942033432</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.7724885520747607</v>
+      </c>
+      <c r="D272" t="n">
+        <v>-0.06504643861933093</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-0.3513264810001051</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.6988239736851856</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-2.23295099413106</v>
+      </c>
+      <c r="C273" t="n">
+        <v>1.193565204031727</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.1850802332667692</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-0.4668650029635156</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.7457406841854888</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-1.273477955402622</v>
+      </c>
+      <c r="C274" t="n">
+        <v>1.208803569669527</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.0984034671725032</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-0.5817338618507549</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.7474385555488232</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-2.857736939959126</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.7535010606212074</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.4736965300338551</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-0.2120739673440545</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.6967083716077178</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-2.728455266198474</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.6838381329204385</v>
+      </c>
+      <c r="D276" t="n">
+        <v>-0.3513281911078237</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.9128468418275266</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.688946470309342</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-2.610045703297214</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.936086730561705</v>
+      </c>
+      <c r="D277" t="n">
+        <v>-0.1717194319776718</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.3488040538994954</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.7170522186918294</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-2.272615343981437</v>
+      </c>
+      <c r="C278" t="n">
+        <v>1.123702501238291</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-0.03812256555809299</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.09938912556795759</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.7379565237802633</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-0.1010851206346155</v>
+      </c>
+      <c r="C279" t="n">
+        <v>1.275657715648611</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-0.1286600441437122</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-0.4486824492585763</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.7548875000535075</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.7811033389397288</v>
+      </c>
+      <c r="C280" t="n">
+        <v>1.190228435922254</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-0.2396986766062024</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.2076423741184451</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0.7453688987096825</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>-1.822142780852433</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.7853622560091688</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.15458946800359</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.1571593320635368</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.7002583724763561</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-1.834753444714825</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.6747362370785603</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.1696227054733157</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.6914255821269084</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0.6879323295104336</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>-5.459893497230455</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.3288105038127123</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0.5286646308731479</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-0.8779170313603332</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.6493889968254914</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-1.234980210304892</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.9543893512755505</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-0.2572152157039554</v>
+      </c>
+      <c r="E284" t="n">
+        <v>-0.2891515731090268</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.7190915119023116</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>-2.055397515839618</v>
+      </c>
+      <c r="C285" t="n">
+        <v>1.27921288766607</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-0.2773750869957498</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-0.4704052724813267</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.755283620274248</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>-2.707558485811043</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.6997780371843045</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-0.5431710737003669</v>
+      </c>
+      <c r="E286" t="n">
+        <v>-0.07231791765577331</v>
+      </c>
+      <c r="F286" t="n">
+        <v>0.6907225076894121</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-2.797545198660823</v>
+      </c>
+      <c r="C287" t="n">
+        <v>1.04485236592022</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-0.3588174296857256</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-0.761890008754936</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.7291709761740622</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-4.0724318559651</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.7566566487847108</v>
+      </c>
+      <c r="D288" t="n">
+        <v>-0.1615308495751573</v>
+      </c>
+      <c r="E288" t="n">
+        <v>-0.6873616931694922</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0.6970599698633732</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>-3.373691234851529</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.7123640069375422</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-0.3393322175205061</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-0.9664560949241243</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0.6921248468989928</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>-2.890519108099808</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.8996379329196724</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-0.5093070070410948</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-0.7942298083774729</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0.7129910633674774</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>-0.8931059994317299</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.9255220537451305</v>
+      </c>
+      <c r="D291" t="n">
+        <v>-0.5144031911310509</v>
+      </c>
+      <c r="E291" t="n">
+        <v>-0.0272880469649251</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.7158750936210641</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-3.012723104767252</v>
+      </c>
+      <c r="C292" t="n">
+        <v>1.121469759239776</v>
+      </c>
+      <c r="D292" t="n">
+        <v>-0.3716801091607134</v>
+      </c>
+      <c r="E292" t="n">
+        <v>-0.4072315566283327</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0.7377077498112499</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-3.504297920953044</v>
+      </c>
+      <c r="C293" t="n">
+        <v>1.173390456652512</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-0.5335566970187681</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-0.3776346605938442</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0.7434927970661049</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-1.151887719532901</v>
+      </c>
+      <c r="C294" t="n">
+        <v>1.088115270376494</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.3306175173594422</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.3135651755424254</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.7339913649425773</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>-3.802716613849701</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.6265167050723826</v>
+      </c>
+      <c r="D295" t="n">
+        <v>-0.505062653571306</v>
+      </c>
+      <c r="E295" t="n">
+        <v>-0.7546696379855981</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.6825596691810616</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>-3.040538585431052</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.5915706669706835</v>
+      </c>
+      <c r="D296" t="n">
+        <v>-0.3709680257504173</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.4278778759705151</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.6786659525735743</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-0.01695830297002857</v>
+      </c>
+      <c r="C297" t="n">
+        <v>1.543715777961806</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-0.3836888747850766</v>
+      </c>
+      <c r="E297" t="n">
+        <v>0.4640089813880651</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0.7847547521283286</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>1.881196701250679</v>
+      </c>
+      <c r="C298" t="n">
+        <v>1.11844411673705</v>
+      </c>
+      <c r="D298" t="n">
+        <v>-0.4105284528035879</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-0.3459554168350867</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.7373706302091109</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>1.658344778547687</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-0.2395416891651967</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-2.876346506440858</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.1584615001189423</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.6001254785412375</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0.05541187345811087</v>
+      </c>
+      <c r="C300" t="n">
+        <v>1.527133610923499</v>
+      </c>
+      <c r="D300" t="n">
+        <v>-0.4022649854515579</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.1342492416350868</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.7829071532961724</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2.359998788144756</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.4207408094510188</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.8332471718002877</v>
+      </c>
+      <c r="E301" t="n">
+        <v>-0.5081775281113734</v>
+      </c>
+      <c r="F301" t="n">
+        <v>0.6596319478791576</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>-2.730325601694054</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.863241126542053</v>
+      </c>
+      <c r="D302" t="n">
+        <v>-0.4585346740604574</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.5066360194582279</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0.7089357009530139</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1.722558191583889</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1.290829599614069</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-2.830602904955286</v>
+      </c>
+      <c r="E303" t="n">
+        <v>0.1451270562873289</v>
+      </c>
+      <c r="F303" t="n">
+        <v>0.7565779639736593</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1.207779489171728</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.8493036122681661</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-0.6480390128193239</v>
+      </c>
+      <c r="E304" t="n">
+        <v>-2.355843363682218</v>
+      </c>
+      <c r="F304" t="n">
+        <v>0.7073827715297302</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1.586848931228099</v>
+      </c>
+      <c r="C305" t="n">
+        <v>1.30630760933136</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-0.1722678509470927</v>
+      </c>
+      <c r="E305" t="n">
+        <v>-0.6553609293265076</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0.7583025366794888</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-1.164918355700126</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.6220843808710093</v>
+      </c>
+      <c r="D306" t="n">
+        <v>-0.5444793880297477</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-0.1043717042432985</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.6820658159350247</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>-1.954749115420489</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.9858433700821316</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-0.06166758125836752</v>
+      </c>
+      <c r="E307" t="n">
+        <v>-0.3728397223880259</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0.722596144817865</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>-2.333812552157907</v>
+      </c>
+      <c r="C308" t="n">
+        <v>-0.2359006730777042</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-1.372091887622283</v>
+      </c>
+      <c r="E308" t="n">
+        <v>-0.2834713962902262</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0.586468408188435</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>2.857169868348622</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1.267580062755614</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-1.321966805699422</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.009580397996419448</v>
+      </c>
+      <c r="F309" t="n">
+        <v>0.753987481255169</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>-2.369450462815782</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.7821030859085812</v>
+      </c>
+      <c r="D310" t="n">
+        <v>-1.050332943520218</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-0.6281402700608707</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.6998952330351882</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>-0.8091826052897799</v>
+      </c>
+      <c r="C311" t="n">
+        <v>-0.01569098101561253</v>
+      </c>
+      <c r="D311" t="n">
+        <v>-0.9902853851059499</v>
+      </c>
+      <c r="E311" t="n">
+        <v>3.085181578722729</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0.8453296883576514</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>-0.7341143282664876</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.4607462496565576</v>
+      </c>
+      <c r="D312" t="n">
+        <v>-0.5345048586600695</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1.896398933197314</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0.6714622266199197</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>-0.2911920455233964</v>
+      </c>
+      <c r="C313" t="n">
+        <v>1.00324571424862</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.0748173880378141</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1.233923013441728</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0.7245351284672582</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>-0.8329315152524704</v>
+      </c>
+      <c r="C314" t="n">
+        <v>-0.120564835081262</v>
+      </c>
+      <c r="D314" t="n">
+        <v>-1.016159161665096</v>
+      </c>
+      <c r="E314" t="n">
+        <v>3.780669878417088</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0.9470495324278043</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/artifacts/MaxRel_01_updated_data.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:G314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,7 @@
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -487,6 +488,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -506,15 +508,20 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
+          <t>PC3</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>PC4</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>PC5</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>MaxRel_Score</t>
         </is>
@@ -534,19 +541,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4195119344233529</v>
+        <v>-1.794327051012559</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4660838440881593</v>
+        <v>0.8266466039163004</v>
       </c>
       <c r="D5" t="n">
-        <v>2.570168971278334</v>
+        <v>0.1410525395332481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8132021610558516</v>
+        <v>2.195805798400938</v>
       </c>
       <c r="F5" t="n">
-        <v>0.875428368862209</v>
+        <v>-0.2757338548187723</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6781757363623478</v>
       </c>
     </row>
     <row r="6">
@@ -556,19 +566,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.556513934636973</v>
+        <v>-3.206607464708913</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.142125407770038</v>
+        <v>1.231880426372369</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9510782337748471</v>
+        <v>-0.9476657654731485</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.198947789636557</v>
+        <v>-1.759708206924972</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6151889609011129</v>
+        <v>-0.8401254901030082</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5768499294315204</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +591,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-2.732642337467384</v>
+        <v>-3.001429808213677</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6877577382785514</v>
+        <v>1.083388471570611</v>
       </c>
       <c r="D7" t="n">
-        <v>2.069306774552422</v>
+        <v>-1.794503406806994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1360842443220136</v>
+        <v>1.217127781404059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7949238742549297</v>
+        <v>-1.080131184438291</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5582473955340463</v>
       </c>
     </row>
     <row r="8">
@@ -600,19 +616,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.418341128183126</v>
+        <v>1.031991897532646</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.23199091104253</v>
+        <v>1.572919391065432</v>
       </c>
       <c r="D8" t="n">
-        <v>2.472625585453397</v>
+        <v>2.607305954845203</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9783204915206499</v>
+        <v>3.140456687212841</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8597500425092688</v>
+        <v>0.3974884593307781</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8633368572292847</v>
       </c>
     </row>
     <row r="9">
@@ -622,19 +641,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.759784704925722</v>
+        <v>-2.717337837461834</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5624826880101348</v>
+        <v>0.985638828674276</v>
       </c>
       <c r="D9" t="n">
-        <v>2.640735320533334</v>
+        <v>-0.9117952634010236</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5988278954596763</v>
+        <v>1.975550457941592</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8867706269128066</v>
+        <v>-0.7280855656084344</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6452716128602287</v>
       </c>
     </row>
     <row r="10">
@@ -644,19 +666,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.482432951521547</v>
+        <v>-1.03154826580518</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.524199988445216</v>
+        <v>2.646505277926869</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5371441692211534</v>
+        <v>-2.431354275949879</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9644139817590437</v>
+        <v>1.340952203322407</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5486565835616674</v>
+        <v>0.1338487990743973</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7540690036122331</v>
       </c>
     </row>
     <row r="11">
@@ -666,19 +691,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.039128352592894</v>
+        <v>-1.724948555673441</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.172837682867973</v>
+        <v>1.335447189674785</v>
       </c>
       <c r="D11" t="n">
-        <v>1.449595613050803</v>
+        <v>0.9565316215221499</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.044284745282894</v>
+        <v>-0.7676723897660104</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6953165687219887</v>
+        <v>-0.5796508931683247</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6564138399961255</v>
       </c>
     </row>
     <row r="12">
@@ -688,19 +716,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.237290392937454</v>
+        <v>-1.310207737443872</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.10562608156653</v>
+        <v>1.954183133808276</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.513447301400873</v>
+        <v>-0.9982346202973417</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8775541256613852</v>
+        <v>-2.056498939309085</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3797930998848826</v>
+        <v>0.005566311535691836</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6673373946767058</v>
       </c>
     </row>
     <row r="13">
@@ -710,19 +741,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.622637005863542</v>
+        <v>-2.06388542579465</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.382550580495274</v>
+        <v>1.659144671584782</v>
       </c>
       <c r="D13" t="n">
-        <v>1.785937948829724</v>
+        <v>-1.25210127580811</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6121181299650731</v>
+        <v>1.453200649073995</v>
       </c>
       <c r="F13" t="n">
-        <v>0.749377485944159</v>
+        <v>-0.3333480318677018</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6303760454783708</v>
       </c>
     </row>
     <row r="14">
@@ -732,19 +766,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.569677428608911</v>
+        <v>-1.109153646070434</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.554041296054391</v>
+        <v>1.885748423667133</v>
       </c>
       <c r="D14" t="n">
-        <v>1.622863985734888</v>
+        <v>-0.86833168105994</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4190516129546148</v>
+        <v>1.772400803816397</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7231663103585916</v>
+        <v>-0.5057035976712174</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6587641422276826</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +791,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2757343362195343</v>
+        <v>-0.1072788982506667</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.588752749455761</v>
+        <v>1.819038944701077</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5036554658556712</v>
+        <v>-1.586126951220008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4711879349990474</v>
+        <v>1.572147989333203</v>
       </c>
       <c r="F15" t="n">
-        <v>0.543273883175983</v>
+        <v>-0.4003524094621577</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6504070204872784</v>
       </c>
     </row>
     <row r="16">
@@ -776,19 +816,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.65948819039014</v>
+        <v>4.205128615459349</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.829698219236582</v>
+        <v>1.814879077295392</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.71699699845938</v>
+        <v>-1.304495418040098</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5951823492917649</v>
+        <v>0.3391348992419715</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6759971933216478</v>
+        <v>-0.4452964990742642</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8466118546548425</v>
       </c>
     </row>
     <row r="17">
@@ -798,19 +841,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-3.263671802234064</v>
+        <v>-3.139614609620388</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.18419344153105</v>
+        <v>1.484462559872185</v>
       </c>
       <c r="D17" t="n">
-        <v>1.692558989926904</v>
+        <v>-2.471806727605942</v>
       </c>
       <c r="E17" t="n">
-        <v>0.411098263247451</v>
+        <v>1.00757991586259</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7343685155276131</v>
+        <v>-0.7533993912566888</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6084925036477432</v>
       </c>
     </row>
     <row r="18">
@@ -820,19 +866,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.008930101492554281</v>
+        <v>-0.8095375790379955</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.360558039340776</v>
+        <v>1.688259503801126</v>
       </c>
       <c r="D18" t="n">
-        <v>1.727457404946159</v>
+        <v>-0.3847500410808603</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5444190453612425</v>
+        <v>1.987997456479268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7399778014391581</v>
+        <v>-0.3609283196558635</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6471310800416386</v>
       </c>
     </row>
     <row r="19">
@@ -842,19 +891,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.364264432413657</v>
+        <v>-0.7485387245176574</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.9743060333187968</v>
+        <v>1.399826749910021</v>
       </c>
       <c r="D19" t="n">
-        <v>2.639056972328434</v>
+        <v>3.697566532975844</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.034129648358749</v>
+        <v>-0.234925292090128</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8865008629440071</v>
+        <v>-1.284854825817167</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -864,19 +916,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3624509392039922</v>
+        <v>-0.439763927416315</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.921668233693249</v>
+        <v>1.796807067120545</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1020434791323256</v>
+        <v>0.6662162297599099</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4751829882288403</v>
+        <v>-1.185089600076414</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4787220558854894</v>
+        <v>0.4607110465391662</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6476218914420823</v>
       </c>
     </row>
     <row r="21">
@@ -886,19 +941,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.850572094728604</v>
+        <v>-3.315725625114254</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.5005500067808011</v>
+        <v>0.8295237185953052</v>
       </c>
       <c r="D21" t="n">
-        <v>2.272851443191966</v>
+        <v>-1.699617343335004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6728391145625736</v>
+        <v>1.412600404229157</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8276399801737792</v>
+        <v>-0.6063769325271198</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5611720488984752</v>
       </c>
     </row>
     <row r="22">
@@ -908,19 +966,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.466952807984113</v>
+        <v>-1.093634772212332</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.4503854881361565</v>
+        <v>0.8897440461673252</v>
       </c>
       <c r="D22" t="n">
-        <v>3.345196764767052</v>
+        <v>2.93383677487331</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1226673444420872</v>
+        <v>1.832831070209446</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>-0.4502153968916001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9042671898228499</v>
       </c>
     </row>
     <row r="23">
@@ -930,19 +991,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.86230179987503</v>
+        <v>-3.133532782504384</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.956797660777561</v>
+        <v>1.269440901868354</v>
       </c>
       <c r="D23" t="n">
-        <v>2.039373360368817</v>
+        <v>-1.875215513716227</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5355743947452036</v>
+        <v>1.228925284894665</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7901126219853953</v>
+        <v>-0.6218414995936979</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5815553696659904</v>
       </c>
     </row>
     <row r="24">
@@ -952,19 +1016,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.729820643750467</v>
+        <v>-0.005007589948370198</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.749009366378937</v>
+        <v>1.772354314905738</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7239303781105761</v>
+        <v>1.668822829050038</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7088260566819197</v>
+        <v>-0.5770910838196393</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5786790716722673</v>
+        <v>0.1309011357821617</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7456988760153263</v>
       </c>
     </row>
     <row r="25">
@@ -974,19 +1041,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2015279032647203</v>
+        <v>-0.1542981151550365</v>
       </c>
       <c r="C25" t="n">
-        <v>-1.981213329832568</v>
+        <v>2.107414558915569</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6098661463287984</v>
+        <v>0.9290913610961483</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.159994691517118</v>
+        <v>-0.6495264212046444</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5603453196095525</v>
+        <v>-0.4960873802960931</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6865336722361345</v>
       </c>
     </row>
     <row r="26">
@@ -996,19 +1066,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9374741982360316</v>
+        <v>-1.922664826738318</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.132550981390873</v>
+        <v>1.312583990890891</v>
       </c>
       <c r="D26" t="n">
-        <v>1.780252340560303</v>
+        <v>1.504251901479138</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.19173088925595</v>
+        <v>-0.8771479786934423</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7484636277547073</v>
+        <v>-0.5929557720800303</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7250700643150136</v>
       </c>
     </row>
     <row r="27">
@@ -1018,19 +1091,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2865032767134751</v>
+        <v>-1.844143693730279</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.5291481963763114</v>
+        <v>0.9505942684323192</v>
       </c>
       <c r="D27" t="n">
-        <v>2.821589937623261</v>
+        <v>0.4707063892764795</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5272938642498802</v>
+        <v>2.173046842601052</v>
       </c>
       <c r="F27" t="n">
-        <v>0.915839719452416</v>
+        <v>-0.510489455566618</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6747757575429606</v>
       </c>
     </row>
     <row r="28">
@@ -1040,19 +1116,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.648340365907385</v>
+        <v>2.740023791428921</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.189366731619616</v>
+        <v>2.017640987334323</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.082483341934498</v>
+        <v>-0.3103300508809074</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6770176248238374</v>
+        <v>-0.8438137095232331</v>
       </c>
       <c r="F28" t="n">
-        <v>0.599367293516583</v>
+        <v>0.1979080941754373</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7036752661178589</v>
       </c>
     </row>
     <row r="29">
@@ -1062,19 +1141,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.64636765269775</v>
+        <v>0.7082837367612</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.532756859389116</v>
+        <v>3.265941909083697</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.519146958162668</v>
+        <v>-2.678087900458027</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9888165227779678</v>
+        <v>-2.256716559385537</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3496776445458151</v>
+        <v>0.01824702062845488</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.8316697796530345</v>
       </c>
     </row>
     <row r="30">
@@ -1084,19 +1166,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.319267445799227</v>
+        <v>1.221471649618208</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.244104780052123</v>
+        <v>1.330681096672033</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05200216731138559</v>
+        <v>-0.7656358458243679</v>
       </c>
       <c r="E30" t="n">
-        <v>1.148490600395166</v>
+        <v>2.008494863626177</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5744284821124763</v>
+        <v>0.4205442862075927</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6501932042781203</v>
       </c>
     </row>
     <row r="31">
@@ -1106,19 +1191,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.042184603004716</v>
+        <v>-0.4314219770991592</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.663203144488622</v>
+        <v>1.676622753910774</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3358165794164945</v>
+        <v>-0.4731271310976896</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.186269001309663</v>
+        <v>-1.361061563410109</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4274371806522259</v>
+        <v>-0.5590212636032742</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.632565636283921</v>
       </c>
     </row>
     <row r="32">
@@ -1128,19 +1216,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.477617926089766</v>
+        <v>3.109911014922511</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.827125725599659</v>
+        <v>2.66921338148746</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.602136135131042</v>
+        <v>-1.181705659756586</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8095610581868992</v>
+        <v>-0.8537476221659599</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5864290829592963</v>
+        <v>-0.01350886227139597</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7569137925221588</v>
       </c>
     </row>
     <row r="33">
@@ -1150,19 +1241,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.569498969483431</v>
+        <v>-1.227913917908319</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.765666324649121</v>
+        <v>1.692674199846267</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1203560523721204</v>
+        <v>-0.5401249936488385</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3771918964833491</v>
+        <v>-1.08453702959394</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4816654691901178</v>
+        <v>0.1413431098258971</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6345765032532266</v>
       </c>
     </row>
     <row r="34">
@@ -1172,19 +1266,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3398922854668763</v>
+        <v>-1.72360898145948</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.9439326234644515</v>
+        <v>1.238427749409204</v>
       </c>
       <c r="D34" t="n">
-        <v>2.205474152118386</v>
+        <v>2.092831436755902</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.429800315759094</v>
+        <v>-0.5163840019418547</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8168103052625093</v>
+        <v>-0.9225322165795042</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.7988479580359505</v>
       </c>
     </row>
     <row r="35">
@@ -1194,19 +1291,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.349392472199256</v>
+        <v>0.6540439113402604</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.261789259385896</v>
+        <v>1.36957612360576</v>
       </c>
       <c r="D35" t="n">
-        <v>1.423108624692335</v>
+        <v>3.233176403034224</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5749998153035886</v>
+        <v>0.2093699003650231</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6910592667626752</v>
+        <v>0.2329620200169475</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9417891319721569</v>
       </c>
     </row>
     <row r="36">
@@ -1216,19 +1316,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3689108405937345</v>
+        <v>0.1791636874451352</v>
       </c>
       <c r="C36" t="n">
-        <v>-2.485814416446983</v>
+        <v>2.259914803533132</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7309684481686501</v>
+        <v>-0.2776997467849952</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.120757864846565</v>
+        <v>-1.146042247207457</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4464897872875588</v>
+        <v>0.7775352195661309</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.7056383501539292</v>
       </c>
     </row>
     <row r="37">
@@ -1238,19 +1341,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4994969098945983</v>
+        <v>-0.7445362503305609</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.52543208081428</v>
+        <v>1.794423683301577</v>
       </c>
       <c r="D37" t="n">
-        <v>1.711953152018167</v>
+        <v>2.372316463312333</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.726618397743815</v>
+        <v>-0.6930547696276783</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7374857745814903</v>
+        <v>-0.9193030972140867</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8338811444619408</v>
       </c>
     </row>
     <row r="38">
@@ -1260,19 +1366,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.3892448701501115</v>
+        <v>-0.9073256349070201</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.225447376189067</v>
+        <v>1.562830873786466</v>
       </c>
       <c r="D38" t="n">
-        <v>1.520657980203532</v>
+        <v>-0.8779573020385022</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4577514791389596</v>
+        <v>1.889271743945711</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7067385526341784</v>
+        <v>-0.5524023383530561</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6323823659752095</v>
       </c>
     </row>
     <row r="39">
@@ -1282,19 +1391,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.098864851231217</v>
+        <v>1.393026372256658</v>
       </c>
       <c r="C39" t="n">
-        <v>-2.878531891710405</v>
+        <v>2.740542239220483</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02196145033098014</v>
+        <v>2.392095052446219</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6387953603671084</v>
+        <v>-0.8627361749164666</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6335103192287275</v>
+        <v>0.835137592895137</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8363603720932307</v>
       </c>
     </row>
     <row r="40">
@@ -1304,19 +1416,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2774167769873147</v>
+        <v>-1.284060309867249</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.160564652179614</v>
+        <v>1.386640182516669</v>
       </c>
       <c r="D40" t="n">
-        <v>2.345177643445632</v>
+        <v>1.13642501167626</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6551223299533194</v>
+        <v>1.557427680750038</v>
       </c>
       <c r="F40" t="n">
-        <v>0.839265102285905</v>
+        <v>0.2545793512859313</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.67896330803641</v>
       </c>
     </row>
     <row r="41">
@@ -1326,19 +1441,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.767967540942014</v>
+        <v>-1.174740106290718</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9230748920394523</v>
+        <v>1.215465460605839</v>
       </c>
       <c r="D41" t="n">
-        <v>1.488632715879264</v>
+        <v>-1.453167274637899</v>
       </c>
       <c r="E41" t="n">
-        <v>1.074074022104394</v>
+        <v>2.26000041333142</v>
       </c>
       <c r="F41" t="n">
-        <v>0.701591073475354</v>
+        <v>-0.2432081139021101</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.6877658218215172</v>
       </c>
     </row>
     <row r="42">
@@ -1348,19 +1466,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.70470005568864</v>
+        <v>2.509091858876031</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.991415591061618</v>
+        <v>2.006988296344491</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.525172274011186</v>
+        <v>0.8495746818683177</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.03386872592200748</v>
+        <v>0.7639031994417528</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6794235773022457</v>
+        <v>0.3213577558215022</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6811453951612144</v>
       </c>
     </row>
     <row r="43">
@@ -1370,19 +1491,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.870749143283886</v>
+        <v>4.708412666080192</v>
       </c>
       <c r="C43" t="n">
-        <v>-3.69875034010539</v>
+        <v>3.452806536068398</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.653513751179224</v>
+        <v>2.134162574578806</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.04482669724439057</v>
+        <v>0.147072062405809</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8435777400629513</v>
+        <v>1.399732910430662</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8957125770611211</v>
       </c>
     </row>
     <row r="44">
@@ -1392,19 +1516,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.486762166006088</v>
+        <v>0.9051102997133903</v>
       </c>
       <c r="C44" t="n">
-        <v>-2.152828515825692</v>
+        <v>2.373459343335402</v>
       </c>
       <c r="D44" t="n">
-        <v>1.472405412640346</v>
+        <v>2.948803854733863</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.961908584890402</v>
+        <v>0.3925112527999333</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6989828294221436</v>
+        <v>-0.2071361989164384</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.9061432992712449</v>
       </c>
     </row>
     <row r="45">
@@ -1414,19 +1541,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.049190168862161</v>
+        <v>1.302410636587264</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.825571651929314</v>
+        <v>1.219486813627053</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.270942191062543</v>
+        <v>0.399282852426334</v>
       </c>
       <c r="E45" t="n">
-        <v>4.142707699025716</v>
+        <v>2.083628976605353</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>4.159982623629783</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.920230912888681</v>
       </c>
     </row>
     <row r="46">
@@ -1436,19 +1566,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5127207977770396</v>
+        <v>-0.6488402660297927</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.29256828071152</v>
+        <v>1.462394816979417</v>
       </c>
       <c r="D46" t="n">
-        <v>1.47989231598431</v>
+        <v>2.153129352937662</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.150031731892318</v>
+        <v>-0.5173764655515621</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7001862130550459</v>
+        <v>-0.4267799721978509</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8064062453786458</v>
       </c>
     </row>
     <row r="47">
@@ -1458,19 +1591,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.792165211649194</v>
+        <v>-2.157965103877004</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.251804313498287</v>
+        <v>1.220702156463602</v>
       </c>
       <c r="D47" t="n">
-        <v>1.088345835389974</v>
+        <v>0.2848361623867781</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.2403186975326974</v>
+        <v>-0.9464536017266205</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6372522329272635</v>
+        <v>0.2430257633599492</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5754495562923118</v>
       </c>
     </row>
     <row r="48">
@@ -1480,19 +1616,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.200407866350103</v>
+        <v>0.3633108042040964</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.461401464134005</v>
+        <v>1.713011259002328</v>
       </c>
       <c r="D48" t="n">
-        <v>2.136895950816551</v>
+        <v>1.522599395213006</v>
       </c>
       <c r="E48" t="n">
-        <v>1.230451538415712</v>
+        <v>2.774146781495195</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8057876058594206</v>
+        <v>0.5907180127882135</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.7645745637160161</v>
       </c>
     </row>
     <row r="49">
@@ -1502,19 +1641,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.45308171897122</v>
+        <v>-1.378375281388108</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.689117953600398</v>
+        <v>1.8161416209738</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6555571206292281</v>
+        <v>-0.1510889325606581</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.168569733602351</v>
+        <v>-1.025333178497073</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5676893132633262</v>
+        <v>-0.7296817962063096</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6500440542718995</v>
       </c>
     </row>
     <row r="50">
@@ -1524,19 +1666,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6001309708084492</v>
+        <v>0.02245427853775907</v>
       </c>
       <c r="C50" t="n">
-        <v>-2.008947308995419</v>
+        <v>2.357429997283382</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9964327705277104</v>
+        <v>1.529023317730916</v>
       </c>
       <c r="E50" t="n">
-        <v>-2.324089542917013</v>
+        <v>-0.8024554233504235</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6224788783341002</v>
+        <v>-1.586502583910758</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.7281751381512649</v>
       </c>
     </row>
     <row r="51">
@@ -1546,19 +1691,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.416071278997086</v>
+        <v>0.4838299509096889</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.826408208811362</v>
+        <v>2.345927380151097</v>
       </c>
       <c r="D51" t="n">
-        <v>1.378972274383189</v>
+        <v>2.019998927735466</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.694584532907937</v>
+        <v>-0.2517092149213299</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6839651506591352</v>
+        <v>-2.15887263906615</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.789718471215767</v>
       </c>
     </row>
     <row r="52">
@@ -1568,19 +1716,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.606677987571263</v>
+        <v>0.2777253650858281</v>
       </c>
       <c r="C52" t="n">
-        <v>-2.099490302949656</v>
+        <v>2.347610421702798</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5015133020740463</v>
+        <v>1.628749070762004</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.521588629224988</v>
+        <v>-1.435272471274667</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5429295692833933</v>
+        <v>-1.425765950798547</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.740675667930827</v>
       </c>
     </row>
     <row r="53">
@@ -1590,19 +1741,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.63161689248705</v>
+        <v>0.9513718190895959</v>
       </c>
       <c r="C53" t="n">
-        <v>-2.383506799095743</v>
+        <v>2.237681258536934</v>
       </c>
       <c r="D53" t="n">
-        <v>0.104495929545711</v>
+        <v>2.259179998355149</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5977029411227951</v>
+        <v>-0.9845377043945397</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5980999040592121</v>
+        <v>0.7942033111488915</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.8196995944975018</v>
       </c>
     </row>
     <row r="54">
@@ -1612,19 +1766,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.043914860230793</v>
+        <v>-0.4184408888823915</v>
       </c>
       <c r="C54" t="n">
-        <v>-2.177770986232654</v>
+        <v>2.088451233331385</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4407484402379381</v>
+        <v>-0.5304562115791941</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.7449282240862437</v>
+        <v>-1.35471499468471</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3953345663194837</v>
+        <v>0.006956514046854807</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.6841580155383722</v>
       </c>
     </row>
     <row r="55">
@@ -1634,19 +1791,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.674806279624932</v>
+        <v>1.872104022260468</v>
       </c>
       <c r="C55" t="n">
-        <v>-2.480076348523352</v>
+        <v>2.580097864538633</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2076123653555517</v>
+        <v>2.707005861705984</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.650000716804917</v>
+        <v>-0.7100185531478943</v>
       </c>
       <c r="F55" t="n">
-        <v>0.677158075652446</v>
+        <v>-0.3356115214881986</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8758341472155958</v>
       </c>
     </row>
     <row r="56">
@@ -1656,19 +1816,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.737705392207292</v>
+        <v>1.115188151118449</v>
       </c>
       <c r="C56" t="n">
-        <v>-2.621169458897848</v>
+        <v>2.421183878079302</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.07212510468772937</v>
+        <v>2.319754671465148</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5425870117080887</v>
+        <v>-1.135113847604135</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6061398275077845</v>
+        <v>1.000447969093642</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.8272925730620532</v>
       </c>
     </row>
     <row r="57">
@@ -1678,19 +1841,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.806310219326617</v>
+        <v>-2.106080540469299</v>
       </c>
       <c r="C57" t="n">
-        <v>-1.789523632560072</v>
+        <v>1.671242616903242</v>
       </c>
       <c r="D57" t="n">
-        <v>1.003843933694974</v>
+        <v>-0.2119093052318455</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5937294866092923</v>
+        <v>-0.4347757717703558</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6236700881102278</v>
+        <v>0.9056660594666429</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.6318916322195978</v>
       </c>
     </row>
     <row r="58">
@@ -1700,19 +1866,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2065031424730624</v>
+        <v>-0.06888279037882533</v>
       </c>
       <c r="C58" t="n">
-        <v>-1.592302761568185</v>
+        <v>1.491797171335064</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1530086738765252</v>
+        <v>1.067040898056935</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4761344319551133</v>
+        <v>-0.9607850388530389</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4900975712348741</v>
+        <v>0.4248231175905327</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6702660743513807</v>
       </c>
     </row>
     <row r="59">
@@ -1722,19 +1891,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.739617175055792</v>
+        <v>-1.7723581412979</v>
       </c>
       <c r="C59" t="n">
-        <v>-2.056938491948376</v>
+        <v>1.973026661492348</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.202739161395296</v>
+        <v>-1.829895462969323</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3421883179877853</v>
+        <v>-1.289469131189905</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4297337860557036</v>
+        <v>-0.02048354301695497</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.6696980435277423</v>
       </c>
     </row>
     <row r="60">
@@ -1744,19 +1916,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.89889129164797</v>
+        <v>2.0407064220926</v>
       </c>
       <c r="C60" t="n">
-        <v>-3.018771259497401</v>
+        <v>2.938077867004708</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0438493236574022</v>
+        <v>2.592432129345295</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5796259757708677</v>
+        <v>-0.3399607674600304</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6941403720124526</v>
+        <v>0.7684474665693886</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8614724371276922</v>
       </c>
     </row>
     <row r="61">
@@ -1766,19 +1941,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.04790360619361342</v>
+        <v>2.375277704384579</v>
       </c>
       <c r="C61" t="n">
-        <v>-2.681316535588999</v>
+        <v>2.676540174377529</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.672846739256908</v>
+        <v>-3.762121709588877</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2260011638787932</v>
+        <v>0.2338968721924676</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4708173402063078</v>
+        <v>-0.5906759987886968</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.7578316665799099</v>
       </c>
     </row>
     <row r="62">
@@ -1788,19 +1966,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4.830789421663072</v>
+        <v>5.047700141838882</v>
       </c>
       <c r="C62" t="n">
-        <v>-4.152460467451951</v>
+        <v>3.869782876179495</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.112170975953126</v>
+        <v>1.589734792260276</v>
       </c>
       <c r="E62" t="n">
-        <v>0.004141674272815476</v>
+        <v>0.09794217550274191</v>
       </c>
       <c r="F62" t="n">
-        <v>0.8405493901126285</v>
+        <v>1.459290784224079</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.9288136859530161</v>
       </c>
     </row>
     <row r="63">
@@ -1810,19 +1991,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5554439751975372</v>
+        <v>1.043825725160137</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.708880323945292</v>
+        <v>2.698899594625399</v>
       </c>
       <c r="D63" t="n">
-        <v>-1.61758713599114</v>
+        <v>-1.987577458649672</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.032157388680614</v>
+        <v>-0.962450231895022</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4323533622575924</v>
+        <v>-0.6249186436284125</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.7606327737081996</v>
       </c>
     </row>
     <row r="64">
@@ -1832,19 +2016,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4599297604412184</v>
+        <v>0.625954021138731</v>
       </c>
       <c r="C64" t="n">
-        <v>-2.314523064790556</v>
+        <v>2.427732213596421</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.1074685637118097</v>
+        <v>0.2788196178959332</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.247869588913733</v>
+        <v>-0.6282840147763203</v>
       </c>
       <c r="F64" t="n">
-        <v>0.509303522998426</v>
+        <v>-0.6259062109851644</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.7266619070426266</v>
       </c>
     </row>
     <row r="65">
@@ -1854,19 +2041,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3.328955408487943</v>
+        <v>4.192847320136334</v>
       </c>
       <c r="C65" t="n">
-        <v>-3.82239209350755</v>
+        <v>3.553800634361198</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.377672935212005</v>
+        <v>0.3061816889508371</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.1752967835909997</v>
+        <v>-0.3174107623913819</v>
       </c>
       <c r="F65" t="n">
-        <v>0.726732807445975</v>
+        <v>1.036505851518262</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.8677316774292969</v>
       </c>
     </row>
     <row r="66">
@@ -1876,19 +2066,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.733701641129556</v>
+        <v>3.304148459784705</v>
       </c>
       <c r="C66" t="n">
-        <v>-2.210764700868111</v>
+        <v>2.269676764075368</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.46874995320997</v>
+        <v>0.2758918804801024</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.022750956451444</v>
+        <v>0.05704583342078518</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6816214642310559</v>
+        <v>-0.4622144477206602</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.7587116391348507</v>
       </c>
     </row>
     <row r="67">
@@ -1898,19 +2091,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.584832268187704</v>
+        <v>1.593118582672547</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.910437578091913</v>
+        <v>2.14944735616301</v>
       </c>
       <c r="D67" t="n">
-        <v>1.830752068785988</v>
+        <v>2.257880052688714</v>
       </c>
       <c r="E67" t="n">
-        <v>1.076691743862464</v>
+        <v>2.901691110766861</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7565805411995415</v>
+        <v>0.7114480289814767</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.8195366475252188</v>
       </c>
     </row>
     <row r="68">
@@ -1920,19 +2116,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.248475483005489</v>
+        <v>-0.638547339529714</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3886361581046381</v>
+        <v>0.961262831345928</v>
       </c>
       <c r="D68" t="n">
-        <v>2.850179147060191</v>
+        <v>1.426610694907361</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1657087368557366</v>
+        <v>2.482540707788985</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9204349152407724</v>
+        <v>-1.138806648538318</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.7210112964500029</v>
       </c>
     </row>
     <row r="69">
@@ -1942,19 +2141,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7429435252388549</v>
+        <v>-0.3720515140274198</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.146908267405378</v>
+        <v>1.407323293252315</v>
       </c>
       <c r="D69" t="n">
-        <v>1.762364219115379</v>
+        <v>0.1247256933705914</v>
       </c>
       <c r="E69" t="n">
-        <v>1.085597884938893</v>
+        <v>2.398481548067423</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7455884373613997</v>
+        <v>0.1755175823702005</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.7084536305736873</v>
       </c>
     </row>
     <row r="70">
@@ -1964,19 +2166,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3.036331682919657</v>
+        <v>1.219999714762955</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.853675488624245</v>
+        <v>2.075849844612407</v>
       </c>
       <c r="D70" t="n">
-        <v>1.791599559809583</v>
+        <v>1.826964363675988</v>
       </c>
       <c r="E70" t="n">
-        <v>1.173364605950211</v>
+        <v>2.811655413682947</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7502874870054808</v>
+        <v>0.7226000754825553</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.7701780086237646</v>
       </c>
     </row>
     <row r="71">
@@ -1986,19 +2191,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.27762526182336</v>
+        <v>0.2685617340700177</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.846198692166786</v>
+        <v>1.916014299420201</v>
       </c>
       <c r="D71" t="n">
-        <v>1.220066211369678</v>
+        <v>0.3347213564615487</v>
       </c>
       <c r="E71" t="n">
-        <v>1.547068002199737</v>
+        <v>2.181142362796922</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6584238892571777</v>
+        <v>1.031861569477216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.6759851538544565</v>
       </c>
     </row>
     <row r="72">
@@ -2008,19 +2216,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.092470102492731</v>
+        <v>0.7626176218958212</v>
       </c>
       <c r="C72" t="n">
-        <v>-3.867708509416376</v>
+        <v>3.374636536994325</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1220915521045159</v>
+        <v>-0.5789768726399908</v>
       </c>
       <c r="E72" t="n">
-        <v>3.559738344946461</v>
+        <v>1.834133659597718</v>
       </c>
       <c r="F72" t="n">
-        <v>0.914736808914428</v>
+        <v>3.651469270480995</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.8468063652142074</v>
       </c>
     </row>
     <row r="73">
@@ -2030,19 +2241,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3.705598348981645</v>
+        <v>2.543490256569481</v>
       </c>
       <c r="C73" t="n">
-        <v>-4.490862550127679</v>
+        <v>3.69106404023695</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.6508345786011948</v>
+        <v>3.027840133670964</v>
       </c>
       <c r="E73" t="n">
-        <v>2.725698992931777</v>
+        <v>0.04987679693844603</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7927529410728149</v>
+        <v>4.712436091159917</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2052,19 +2266,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3.745044472885484</v>
+        <v>1.554267067002402</v>
       </c>
       <c r="C74" t="n">
-        <v>-2.075543807863185</v>
+        <v>2.382491341771097</v>
       </c>
       <c r="D74" t="n">
-        <v>2.134361991426617</v>
+        <v>2.453542880288751</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9659367975786811</v>
+        <v>3.107489154558694</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8053803179439509</v>
+        <v>0.5455213557260904</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.8440627997860608</v>
       </c>
     </row>
     <row r="75">
@@ -2074,19 +2291,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.871156199446205</v>
+        <v>-0.1399661265845654</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8226642061787089</v>
+        <v>1.186108012815809</v>
       </c>
       <c r="D75" t="n">
-        <v>2.560765568963235</v>
+        <v>1.670811290226518</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8482761382834464</v>
+        <v>2.751468256283444</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8739169428533896</v>
+        <v>0.0525670445554026</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.7611866004872603</v>
       </c>
     </row>
     <row r="76">
@@ -2096,19 +2316,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.011543654362223</v>
+        <v>0.2206836035140252</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9313046021949455</v>
+        <v>1.615566987286201</v>
       </c>
       <c r="D76" t="n">
-        <v>2.672366247717456</v>
+        <v>1.338352793273174</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5171394983765513</v>
+        <v>2.860009626251677</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8918547235437025</v>
+        <v>-1.583327366061115</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.7774016835589151</v>
       </c>
     </row>
     <row r="77">
@@ -2118,19 +2341,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.736207309485154</v>
+        <v>-0.4769948182431654</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.584287211314497</v>
+        <v>1.745376667002049</v>
       </c>
       <c r="D77" t="n">
-        <v>1.762507876497283</v>
+        <v>0.4313868000102782</v>
       </c>
       <c r="E77" t="n">
-        <v>1.27200772905662</v>
+        <v>2.12011424587704</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7456115276744687</v>
+        <v>0.6557597775984629</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.6668681140948498</v>
       </c>
     </row>
     <row r="78">
@@ -2140,19 +2366,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.894474151095204</v>
+        <v>0.5402665610092713</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.673483949526989</v>
+        <v>1.854472129673667</v>
       </c>
       <c r="D78" t="n">
-        <v>1.560472310888082</v>
+        <v>0.9198460693361025</v>
       </c>
       <c r="E78" t="n">
-        <v>1.22605668469724</v>
+        <v>2.452561512835197</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7131379826387567</v>
+        <v>0.6623722839731091</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.7165326802620989</v>
       </c>
     </row>
     <row r="79">
@@ -2162,19 +2391,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.439691721669145</v>
+        <v>-1.994061602681926</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.47217355078788</v>
+        <v>1.4561338080764</v>
       </c>
       <c r="D79" t="n">
-        <v>1.273663409670169</v>
+        <v>0.3519799136799996</v>
       </c>
       <c r="E79" t="n">
-        <v>0.08525776919637312</v>
+        <v>-0.4608354850407863</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6670386647178785</v>
+        <v>0.431455337896204</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.6049435802986112</v>
       </c>
     </row>
     <row r="80">
@@ -2184,19 +2416,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.1643757715452476</v>
+        <v>-0.3375314115751923</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.89234987021767</v>
+        <v>2.108127469582552</v>
       </c>
       <c r="D80" t="n">
-        <v>1.210214481049945</v>
+        <v>-0.8191454037635857</v>
       </c>
       <c r="E80" t="n">
-        <v>1.004752836907743</v>
+        <v>2.075252011812908</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6568404026702845</v>
+        <v>0.1486470370548788</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.6866229831005926</v>
       </c>
     </row>
     <row r="81">
@@ -2206,19 +2441,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3.073875442608585</v>
+        <v>0.9487057220002256</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.28408703041189</v>
+        <v>1.793710333539567</v>
       </c>
       <c r="D81" t="n">
-        <v>2.489365025516056</v>
+        <v>2.198615678811487</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1286140804379066</v>
+        <v>2.969389509437928</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8624406032484547</v>
+        <v>-0.5784428976725715</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.8121079137427981</v>
       </c>
     </row>
     <row r="82">
@@ -2228,19 +2466,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.391602924069187</v>
+        <v>0.3792691866557987</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.126449819645205</v>
+        <v>1.649710126985179</v>
       </c>
       <c r="D82" t="n">
-        <v>1.435112260634117</v>
+        <v>2.141939040453661</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.650112491409349</v>
+        <v>-0.2188362564572196</v>
       </c>
       <c r="F82" t="n">
-        <v>0.6929886330659415</v>
+        <v>-2.213222551005276</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.8050035501851058</v>
       </c>
     </row>
     <row r="83">
@@ -2250,19 +2491,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.3282419540653854</v>
+        <v>-0.4728217899755202</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.878371981994969</v>
+        <v>2.026641085124799</v>
       </c>
       <c r="D83" t="n">
-        <v>1.103081527051819</v>
+        <v>1.73119162536748</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.350731652089521</v>
+        <v>-0.8067544098212359</v>
       </c>
       <c r="F83" t="n">
-        <v>0.63962072753053</v>
+        <v>-0.4979848705483108</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.7535167462442788</v>
       </c>
     </row>
     <row r="84">
@@ -2272,19 +2516,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.152429474808053</v>
+        <v>1.569844670853233</v>
       </c>
       <c r="C84" t="n">
-        <v>-2.996339265691621</v>
+        <v>3.130494278007014</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5512713889690511</v>
+        <v>0.04313514750004509</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9840067066319583</v>
+        <v>2.211700037762383</v>
       </c>
       <c r="F84" t="n">
-        <v>0.6375697175070046</v>
+        <v>0.6134867931040531</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.8147013913534771</v>
       </c>
     </row>
     <row r="85">
@@ -2294,19 +2541,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.933645193288293</v>
+        <v>0.8245674864149618</v>
       </c>
       <c r="C85" t="n">
-        <v>-2.099876518330802</v>
+        <v>2.297626047899135</v>
       </c>
       <c r="D85" t="n">
-        <v>1.314316568909814</v>
+        <v>0.5112625719040825</v>
       </c>
       <c r="E85" t="n">
-        <v>1.164950726828277</v>
+        <v>2.529980838513743</v>
       </c>
       <c r="F85" t="n">
-        <v>0.6735729211664</v>
+        <v>0.5529807811981422</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.7280984159589723</v>
       </c>
     </row>
     <row r="86">
@@ -2316,19 +2566,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4.715428532332534</v>
+        <v>3.40419183581819</v>
       </c>
       <c r="C86" t="n">
-        <v>-2.927320758078244</v>
+        <v>3.01699128354548</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4997827217294047</v>
+        <v>1.556485113058522</v>
       </c>
       <c r="E86" t="n">
-        <v>1.565610871771081</v>
+        <v>3.186828367929331</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8318067580495626</v>
+        <v>1.301306185074477</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.8262253997809225</v>
       </c>
     </row>
     <row r="87">
@@ -2338,19 +2591,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-1.265767594382391</v>
+        <v>-1.052900721182825</v>
       </c>
       <c r="C87" t="n">
-        <v>-1.790068818395849</v>
+        <v>2.172184607215459</v>
       </c>
       <c r="D87" t="n">
-        <v>1.021095756696391</v>
+        <v>-1.99949894008007</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.1024833938394327</v>
+        <v>1.405187804797811</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6264430050939052</v>
+        <v>-1.130159836037533</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.6946478291320304</v>
       </c>
     </row>
     <row r="88">
@@ -2360,19 +2616,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.1172208193228845</v>
+        <v>0.2719617466086407</v>
       </c>
       <c r="C88" t="n">
-        <v>-2.313570666032542</v>
+        <v>2.465992852498025</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3300007243006164</v>
+        <v>-1.423761890210562</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6927927818544081</v>
+        <v>1.562136519328671</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5153620397658929</v>
+        <v>0.04262778152934545</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.7314550612108526</v>
       </c>
     </row>
     <row r="89">
@@ -2382,19 +2641,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-1.838567936931126</v>
+        <v>-1.916164933331634</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.882669540313854</v>
+        <v>1.721021096454561</v>
       </c>
       <c r="D89" t="n">
-        <v>0.6842793664450749</v>
+        <v>-0.4479843900347247</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6233686544013575</v>
+        <v>-0.5699898752521692</v>
       </c>
       <c r="F89" t="n">
-        <v>0.572305892231565</v>
+        <v>0.9880786234918055</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.638127699718705</v>
       </c>
     </row>
     <row r="90">
@@ -2404,19 +2666,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.967082091421543</v>
+        <v>1.082402039873274</v>
       </c>
       <c r="C90" t="n">
-        <v>-2.389383945358097</v>
+        <v>2.275713194374747</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3220380550562172</v>
+        <v>2.337477128146078</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.3144412415614247</v>
+        <v>-0.4755468961632163</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6235231547056608</v>
+        <v>0.8892849058317603</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.8295140664153087</v>
       </c>
     </row>
     <row r="91">
@@ -2426,19 +2691,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.9405982695952468</v>
+        <v>-1.253107900808242</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.5221363735236013</v>
+        <v>1.026392095548847</v>
       </c>
       <c r="D91" t="n">
-        <v>3.26284177802724</v>
+        <v>1.709161965297633</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2598248194096635</v>
+        <v>2.481081222334391</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9867629327403485</v>
+        <v>-0.6307007609402238</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.7507553489786106</v>
       </c>
     </row>
     <row r="92">
@@ -2448,19 +2716,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2.092628900478926</v>
+        <v>1.460716358517828</v>
       </c>
       <c r="C92" t="n">
-        <v>-2.642928383626745</v>
+        <v>2.425443614422738</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.1643021282428402</v>
+        <v>2.156384737629269</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.1155861251568424</v>
+        <v>-0.6596316404864314</v>
       </c>
       <c r="F92" t="n">
-        <v>0.6330377273190512</v>
+        <v>1.245697813585662</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.8068143048020595</v>
       </c>
     </row>
     <row r="93">
@@ -2470,19 +2741,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3.084154141652329</v>
+        <v>1.941638102228046</v>
       </c>
       <c r="C93" t="n">
-        <v>-2.696647460029953</v>
+        <v>2.356197902845915</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.09894899774449423</v>
+        <v>3.464902463011348</v>
       </c>
       <c r="E93" t="n">
-        <v>0.08172978685871347</v>
+        <v>-0.8518574070514775</v>
       </c>
       <c r="F93" t="n">
-        <v>0.708180528446253</v>
+        <v>1.925371240111273</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.9708357766492006</v>
       </c>
     </row>
     <row r="94">
@@ -2492,19 +2766,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-2.570936930083669</v>
+        <v>-2.199998096684334</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.472466567790199</v>
+        <v>1.426039143036312</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4551502338205633</v>
+        <v>-0.8836918123425634</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.4237476399713649</v>
+        <v>-1.281508673609691</v>
       </c>
       <c r="F94" t="n">
-        <v>0.535477548742438</v>
+        <v>-0.03306517959159352</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.6011734297386784</v>
       </c>
     </row>
     <row r="95">
@@ -2514,19 +2791,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.284979709087783</v>
+        <v>2.447763679560754</v>
       </c>
       <c r="C95" t="n">
-        <v>2.511081412547276</v>
+        <v>-2.288447224497336</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.7777448555776301</v>
+        <v>-0.4233503514377389</v>
       </c>
       <c r="E95" t="n">
-        <v>0.2847132985678413</v>
+        <v>1.968228901208651</v>
       </c>
       <c r="F95" t="n">
-        <v>0.8925394350711079</v>
+        <v>-0.9065646888421393</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.6751621777226184</v>
       </c>
     </row>
     <row r="96">
@@ -2536,19 +2816,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.9237323690284843</v>
+        <v>-0.654521650963783</v>
       </c>
       <c r="C96" t="n">
-        <v>-2.432706763882072</v>
+        <v>2.384503149155707</v>
       </c>
       <c r="D96" t="n">
-        <v>0.05742994940020209</v>
+        <v>-0.2383492323242572</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.5719594047518956</v>
+        <v>-1.007672971921354</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4715512418627715</v>
+        <v>0.1079158810166556</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.7212463265306178</v>
       </c>
     </row>
     <row r="97">
@@ -2558,19 +2841,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.989463893239453</v>
+        <v>2.332160485036751</v>
       </c>
       <c r="C97" t="n">
-        <v>-2.687358159191414</v>
+        <v>2.473134028806172</v>
       </c>
       <c r="D97" t="n">
-        <v>-1.24682270073916</v>
+        <v>0.4094588163406827</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1438945825467666</v>
+        <v>-0.200123772071465</v>
       </c>
       <c r="F97" t="n">
-        <v>0.62521936092718</v>
+        <v>1.003191728397639</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.7323496818959766</v>
       </c>
     </row>
     <row r="98">
@@ -2580,19 +2866,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8725892451013545</v>
+        <v>1.988345865894807</v>
       </c>
       <c r="C98" t="n">
-        <v>-3.093980568815844</v>
+        <v>3.019640999022974</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.636185564490966</v>
+        <v>-0.6203146197765697</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.10074742751748</v>
+        <v>-1.038798765810607</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5405769473162717</v>
+        <v>-0.1971109931295074</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.8008140943433474</v>
       </c>
     </row>
     <row r="99">
@@ -2602,19 +2891,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3670336561595248</v>
+        <v>0.7594149389704883</v>
       </c>
       <c r="C99" t="n">
-        <v>-3.197372112518885</v>
+        <v>2.992397548890819</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.73812679321852</v>
+        <v>0.2409102764578254</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.3861396179946792</v>
+        <v>-1.154868580499819</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5022633860461179</v>
+        <v>0.7643330743166016</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.7974011336530248</v>
       </c>
     </row>
     <row r="100">
@@ -2624,19 +2916,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6160652749145055</v>
+        <v>1.153967232584046</v>
       </c>
       <c r="C100" t="n">
-        <v>-2.42449706171116</v>
+        <v>2.478534793722573</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.6510925612359466</v>
+        <v>-0.3913486908890101</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.8231661594626066</v>
+        <v>-0.3289300934557006</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5211362625251322</v>
+        <v>-0.3771404463857008</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.7330262701499582</v>
       </c>
     </row>
     <row r="101">
@@ -2646,19 +2941,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.04038853156291139</v>
+        <v>0.8586821589576104</v>
       </c>
       <c r="C101" t="n">
-        <v>-2.999890878298487</v>
+        <v>3.039839679977914</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.7609780050244566</v>
+        <v>-0.9552481190883473</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.8460506226987625</v>
+        <v>-0.5129381930982461</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4775085652735411</v>
+        <v>-0.3815269077533109</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.8033445118844873</v>
       </c>
     </row>
     <row r="102">
@@ -2668,19 +2966,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.3009293547616623</v>
+        <v>0.4488850664819425</v>
       </c>
       <c r="C102" t="n">
-        <v>-3.844353800151849</v>
+        <v>3.200350313929536</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.370145024621824</v>
+        <v>-0.9513282048811229</v>
       </c>
       <c r="E102" t="n">
-        <v>2.058255897092977</v>
+        <v>-0.6683363086725812</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6951348967947746</v>
+        <v>3.097333830586858</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.8234527023448822</v>
       </c>
     </row>
     <row r="103">
@@ -2690,19 +2991,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-1.374066847992175</v>
+        <v>-0.7653980385291805</v>
       </c>
       <c r="C103" t="n">
-        <v>-4.425495612905637</v>
+        <v>3.88084071187345</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.7101735641601755</v>
+        <v>-0.6599240271314982</v>
       </c>
       <c r="E103" t="n">
-        <v>1.105498797802428</v>
+        <v>-1.545199158827134</v>
       </c>
       <c r="F103" t="n">
-        <v>0.5557877595112918</v>
+        <v>2.488894407886642</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.9087020730030925</v>
       </c>
     </row>
     <row r="104">
@@ -2712,19 +3016,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-0.3544708743658319</v>
+        <v>-0.5474484423397543</v>
       </c>
       <c r="C104" t="n">
-        <v>-1.972999745344633</v>
+        <v>2.059802422670083</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5125206606133792</v>
+        <v>0.8400742437849846</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.390577281576049</v>
+        <v>-1.203597389139334</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5446988021022459</v>
+        <v>-0.5376035106742799</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.6805689963746022</v>
       </c>
     </row>
     <row r="105">
@@ -2734,19 +3041,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-3.611888463805845</v>
+        <v>-3.42174044927612</v>
       </c>
       <c r="C105" t="n">
-        <v>-1.158418524093345</v>
+        <v>1.250643029789915</v>
       </c>
       <c r="D105" t="n">
-        <v>1.251614665824742</v>
+        <v>-1.272465629989063</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.4896488581579503</v>
+        <v>-1.025925262945062</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6634947298958765</v>
+        <v>-0.4998845810261304</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.5792004403837515</v>
       </c>
     </row>
     <row r="106">
@@ -2756,19 +3066,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.412304344207625</v>
+        <v>1.340306844867556</v>
       </c>
       <c r="C106" t="n">
-        <v>-2.412549697018496</v>
+        <v>2.30356013121415</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3816881753645561</v>
+        <v>2.836637788115613</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.4553232739853179</v>
+        <v>-0.5213333996202379</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6572643504002024</v>
+        <v>0.8959074613888889</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.8920833878301081</v>
       </c>
     </row>
     <row r="107">
@@ -2778,19 +3091,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.518313469767968</v>
+        <v>1.307329314883321</v>
       </c>
       <c r="C107" t="n">
-        <v>-2.447841766956383</v>
+        <v>2.36346327197656</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5907842791285374</v>
+        <v>2.777665863383956</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.1744022873879949</v>
+        <v>-0.09944444666494019</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6652982584732056</v>
+        <v>0.9891533932482686</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.8846913122742949</v>
       </c>
     </row>
     <row r="108">
@@ -2800,19 +3116,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-2.287427825976956</v>
+        <v>-2.0551907988522</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.107211390967485</v>
+        <v>1.068704209698058</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4669853192864558</v>
+        <v>-0.3593647085555881</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.7273135376168756</v>
+        <v>-1.52864263906136</v>
       </c>
       <c r="F108" t="n">
-        <v>0.5373798236202265</v>
+        <v>-0.1734147384078129</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.5564078044288699</v>
       </c>
     </row>
     <row r="109">
@@ -2822,19 +3141,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.626583349923795</v>
+        <v>1.834075868334332</v>
       </c>
       <c r="C109" t="n">
-        <v>-2.96405012569673</v>
+        <v>2.639457761836455</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.121000504252525</v>
+        <v>0.7921715383228389</v>
       </c>
       <c r="E109" t="n">
-        <v>0.2461595218515032</v>
+        <v>-0.727963456230909</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5977184367277821</v>
+        <v>1.468000730253405</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.753186116339721</v>
       </c>
     </row>
     <row r="110">
@@ -2844,19 +3166,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.02008525269803771</v>
+        <v>0.02911617105192732</v>
       </c>
       <c r="C110" t="n">
-        <v>-2.670456672971286</v>
+        <v>2.488183436920834</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.1578205727030041</v>
+        <v>0.3741910457712238</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.05391538529520693</v>
+        <v>-0.8689108561691844</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4729255558296746</v>
+        <v>0.8736033054561643</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.7342350171989138</v>
       </c>
     </row>
     <row r="111">
@@ -2866,19 +3191,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.568335251812549</v>
+        <v>-0.384613035968722</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.715551251727707</v>
+        <v>1.951768754281667</v>
       </c>
       <c r="D111" t="n">
-        <v>1.627695206359269</v>
+        <v>-0.07902682912359367</v>
       </c>
       <c r="E111" t="n">
-        <v>1.015816764011211</v>
+        <v>2.202148056909825</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7239428412631888</v>
+        <v>0.2341148452439788</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.6791232114920023</v>
       </c>
     </row>
     <row r="112">
@@ -2888,19 +3216,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.5642337205745971</v>
+        <v>-1.052655286240478</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.316607983800496</v>
+        <v>1.796314725267744</v>
       </c>
       <c r="D112" t="n">
-        <v>1.743033240005803</v>
+        <v>-1.016880104844482</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.1088944564556278</v>
+        <v>1.902545578885472</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7424813338234342</v>
+        <v>-1.238461517795595</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.6475602126392265</v>
       </c>
     </row>
     <row r="113">
@@ -2910,19 +3241,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.612272244114549</v>
+        <v>2.991838497698817</v>
       </c>
       <c r="C113" t="n">
-        <v>2.799591102402836</v>
+        <v>-2.550353478515976</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.142849575810555</v>
+        <v>-0.6412057424268172</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1582066978971005</v>
+        <v>2.083066044577584</v>
       </c>
       <c r="F113" t="n">
-        <v>0.9246854244831948</v>
+        <v>-1.147283049790908</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.7282424741887771</v>
       </c>
     </row>
     <row r="114">
@@ -2932,19 +3266,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.757973208919863</v>
+        <v>1.023740781164776</v>
       </c>
       <c r="C114" t="n">
-        <v>-2.485554707796243</v>
+        <v>2.260632406047243</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00350199000334293</v>
+        <v>2.550529438188161</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.4898153904926215</v>
+        <v>-1.213271138202011</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6076758252386268</v>
+        <v>1.123579478174012</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.8562199740202915</v>
       </c>
     </row>
     <row r="115">
@@ -2954,19 +3291,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.83628310467928</v>
+        <v>0.8948740480581974</v>
       </c>
       <c r="C115" t="n">
-        <v>-2.320082720361562</v>
+        <v>2.133562866702775</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3679872403175844</v>
+        <v>2.192624974578376</v>
       </c>
       <c r="E115" t="n">
-        <v>0.2647373364198807</v>
+        <v>-0.2375887887452175</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6136105454847579</v>
+        <v>1.365631070359592</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.8113569845756531</v>
       </c>
     </row>
     <row r="116">
@@ -2976,19 +3316,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-3.094442042941208</v>
+        <v>-2.765661787087752</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.8338551306692454</v>
+        <v>1.161952764697944</v>
       </c>
       <c r="D116" t="n">
-        <v>1.398500437703607</v>
+        <v>-2.739268592409057</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3190408778381391</v>
+        <v>1.11918386546951</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6871039479750344</v>
+        <v>-0.9911979242535386</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.5680896454255198</v>
       </c>
     </row>
     <row r="117">
@@ -2998,19 +3341,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.17072214222851</v>
+        <v>-1.61711439273317</v>
       </c>
       <c r="C117" t="n">
-        <v>-2.028077509095643</v>
+        <v>1.887184911014305</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.02594791136429362</v>
+        <v>-0.7818209974832442</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.4259918930239834</v>
+        <v>-1.574002160571528</v>
       </c>
       <c r="F117" t="n">
-        <v>0.458149766195094</v>
+        <v>0.2804512875885946</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6589441001560751</v>
       </c>
     </row>
     <row r="118">
@@ -3020,19 +3366,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.8146890703616763</v>
+        <v>-0.8831658024887786</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.244580918161565</v>
+        <v>1.587529889110213</v>
       </c>
       <c r="D118" t="n">
-        <v>1.14489867226429</v>
+        <v>-1.691342110282309</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4392153987280918</v>
+        <v>1.867744714290959</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6463420735679341</v>
+        <v>-0.7431080950432013</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6291664255992963</v>
       </c>
     </row>
     <row r="119">
@@ -3042,19 +3391,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.3249196808717336</v>
+        <v>1.687996809722287</v>
       </c>
       <c r="C119" t="n">
-        <v>-5.49944432661073</v>
+        <v>4.609612809472467</v>
       </c>
       <c r="D119" t="n">
-        <v>-2.564264249443796</v>
+        <v>-1.396492782571368</v>
       </c>
       <c r="E119" t="n">
-        <v>2.533468059868231</v>
+        <v>-0.9914278449979967</v>
       </c>
       <c r="F119" t="n">
-        <v>0.7646378735076567</v>
+        <v>4.078818623154991</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3064,19 +3416,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.1869266136253336</v>
+        <v>-0.1119360509710511</v>
       </c>
       <c r="C120" t="n">
-        <v>-1.72267651210624</v>
+        <v>1.978471614373649</v>
       </c>
       <c r="D120" t="n">
-        <v>0.6698290421679168</v>
+        <v>-1.698991753863731</v>
       </c>
       <c r="E120" t="n">
-        <v>0.7115818402334427</v>
+        <v>1.9600554422534</v>
       </c>
       <c r="F120" t="n">
-        <v>0.5699832652486376</v>
+        <v>-0.3305295823912547</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.67038016748981</v>
       </c>
     </row>
     <row r="121">
@@ -3086,19 +3441,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-1.85751415156914</v>
+        <v>-1.068922733561486</v>
       </c>
       <c r="C121" t="n">
-        <v>-1.46919433137313</v>
+        <v>1.82219431818382</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4853921496558878</v>
+        <v>-3.059115402608133</v>
       </c>
       <c r="E121" t="n">
-        <v>0.07142550117139783</v>
+        <v>1.403759140261172</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5403383870452557</v>
+        <v>-1.223223474257248</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.6508023142407365</v>
       </c>
     </row>
     <row r="122">
@@ -3108,19 +3466,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3.162393074465823</v>
+        <v>3.752056587077</v>
       </c>
       <c r="C122" t="n">
-        <v>-2.42879318035731</v>
+        <v>2.366823200873719</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.819048214450467</v>
+        <v>0.6047935445452619</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.8352537646165008</v>
+        <v>-0.18311016023764</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7141098707611813</v>
+        <v>0.02823527753065581</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.8024098501045118</v>
       </c>
     </row>
     <row r="123">
@@ -3130,19 +3491,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-1.69137917575485</v>
+        <v>0.1214973850589617</v>
       </c>
       <c r="C123" t="n">
-        <v>-3.046869892793073</v>
+        <v>2.916726623606207</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.709189540419653</v>
+        <v>-1.921573625587333</v>
       </c>
       <c r="E123" t="n">
-        <v>-1.447734266538161</v>
+        <v>-2.238309599845313</v>
       </c>
       <c r="F123" t="n">
-        <v>0.3462664435142515</v>
+        <v>-0.4749119464220231</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.7879213543980511</v>
       </c>
     </row>
     <row r="124">
@@ -3152,19 +3516,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.860555662726946</v>
+        <v>2.366373722226914</v>
       </c>
       <c r="C124" t="n">
-        <v>2.572513797044856</v>
+        <v>-2.385974950535407</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.129086933050164</v>
+        <v>-0.7969234508026781</v>
       </c>
       <c r="E124" t="n">
-        <v>0.09846601584310688</v>
+        <v>1.547898938964074</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8993842824057231</v>
+        <v>-1.007095288839621</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.6672217200491078</v>
       </c>
     </row>
     <row r="125">
@@ -3174,19 +3541,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3.043832811435978</v>
+        <v>3.24550453435788</v>
       </c>
       <c r="C125" t="n">
-        <v>-2.054541112179094</v>
+        <v>2.012818280460776</v>
       </c>
       <c r="D125" t="n">
-        <v>-1.261376331873786</v>
+        <v>0.811764466867162</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.4200676642560363</v>
+        <v>0.247795551535914</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7051247739663712</v>
+        <v>0.2207420886628516</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.7529902992679407</v>
       </c>
     </row>
     <row r="126">
@@ -3196,19 +3566,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-0.06813021593373952</v>
+        <v>1.2117820460117</v>
       </c>
       <c r="C126" t="n">
-        <v>-2.78504312624066</v>
+        <v>2.751664079324688</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.436000481841276</v>
+        <v>-1.348186610475667</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.9590837729682981</v>
+        <v>-0.9217512925040259</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4692844653483959</v>
+        <v>-0.3875876110812295</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7672429171096496</v>
       </c>
     </row>
     <row r="127">
@@ -3218,19 +3591,22 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.8667294561955123</v>
+        <v>1.101003856823175</v>
       </c>
       <c r="C127" t="n">
-        <v>-2.932118757654166</v>
+        <v>2.921539265057804</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.4395625108529136</v>
+        <v>0.24980870302234</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.7277644491706599</v>
+        <v>-0.51217632613539</v>
       </c>
       <c r="F127" t="n">
-        <v>0.5401328628551662</v>
+        <v>0.04300223618765148</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.7885242646759798</v>
       </c>
     </row>
     <row r="128">
@@ -3240,19 +3616,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-0.2212105731050684</v>
+        <v>1.245521589322489</v>
       </c>
       <c r="C128" t="n">
-        <v>-3.106975434091657</v>
+        <v>2.700660948967684</v>
       </c>
       <c r="D128" t="n">
-        <v>-2.09391833801232</v>
+        <v>-1.444461904657844</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3280903199514703</v>
+        <v>-1.27683663603304</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4576832611049282</v>
+        <v>1.292261512506287</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.760853429796279</v>
       </c>
     </row>
     <row r="129">
@@ -3262,19 +3641,22 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5734693285889111</v>
+        <v>2.036399368428442</v>
       </c>
       <c r="C129" t="n">
-        <v>-3.320623003423421</v>
+        <v>3.257029129682842</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.870709170254469</v>
+        <v>-1.51090499909623</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.812942210374507</v>
+        <v>-0.686765378019133</v>
       </c>
       <c r="F129" t="n">
-        <v>0.5179081261241051</v>
+        <v>-0.2132739220129475</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.8305532189535241</v>
       </c>
     </row>
     <row r="130">
@@ -3284,19 +3666,22 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.4602812204788576</v>
+        <v>0.3440007170018752</v>
       </c>
       <c r="C130" t="n">
-        <v>-2.61217302905935</v>
+        <v>2.849715028456413</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.1112349728812696</v>
+        <v>-2.563406765899339</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2721779570806881</v>
+        <v>1.480123613669707</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4444414212074977</v>
+        <v>-0.6034063358777269</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.7795263846371498</v>
       </c>
     </row>
     <row r="131">
@@ -3306,19 +3691,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5359752687405257</v>
+        <v>2.0761156025256</v>
       </c>
       <c r="C131" t="n">
-        <v>-3.185406715854489</v>
+        <v>3.048668946824336</v>
       </c>
       <c r="D131" t="n">
-        <v>-2.116674896553371</v>
+        <v>-1.230472131478751</v>
       </c>
       <c r="E131" t="n">
-        <v>-1.013229550173015</v>
+        <v>-1.243865900851402</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5150666365022126</v>
+        <v>-0.1091575686419311</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.8044506104338647</v>
       </c>
     </row>
     <row r="132">
@@ -3328,19 +3716,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4.868821418263976</v>
+        <v>5.777362247131088</v>
       </c>
       <c r="C132" t="n">
-        <v>-4.016242946678913</v>
+        <v>3.886921075383016</v>
       </c>
       <c r="D132" t="n">
-        <v>-2.845422237559242</v>
+        <v>1.065727267327689</v>
       </c>
       <c r="E132" t="n">
-        <v>-1.340938535067367</v>
+        <v>-0.4962132492313227</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8434316473042559</v>
+        <v>0.1628604557791031</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3350,19 +3741,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5282783558540581</v>
+        <v>1.439036245298859</v>
       </c>
       <c r="C133" t="n">
-        <v>-2.343833099918592</v>
+        <v>2.355386536234587</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.161257142749651</v>
+        <v>-0.7519582951517005</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.9400935666908858</v>
+        <v>-0.6070103233222104</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5144833254877228</v>
+        <v>-0.4338212734740159</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.7175987027952587</v>
       </c>
     </row>
     <row r="134">
@@ -3372,19 +3766,22 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6573566343683632</v>
+        <v>0.324775888647767</v>
       </c>
       <c r="C134" t="n">
-        <v>-2.092105423259358</v>
+        <v>2.099437055588153</v>
       </c>
       <c r="D134" t="n">
-        <v>0.256652865980201</v>
+        <v>1.15105330077468</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.8310923326401757</v>
+        <v>-0.7205247329692527</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5242655307301869</v>
+        <v>0.0317882966208609</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.6855342795332532</v>
       </c>
     </row>
     <row r="135">
@@ -3394,19 +3791,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3923990480813608</v>
+        <v>0.1459082236803943</v>
       </c>
       <c r="C135" t="n">
-        <v>2.294747739116143</v>
+        <v>-2.172756773702072</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1769129605768491</v>
+        <v>0.2564672247861362</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.01412501929469576</v>
+        <v>0.58087230465972</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8684353573915103</v>
+        <v>-0.5853238006912916</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5686614232629905</v>
       </c>
     </row>
     <row r="136">
@@ -3416,19 +3816,22 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3967773856940759</v>
+        <v>1.897121282314497</v>
       </c>
       <c r="C136" t="n">
-        <v>-3.190549330577665</v>
+        <v>3.045826906867114</v>
       </c>
       <c r="D136" t="n">
-        <v>-2.049764596580563</v>
+        <v>-1.080002208836223</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.142460725990391</v>
+        <v>-1.466861079941587</v>
       </c>
       <c r="F136" t="n">
-        <v>0.5045175164105158</v>
+        <v>-0.1256896735781083</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.8040945699688253</v>
       </c>
     </row>
     <row r="137">
@@ -3438,19 +3841,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4.466954486095105</v>
+        <v>3.65128918618618</v>
       </c>
       <c r="C137" t="n">
-        <v>2.772922230099908</v>
+        <v>-2.530792806142827</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.3613046278859822</v>
+        <v>1.57363004172158</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3484389482483349</v>
+        <v>2.527072547756628</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9217139565678142</v>
+        <v>-0.5796434660403298</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.7925789163154541</v>
       </c>
     </row>
     <row r="138">
@@ -3460,19 +3866,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.759752247077424</v>
+        <v>0.9766159035087475</v>
       </c>
       <c r="C138" t="n">
-        <v>2.191947319774002</v>
+        <v>-2.021090521118143</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3645177515441511</v>
+        <v>1.704627154058739</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.5669990897510353</v>
+        <v>0.479837444506437</v>
       </c>
       <c r="F138" t="n">
-        <v>0.8569812492352644</v>
+        <v>-0.7330207663258855</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.750186914635289</v>
       </c>
     </row>
     <row r="139">
@@ -3482,19 +3891,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3.610813181974859</v>
+        <v>3.678745921419497</v>
       </c>
       <c r="C139" t="n">
-        <v>2.599073334185725</v>
+        <v>-2.416337482644825</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.262441850872404</v>
+        <v>0.5473178961900461</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.1440506053088907</v>
+        <v>1.657558060163352</v>
       </c>
       <c r="F139" t="n">
-        <v>0.9023435681064832</v>
+        <v>-0.9025091467437731</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.7952576134313485</v>
       </c>
     </row>
     <row r="140">
@@ -3504,19 +3916,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.029607059546068</v>
+        <v>0.03905421316625794</v>
       </c>
       <c r="C140" t="n">
-        <v>1.849235847767818</v>
+        <v>-1.722927355062684</v>
       </c>
       <c r="D140" t="n">
-        <v>0.8382491459832028</v>
+        <v>1.820665233936148</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.393587434572495</v>
+        <v>0.224689992770646</v>
       </c>
       <c r="F140" t="n">
-        <v>0.8187960522111127</v>
+        <v>-0.4223592077687806</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.7647321793134968</v>
       </c>
     </row>
     <row r="141">
@@ -3526,19 +3941,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>6.705044799072948</v>
+        <v>5.671338999437356</v>
       </c>
       <c r="C141" t="n">
-        <v>2.83517446060035</v>
+        <v>-2.406067413772823</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.5162309809313866</v>
+        <v>1.613200997802526</v>
       </c>
       <c r="E141" t="n">
-        <v>0.6999708482849797</v>
+        <v>4.350049863009565</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9825899486763504</v>
+        <v>-0.904618900346049</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -3548,19 +3966,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2.527872834945208</v>
+        <v>1.446149594398118</v>
       </c>
       <c r="C142" t="n">
-        <v>2.369398243763741</v>
+        <v>-2.165920309593937</v>
       </c>
       <c r="D142" t="n">
-        <v>0.494407454870707</v>
+        <v>2.26471822172839</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.5548649694881509</v>
+        <v>0.7938960500722622</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8767529786582693</v>
+        <v>-0.7304969875638471</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.8203938056124732</v>
       </c>
     </row>
     <row r="143">
@@ -3570,19 +3991,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3.193335256101532</v>
+        <v>3.062697081747177</v>
       </c>
       <c r="C143" t="n">
-        <v>2.387332859721196</v>
+        <v>-2.180592423313492</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.7746324909663875</v>
+        <v>0.3686216655433153</v>
       </c>
       <c r="E143" t="n">
-        <v>0.2163359828988708</v>
+        <v>2.011251968353633</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8787512684729608</v>
+        <v>-0.74408274202388</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.735155484170255</v>
       </c>
     </row>
     <row r="144">
@@ -3592,19 +4016,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2.320827921740788</v>
+        <v>1.383537256714317</v>
       </c>
       <c r="C144" t="n">
-        <v>2.130831713149962</v>
+        <v>-1.925420661894431</v>
       </c>
       <c r="D144" t="n">
-        <v>0.4402586561738887</v>
+        <v>1.827809901416733</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.3803596578165541</v>
+        <v>0.9674704126720158</v>
       </c>
       <c r="F144" t="n">
-        <v>0.8501716975545801</v>
+        <v>-0.6904802708448441</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.7656277566933765</v>
       </c>
     </row>
     <row r="145">
@@ -3614,19 +4041,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2.391003312717928</v>
+        <v>1.582596862217146</v>
       </c>
       <c r="C145" t="n">
-        <v>2.181556563040062</v>
+        <v>-1.97614270879136</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2647071634972191</v>
+        <v>1.607235337773207</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.3233712843418087</v>
+        <v>1.07273984492745</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8558235024846439</v>
+        <v>-0.7170160647272568</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.7379789416417593</v>
       </c>
     </row>
     <row r="146">
@@ -3636,19 +4066,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4.672241003302276</v>
+        <v>3.13769726044028</v>
       </c>
       <c r="C146" t="n">
-        <v>3.305489328958255</v>
+        <v>-3.10592208778765</v>
       </c>
       <c r="D146" t="n">
-        <v>0.310094370417473</v>
+        <v>2.853006343956327</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4357358464920209</v>
+        <v>2.329302140659399</v>
       </c>
       <c r="F146" t="n">
-        <v>0.9810530253169335</v>
+        <v>-0.2192251607905306</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.8941351709805596</v>
       </c>
     </row>
     <row r="147">
@@ -3658,19 +4091,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-1.064640378167739</v>
+        <v>-0.8147959198728887</v>
       </c>
       <c r="C147" t="n">
-        <v>1.836684902166523</v>
+        <v>-1.733210499517544</v>
       </c>
       <c r="D147" t="n">
-        <v>0.07923179141070701</v>
+        <v>-0.7034989050723955</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.2297033441510425</v>
+        <v>-0.03194325595178839</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8173976154216486</v>
+        <v>-0.7664795301984579</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.4483305676019988</v>
       </c>
     </row>
     <row r="148">
@@ -3680,19 +4116,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2.540274000460837</v>
+        <v>1.462957511999851</v>
       </c>
       <c r="C148" t="n">
-        <v>2.22024475676963</v>
+        <v>-1.992649195986101</v>
       </c>
       <c r="D148" t="n">
-        <v>0.5871950152945987</v>
+        <v>1.872200167680376</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.1696983890937031</v>
+        <v>1.330663828103749</v>
       </c>
       <c r="F148" t="n">
-        <v>0.860134173182138</v>
+        <v>-0.6310602352140169</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.7711920350115196</v>
       </c>
     </row>
     <row r="149">
@@ -3702,19 +4141,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3.992613529635443</v>
+        <v>2.631508535451588</v>
       </c>
       <c r="C149" t="n">
-        <v>2.99582075077735</v>
+        <v>-2.807857666118066</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2916188268366853</v>
+        <v>2.786344696685878</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.03881487592186738</v>
+        <v>1.614546392485086</v>
       </c>
       <c r="F149" t="n">
-        <v>0.9465494949833665</v>
+        <v>-0.4154410520778076</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.8857791959035988</v>
       </c>
     </row>
     <row r="150">
@@ -3724,19 +4166,22 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.8538953124063497</v>
+        <v>0.3185716479926297</v>
       </c>
       <c r="C150" t="n">
-        <v>1.977640443969452</v>
+        <v>-1.819052216286126</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3978389181292276</v>
+        <v>1.022019610986927</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.4582048006031265</v>
+        <v>0.345360654227024</v>
       </c>
       <c r="F150" t="n">
-        <v>0.8331029990316078</v>
+        <v>-0.7311096003991759</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.6646226981659191</v>
       </c>
     </row>
     <row r="151">
@@ -3746,19 +4191,22 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.623152341074236</v>
+        <v>0.5357117740302405</v>
       </c>
       <c r="C151" t="n">
-        <v>2.095808501360983</v>
+        <v>-1.96548605337222</v>
       </c>
       <c r="D151" t="n">
-        <v>0.7415405930544633</v>
+        <v>2.063592011426003</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.3034757007126972</v>
+        <v>0.4799501427369055</v>
       </c>
       <c r="F151" t="n">
-        <v>0.8462693821907202</v>
+        <v>-0.3809600560615914</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.7951828234446906</v>
       </c>
     </row>
     <row r="152">
@@ -3768,19 +4216,22 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2.305767495483289</v>
+        <v>1.495717140617651</v>
       </c>
       <c r="C152" t="n">
-        <v>2.04546024545887</v>
+        <v>-1.949415887636238</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1128843439028534</v>
+        <v>1.933889841677597</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.3108084797525963</v>
+        <v>0.5519649875128406</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8406595376757695</v>
+        <v>-0.350144154945258</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.7789247778934242</v>
       </c>
     </row>
     <row r="153">
@@ -3790,19 +4241,22 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.423401747995108</v>
+        <v>0.4381056105105999</v>
       </c>
       <c r="C153" t="n">
-        <v>2.168655179620119</v>
+        <v>-2.074361727723887</v>
       </c>
       <c r="D153" t="n">
-        <v>0.6609509048372327</v>
+        <v>1.7104552891461</v>
       </c>
       <c r="E153" t="n">
-        <v>0.04427746122811687</v>
+        <v>0.6521746249010972</v>
       </c>
       <c r="F153" t="n">
-        <v>0.8543860196221917</v>
+        <v>-0.1739673811628859</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.750917465912211</v>
       </c>
     </row>
     <row r="154">
@@ -3812,19 +4266,22 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3.144660249086152</v>
+        <v>1.855099289364509</v>
       </c>
       <c r="C154" t="n">
-        <v>2.154238169350703</v>
+        <v>-1.908228540714084</v>
       </c>
       <c r="D154" t="n">
-        <v>0.655674740486154</v>
+        <v>2.35926567477197</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.2538141216882162</v>
+        <v>1.449839848771132</v>
       </c>
       <c r="F154" t="n">
-        <v>0.852779664356597</v>
+        <v>-0.6266151563072676</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.8322452403365068</v>
       </c>
     </row>
     <row r="155">
@@ -3834,19 +4291,22 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>5.891795819249972</v>
+        <v>4.279989831293451</v>
       </c>
       <c r="C155" t="n">
-        <v>3.144666864262067</v>
+        <v>-2.898432750371442</v>
       </c>
       <c r="D155" t="n">
-        <v>0.06936867702634336</v>
+        <v>3.136011220841886</v>
       </c>
       <c r="E155" t="n">
-        <v>0.4265257556518525</v>
+        <v>2.857295768945626</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9631340526476359</v>
+        <v>-0.2940697862035225</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.9296095673500351</v>
       </c>
     </row>
     <row r="156">
@@ -3856,19 +4316,22 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>4.837629479491945</v>
+        <v>3.967351422025448</v>
       </c>
       <c r="C156" t="n">
-        <v>3.031015045974167</v>
+        <v>-2.822630938346176</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5044166969220915</v>
+        <v>1.855235618934821</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3919865178132687</v>
+        <v>2.502272852347996</v>
       </c>
       <c r="F156" t="n">
-        <v>0.950470872602708</v>
+        <v>-0.459525110226989</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.8234141555524372</v>
       </c>
     </row>
     <row r="157">
@@ -3878,19 +4341,22 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2.746603678568132</v>
+        <v>2.129854945979436</v>
       </c>
       <c r="C157" t="n">
-        <v>2.497435852612682</v>
+        <v>-2.344520042487236</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.2102454353907318</v>
+        <v>1.606451104354822</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.3249454655215883</v>
+        <v>0.9543051515067215</v>
       </c>
       <c r="F157" t="n">
-        <v>0.8910190354429394</v>
+        <v>-0.6501388563178429</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.7378806387169611</v>
       </c>
     </row>
     <row r="158">
@@ -3900,19 +4366,22 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-0.2786205447688595</v>
+        <v>-0.5336469646155383</v>
       </c>
       <c r="C158" t="n">
-        <v>2.094929716279219</v>
+        <v>-2.028526582993385</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3278774840360043</v>
+        <v>0.34226453843889</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.1175389296257816</v>
+        <v>0.02694042381037639</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8461714672265884</v>
+        <v>-0.43979237467688</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.5794160362062324</v>
       </c>
     </row>
     <row r="159">
@@ -3922,19 +4391,22 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6.262908248800912</v>
+        <v>5.657407597592139</v>
       </c>
       <c r="C159" t="n">
-        <v>2.687584274590168</v>
+        <v>-2.431431646844307</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.162762878044976</v>
+        <v>1.36358477399297</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7509864004991916</v>
+        <v>3.559846253347655</v>
       </c>
       <c r="F159" t="n">
-        <v>0.949082603135816</v>
+        <v>-0.4786730884132331</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.9882971456355734</v>
       </c>
     </row>
     <row r="160">
@@ -3944,19 +4416,22 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-0.3959797932077877</v>
+        <v>-0.2892571520640165</v>
       </c>
       <c r="C160" t="n">
-        <v>2.028969473543796</v>
+        <v>-2.069521918519902</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.3278530187329633</v>
+        <v>0.6182697197875555</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.7815029893366046</v>
+        <v>-1.154017225706817</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8388221221641986</v>
+        <v>-0.4954713353662767</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.6140130272932476</v>
       </c>
     </row>
     <row r="161">
@@ -3966,19 +4441,22 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.9288274222814916</v>
+        <v>0.5688699780212773</v>
       </c>
       <c r="C161" t="n">
-        <v>2.150641775719913</v>
+        <v>-2.032553917380298</v>
       </c>
       <c r="D161" t="n">
-        <v>0.05972269380776481</v>
+        <v>1.018441511835799</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.586219512561146</v>
+        <v>0.06884279648274236</v>
       </c>
       <c r="F161" t="n">
-        <v>0.8523789511894414</v>
+        <v>-0.7370946242074711</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.6641741867871287</v>
       </c>
     </row>
     <row r="162">
@@ -3988,19 +4466,22 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-0.680079215652909</v>
+        <v>-1.212268888798663</v>
       </c>
       <c r="C162" t="n">
-        <v>1.833916788524341</v>
+        <v>-1.793778607092418</v>
       </c>
       <c r="D162" t="n">
-        <v>0.7738803137629753</v>
+        <v>0.7329719464088267</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.1186559436716445</v>
+        <v>-0.2569397243397419</v>
       </c>
       <c r="F162" t="n">
-        <v>0.8170891898991728</v>
+        <v>-0.2366172321864573</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.6283908440164194</v>
       </c>
     </row>
     <row r="163">
@@ -4010,19 +4491,22 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1.557884831341269</v>
+        <v>0.5972234513296197</v>
       </c>
       <c r="C163" t="n">
-        <v>1.971492561076107</v>
+        <v>-1.839399959362546</v>
       </c>
       <c r="D163" t="n">
-        <v>0.6377512256327126</v>
+        <v>1.769310352644117</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.2179147506147645</v>
+        <v>0.5898260013165003</v>
       </c>
       <c r="F163" t="n">
-        <v>0.832417996810382</v>
+        <v>-0.3817785331466304</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0.7582948930217924</v>
       </c>
     </row>
     <row r="164">
@@ -4032,19 +4516,22 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2.706509912349437</v>
+        <v>2.407453540548493</v>
       </c>
       <c r="C164" t="n">
-        <v>2.717135798737733</v>
+        <v>-2.572424888239317</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.5863931944106784</v>
+        <v>1.011899868574467</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.1474110978030476</v>
+        <v>1.156025548871551</v>
       </c>
       <c r="F164" t="n">
-        <v>0.9154981860236623</v>
+        <v>-0.6913890376427824</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.6712294940952355</v>
       </c>
     </row>
     <row r="165">
@@ -4054,19 +4541,22 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1.523412351883168</v>
+        <v>0.5756198828584363</v>
       </c>
       <c r="C165" t="n">
-        <v>2.107512072663106</v>
+        <v>-1.996432695595976</v>
       </c>
       <c r="D165" t="n">
-        <v>0.5567500465580024</v>
+        <v>2.003062998924359</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.4542489148332218</v>
+        <v>0.2263918370444927</v>
       </c>
       <c r="F165" t="n">
-        <v>0.8475734038315531</v>
+        <v>-0.4348486170613273</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.7875955683946494</v>
       </c>
     </row>
     <row r="166">
@@ -4076,19 +4566,22 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3.114433934198862</v>
+        <v>2.446415398999239</v>
       </c>
       <c r="C166" t="n">
-        <v>2.804736669184483</v>
+        <v>-2.699540744629748</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.3389013464071102</v>
+        <v>1.631666934989031</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1086289467868011</v>
+        <v>1.285556129817813</v>
       </c>
       <c r="F166" t="n">
-        <v>0.9252587478102722</v>
+        <v>-0.3330877686061</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0.7410414194799909</v>
       </c>
     </row>
     <row r="167">
@@ -4098,19 +4591,22 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.346007077664504</v>
+        <v>0.563924361596591</v>
       </c>
       <c r="C167" t="n">
-        <v>2.106094025657893</v>
+        <v>-2.002933721868619</v>
       </c>
       <c r="D167" t="n">
-        <v>0.4207442616681898</v>
+        <v>1.643726259258437</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.3471672076927065</v>
+        <v>0.2893925564298548</v>
       </c>
       <c r="F167" t="n">
-        <v>0.8474154038557525</v>
+        <v>-0.4280174956169031</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.7425530444872658</v>
       </c>
     </row>
     <row r="168">
@@ -4120,19 +4616,22 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-1.703290794607403</v>
+        <v>-0.9964013764079884</v>
       </c>
       <c r="C168" t="n">
-        <v>1.747698762300437</v>
+        <v>-1.693471559125871</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.3465692072587775</v>
+        <v>-1.255365880175981</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.4442643105651246</v>
+        <v>-0.5783497184575448</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8074827057650966</v>
+        <v>-0.8631779060823641</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.3791545589286053</v>
       </c>
     </row>
     <row r="169">
@@ -4142,19 +4641,22 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.05877604299848433</v>
+        <v>-0.2895433375771105</v>
       </c>
       <c r="C169" t="n">
-        <v>1.911443771384944</v>
+        <v>-1.806416746650229</v>
       </c>
       <c r="D169" t="n">
-        <v>0.381880180027533</v>
+        <v>0.5840655663392709</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.313039415079129</v>
+        <v>0.07263740455132477</v>
       </c>
       <c r="F169" t="n">
-        <v>0.8257273107589458</v>
+        <v>-0.5783255361123444</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.6097255686803082</v>
       </c>
     </row>
     <row r="170">
@@ -4164,19 +4666,22 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0706919988695723</v>
+        <v>-0.2219053093603202</v>
       </c>
       <c r="C170" t="n">
-        <v>2.143584590872986</v>
+        <v>-2.071890358859637</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2861052500682971</v>
+        <v>0.2790344532913016</v>
       </c>
       <c r="E170" t="n">
-        <v>0.1418663903759065</v>
+        <v>0.4196821378018407</v>
       </c>
       <c r="F170" t="n">
-        <v>0.8515926337888647</v>
+        <v>-0.3346007986679157</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0.5714902042287563</v>
       </c>
     </row>
     <row r="171">
@@ -4186,19 +4691,22 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.9703751746601426</v>
+        <v>0.3737778175842031</v>
       </c>
       <c r="C171" t="n">
-        <v>2.051817059408971</v>
+        <v>-1.902567681708905</v>
       </c>
       <c r="D171" t="n">
-        <v>0.4283235040734252</v>
+        <v>1.044648721769038</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.2770308155087401</v>
+        <v>0.5163923285867948</v>
       </c>
       <c r="F171" t="n">
-        <v>0.841367819168973</v>
+        <v>-0.6122371777888872</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.6674592360171663</v>
       </c>
     </row>
     <row r="172">
@@ -4208,19 +4716,22 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2.642700658044948</v>
+        <v>1.9136789479854</v>
       </c>
       <c r="C172" t="n">
-        <v>2.174233066290751</v>
+        <v>-1.971602574723963</v>
       </c>
       <c r="D172" t="n">
-        <v>0.09534968905832764</v>
+        <v>1.444151888700537</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.1726054382607719</v>
+        <v>1.307096049652734</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8550075123905827</v>
+        <v>-0.6671962067304991</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.717536583978628</v>
       </c>
     </row>
     <row r="173">
@@ -4230,19 +4741,22 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.3833118315668738</v>
+        <v>-0.09198082048018529</v>
       </c>
       <c r="C173" t="n">
-        <v>2.011028459455372</v>
+        <v>-1.912870101927578</v>
       </c>
       <c r="D173" t="n">
-        <v>0.4165288275310011</v>
+        <v>0.7767191629682588</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.1572075633017678</v>
+        <v>0.2711820728567056</v>
       </c>
       <c r="F173" t="n">
-        <v>0.8368231194644373</v>
+        <v>-0.452853355223147</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.6338745166561602</v>
       </c>
     </row>
     <row r="174">
@@ -4252,19 +4766,22 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>1.745429763975064</v>
+        <v>0.8243790637357526</v>
       </c>
       <c r="C174" t="n">
-        <v>2.057149653987751</v>
+        <v>-1.890111956228335</v>
       </c>
       <c r="D174" t="n">
-        <v>0.5669773849340657</v>
+        <v>1.732288660545079</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.3280672511396407</v>
+        <v>0.6918834292585762</v>
       </c>
       <c r="F174" t="n">
-        <v>0.8419619812886378</v>
+        <v>-0.5577795341760998</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.7536542585767505</v>
       </c>
     </row>
     <row r="175">
@@ -4274,19 +4791,22 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2.069453437259415</v>
+        <v>1.746896858101637</v>
       </c>
       <c r="C175" t="n">
-        <v>2.542834354046599</v>
+        <v>-2.415592789022216</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.3116213714751275</v>
+        <v>0.6728106871483694</v>
       </c>
       <c r="E175" t="n">
-        <v>0.1783884550063741</v>
+        <v>1.25168303905324</v>
       </c>
       <c r="F175" t="n">
-        <v>0.896077374201509</v>
+        <v>-0.4873468593056628</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.6208496864908717</v>
       </c>
     </row>
     <row r="176">
@@ -4296,19 +4816,22 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-4.134150650036776</v>
+        <v>-2.971026837619953</v>
       </c>
       <c r="C176" t="n">
-        <v>1.466816095529297</v>
+        <v>-1.425461918021135</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.01977075951793842</v>
+        <v>-2.668974575076273</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.3354079690299642</v>
+        <v>-1.088745244046973</v>
       </c>
       <c r="F176" t="n">
-        <v>0.7761865256035769</v>
+        <v>-0.9605435916716295</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.2439477119021697</v>
       </c>
     </row>
     <row r="177">
@@ -4318,19 +4841,22 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.6002668769538846</v>
+        <v>0.3558777514488142</v>
       </c>
       <c r="C177" t="n">
-        <v>2.177672945611776</v>
+        <v>-2.108850461729216</v>
       </c>
       <c r="D177" t="n">
-        <v>0.03238714473311769</v>
+        <v>0.3696342053356092</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1265172645502498</v>
+        <v>0.542583514338696</v>
       </c>
       <c r="F177" t="n">
-        <v>0.8553907866032717</v>
+        <v>-0.3403545635728295</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0.5828467983283543</v>
       </c>
     </row>
     <row r="178">
@@ -4340,19 +4866,22 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1.512569380566717</v>
+        <v>0.9591156545330873</v>
       </c>
       <c r="C178" t="n">
-        <v>2.153311821891128</v>
+        <v>-2.026329787994694</v>
       </c>
       <c r="D178" t="n">
-        <v>0.1551951291960705</v>
+        <v>1.08978425732262</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.1282706776032193</v>
+        <v>0.7275136535318103</v>
       </c>
       <c r="F178" t="n">
-        <v>0.8526764499528023</v>
+        <v>-0.495659549382498</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.6731169331430847</v>
       </c>
     </row>
     <row r="179">
@@ -4362,19 +4891,22 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3.195414376350735</v>
+        <v>2.615319379877505</v>
       </c>
       <c r="C179" t="n">
-        <v>2.596839432777065</v>
+        <v>-2.448278807671661</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.3314033441575999</v>
+        <v>1.068946145846748</v>
       </c>
       <c r="E179" t="n">
-        <v>0.4816914002537471</v>
+        <v>1.935349268992955</v>
       </c>
       <c r="F179" t="n">
-        <v>0.902094664955028</v>
+        <v>-0.3197593950751082</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.6915090218530723</v>
       </c>
     </row>
     <row r="180">
@@ -4384,19 +4916,22 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1.242734203282908</v>
+        <v>0.7692461592915364</v>
       </c>
       <c r="C180" t="n">
-        <v>2.072608493729737</v>
+        <v>-1.914903152164475</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1989719010091702</v>
+        <v>0.9030874894611259</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.2806696153487288</v>
+        <v>0.6499668064335096</v>
       </c>
       <c r="F180" t="n">
-        <v>0.8436844180598873</v>
+        <v>-0.6797729129530937</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.6497146680764767</v>
       </c>
     </row>
     <row r="181">
@@ -4406,19 +4941,22 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.01497458891878667</v>
+        <v>0.1610220344019888</v>
       </c>
       <c r="C181" t="n">
-        <v>1.89139406936564</v>
+        <v>-1.778981463624758</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.1711276948841827</v>
+        <v>-0.2480252903433934</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.2731598790362465</v>
+        <v>0.2355168700229461</v>
       </c>
       <c r="F181" t="n">
-        <v>0.8234933562974832</v>
+        <v>-0.7572530378143906</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.5054237587955491</v>
       </c>
     </row>
     <row r="182">
@@ -4428,19 +4966,22 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-0.6618426110308104</v>
+        <v>0.1973599356661497</v>
       </c>
       <c r="C182" t="n">
-        <v>2.214807101136349</v>
+        <v>-2.097251388883671</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.7672038763675828</v>
+        <v>-1.732603437652948</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.001471695125544279</v>
+        <v>0.5043502261761398</v>
       </c>
       <c r="F182" t="n">
-        <v>0.8595283050724688</v>
+        <v>-0.9691123696690911</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.4556113109810385</v>
       </c>
     </row>
     <row r="183">
@@ -4450,19 +4991,22 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>6.934774128810085</v>
+        <v>5.735893995253988</v>
       </c>
       <c r="C183" t="n">
-        <v>2.716911014011337</v>
+        <v>-2.537976750906674</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.8670332158306864</v>
+        <v>2.927131631486817</v>
       </c>
       <c r="E183" t="n">
-        <v>0.4823145827049648</v>
+        <v>2.973033912299244</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>-0.1241784988812803</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.9959543301211721</v>
       </c>
     </row>
     <row r="184">
@@ -4472,19 +5016,22 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.5579253576383147</v>
+        <v>0.04096808845398864</v>
       </c>
       <c r="C184" t="n">
-        <v>1.988178012958278</v>
+        <v>-1.860926975928626</v>
       </c>
       <c r="D184" t="n">
-        <v>0.4197768769253154</v>
+        <v>1.0403965905848</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.483831520194286</v>
+        <v>0.09354852629534897</v>
       </c>
       <c r="F184" t="n">
-        <v>0.8342771037256772</v>
+        <v>-0.657348320990546</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.6669262353540517</v>
       </c>
     </row>
     <row r="185">
@@ -4494,19 +5041,22 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1.402018679196382</v>
+        <v>1.497275737869517</v>
       </c>
       <c r="C185" t="n">
-        <v>2.527479860397676</v>
+        <v>-2.41294457862011</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.6150902584400506</v>
+        <v>0.01811581801070342</v>
       </c>
       <c r="E185" t="n">
-        <v>0.01399425120717305</v>
+        <v>0.9143723863928949</v>
       </c>
       <c r="F185" t="n">
-        <v>0.8943665637586663</v>
+        <v>-0.6752616746188735</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.5824319500948489</v>
       </c>
     </row>
     <row r="186">
@@ -4516,19 +5066,22 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3.805661986881031</v>
+        <v>3.383332673797482</v>
       </c>
       <c r="C186" t="n">
-        <v>2.851794279303387</v>
+        <v>-2.689928861802612</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.7755085516336524</v>
+        <v>1.24316977695261</v>
       </c>
       <c r="E186" t="n">
-        <v>0.1173893791890206</v>
+        <v>1.796204621355489</v>
       </c>
       <c r="F186" t="n">
-        <v>0.9305019458373391</v>
+        <v>-0.5843515040487437</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.7664369030417927</v>
       </c>
     </row>
     <row r="187">
@@ -4538,19 +5091,22 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>4.590134738798424</v>
+        <v>3.530561980706806</v>
       </c>
       <c r="C187" t="n">
-        <v>2.435086535521586</v>
+        <v>-2.14439146604136</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.04619462602617604</v>
+        <v>2.104505638423478</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.05216740394860648</v>
+        <v>2.311827797320549</v>
       </c>
       <c r="F187" t="n">
-        <v>0.8840720227167302</v>
+        <v>-0.766682705213523</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.8003113082856363</v>
       </c>
     </row>
     <row r="188">
@@ -4560,19 +5116,22 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3.347906994878258</v>
+        <v>2.822329256149292</v>
       </c>
       <c r="C188" t="n">
-        <v>2.453695078608576</v>
+        <v>-2.270498349339145</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.4578540032993383</v>
+        <v>1.429232358626626</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.2058575322921883</v>
+        <v>1.407382503954457</v>
       </c>
       <c r="F188" t="n">
-        <v>0.8861454020522673</v>
+        <v>-0.7091063572893047</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.7156664348514725</v>
       </c>
     </row>
     <row r="189">
@@ -4582,19 +5141,22 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2.914028236455228</v>
+        <v>2.118456480277786</v>
       </c>
       <c r="C189" t="n">
-        <v>2.381973348794318</v>
+        <v>-2.176807914291918</v>
       </c>
       <c r="D189" t="n">
-        <v>0.05191672056925545</v>
+        <v>1.715420887155209</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.2884716161122591</v>
+        <v>1.251170521096258</v>
       </c>
       <c r="F189" t="n">
-        <v>0.878154107311422</v>
+        <v>-0.7191613526590169</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.751539898973878</v>
       </c>
     </row>
     <row r="190">
@@ -4604,19 +5166,22 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2.671951524277782</v>
+        <v>2.116939716781356</v>
       </c>
       <c r="C190" t="n">
-        <v>3.475538093656015</v>
+        <v>-3.37273817669727</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.3131682748472714</v>
+        <v>0.971837911877488</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6594019217176065</v>
+        <v>1.762501773725284</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>-0.2341678459895875</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.658332469162474</v>
       </c>
     </row>
     <row r="191">
@@ -4626,19 +5191,22 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>5.137263054440779</v>
+        <v>3.910535045286303</v>
       </c>
       <c r="C191" t="n">
-        <v>2.515574825724495</v>
+        <v>-2.296475139072883</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.1446279012196382</v>
+        <v>2.554414759053679</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2068430705247172</v>
+        <v>2.371565817809234</v>
       </c>
       <c r="F191" t="n">
-        <v>0.8930400949016023</v>
+        <v>-0.3722326866269793</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.8567069953533609</v>
       </c>
     </row>
     <row r="192">
@@ -4648,19 +5216,22 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1.196430978987119</v>
+        <v>0.6878838537382181</v>
       </c>
       <c r="C192" t="n">
-        <v>1.8757809347033</v>
+        <v>-1.694936585156685</v>
       </c>
       <c r="D192" t="n">
-        <v>0.2893868814174262</v>
+        <v>1.020601094525612</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.4981153595792332</v>
+        <v>0.5064684623158053</v>
       </c>
       <c r="F192" t="n">
-        <v>0.8217537278579796</v>
+        <v>-0.8062575465904464</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.6644448884555034</v>
       </c>
     </row>
     <row r="193">
@@ -4670,19 +5241,22 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>4.641213954405176</v>
+        <v>4.619236587702811</v>
       </c>
       <c r="C193" t="n">
-        <v>2.637299281177488</v>
+        <v>-2.317549228706191</v>
       </c>
       <c r="D193" t="n">
-        <v>-1.231603000414515</v>
+        <v>0.2267172487336202</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2156400849661303</v>
+        <v>2.951896530185182</v>
       </c>
       <c r="F193" t="n">
-        <v>0.9066027348882969</v>
+        <v>-1.136887209546165</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0.887012500306678</v>
       </c>
     </row>
     <row r="194">
@@ -4692,19 +5266,22 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>-1.321172998435992</v>
+        <v>-1.453730244507297</v>
       </c>
       <c r="C194" t="n">
-        <v>1.753426603682613</v>
+        <v>-1.737835300552488</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4753620707486512</v>
+        <v>0.09461289313136698</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.2135348579071244</v>
+        <v>-0.569895292057901</v>
       </c>
       <c r="F194" t="n">
-        <v>0.808120906612069</v>
+        <v>-0.3433009644399841</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0.5483731343174977</v>
       </c>
     </row>
     <row r="195">
@@ -4714,19 +5291,22 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-2.497349659304359</v>
+        <v>-1.632119595436892</v>
       </c>
       <c r="C195" t="n">
-        <v>1.20080974616672</v>
+        <v>-1.295310878665192</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.407215571389522</v>
+        <v>-1.698592886515189</v>
       </c>
       <c r="E195" t="n">
-        <v>0.132895997735734</v>
+        <v>-0.8275683773242296</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7465478770908068</v>
+        <v>-0.1612006015935472</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.3235964686314858</v>
       </c>
     </row>
     <row r="196">
@@ -4736,19 +5316,22 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-1.37249687616999</v>
+        <v>-0.9321129569804937</v>
       </c>
       <c r="C196" t="n">
-        <v>1.009735740727663</v>
+        <v>-1.065043534435825</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.2499377901379202</v>
+        <v>-0.6366483939420186</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.1933224304484075</v>
+        <v>-0.7712576733714165</v>
       </c>
       <c r="F196" t="n">
-        <v>0.7252582526111437</v>
+        <v>-0.2191061761551563</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.4567102165869878</v>
       </c>
     </row>
     <row r="197">
@@ -4758,19 +5341,22 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.4010055884956483</v>
+        <v>0.214599869609736</v>
       </c>
       <c r="C197" t="n">
-        <v>0.9720603568411339</v>
+        <v>-1.086828872171953</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.254898725569834</v>
+        <v>1.145295204991168</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.3814019766992158</v>
+        <v>-0.8933043624304698</v>
       </c>
       <c r="F197" t="n">
-        <v>0.7210604300280651</v>
+        <v>0.1588428121390181</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.6800751784641913</v>
       </c>
     </row>
     <row r="198">
@@ -4780,19 +5366,22 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-0.02542198983260159</v>
+        <v>-0.03070851417635526</v>
       </c>
       <c r="C198" t="n">
-        <v>1.082634134144745</v>
+        <v>-1.102311939478346</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.2148921298598123</v>
+        <v>0.8039368984534756</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.8511704914220783</v>
+        <v>-1.03843566864302</v>
       </c>
       <c r="F198" t="n">
-        <v>0.733380652188492</v>
+        <v>-0.4225978098693224</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.637286234318088</v>
       </c>
     </row>
     <row r="199">
@@ -4802,19 +5391,22 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2.138344799522687</v>
+        <v>1.571258459974584</v>
       </c>
       <c r="C199" t="n">
-        <v>1.045059327646767</v>
+        <v>-1.169550166905275</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.4465749628114145</v>
+        <v>2.293546993413061</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.4587051535869041</v>
+        <v>-0.6254860867186953</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7291940360216314</v>
+        <v>0.3237690876585977</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.8240074651537562</v>
       </c>
     </row>
     <row r="200">
@@ -4824,19 +5416,22 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-2.793570692276749</v>
+        <v>-2.226582542306372</v>
       </c>
       <c r="C200" t="n">
-        <v>1.058952409465378</v>
+        <v>-1.238455591068256</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.02984849517197548</v>
+        <v>-1.42282353178746</v>
       </c>
       <c r="E200" t="n">
-        <v>0.6257902674023643</v>
+        <v>-0.8291161058757912</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7307420147438223</v>
+        <v>0.4255551356144502</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0.3810146908705792</v>
       </c>
     </row>
     <row r="201">
@@ -4846,19 +5441,22 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-1.242252395786728</v>
+        <v>-1.165156957958407</v>
       </c>
       <c r="C201" t="n">
-        <v>1.424810722039239</v>
+        <v>-1.51858453464332</v>
       </c>
       <c r="D201" t="n">
-        <v>0.0341132362140615</v>
+        <v>0.1032165406497305</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.173405503681356</v>
+        <v>-0.9719204718873483</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7715062519803992</v>
+        <v>-0.01103151463263112</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.5494515934792212</v>
       </c>
     </row>
     <row r="202">
@@ -4868,19 +5466,22 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.4256896079965353</v>
+        <v>0.2192885906403475</v>
       </c>
       <c r="C202" t="n">
-        <v>1.026120825852422</v>
+        <v>-1.303250986973984</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.406920649836397</v>
+        <v>0.8959998929674878</v>
       </c>
       <c r="E202" t="n">
-        <v>0.7006576574337134</v>
+        <v>-0.4807414003037118</v>
       </c>
       <c r="F202" t="n">
-        <v>0.7270838924127058</v>
+        <v>1.117649920277744</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.6488262444913812</v>
       </c>
     </row>
     <row r="203">
@@ -4890,19 +5491,22 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.9256385037998293</v>
+        <v>0.5058577556653271</v>
       </c>
       <c r="C203" t="n">
-        <v>1.343125782091253</v>
+        <v>-1.283008718179678</v>
       </c>
       <c r="D203" t="n">
-        <v>0.1054793782042085</v>
+        <v>1.188162762227634</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.5129420790854685</v>
+        <v>-0.1240821625886156</v>
       </c>
       <c r="F203" t="n">
-        <v>0.762404848086445</v>
+        <v>-0.4008385120688767</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.685448586631332</v>
       </c>
     </row>
     <row r="204">
@@ -4912,19 +5516,22 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-1.795429563278699</v>
+        <v>-1.183728909744739</v>
       </c>
       <c r="C204" t="n">
-        <v>1.018722966952137</v>
+        <v>-1.019854497373247</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.2678594156722152</v>
+        <v>-0.8105916838707387</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.6912345598695996</v>
+        <v>-1.138189540819377</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7262596168259837</v>
+        <v>-0.6663284987829552</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0.4349065880394938</v>
       </c>
     </row>
     <row r="205">
@@ -4934,19 +5541,22 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2.288569679761744</v>
+        <v>1.114294642258787</v>
       </c>
       <c r="C205" t="n">
-        <v>2.068873543865478</v>
+        <v>-1.861027708654654</v>
       </c>
       <c r="D205" t="n">
-        <v>0.7360886624228994</v>
+        <v>2.218646435255117</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.4402347598603693</v>
+        <v>0.8598540313194757</v>
       </c>
       <c r="F205" t="n">
-        <v>0.8432682668420505</v>
+        <v>-0.6325967320441711</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0.8146187503102864</v>
       </c>
     </row>
     <row r="206">
@@ -4956,19 +5566,22 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-1.373797255002219</v>
+        <v>-0.5363368241784087</v>
       </c>
       <c r="C206" t="n">
-        <v>2.35376038926401</v>
+        <v>-2.318503953765332</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.6165440101354112</v>
+        <v>-1.82264259527393</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2837184927123618</v>
+        <v>0.2272426779379167</v>
       </c>
       <c r="F206" t="n">
-        <v>0.87501059591394</v>
+        <v>-0.6185665445208924</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.3840904991901393</v>
       </c>
     </row>
     <row r="207">
@@ -4978,19 +5591,22 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.8042107434048156</v>
+        <v>0.2382563844369028</v>
       </c>
       <c r="C207" t="n">
-        <v>1.950632431270586</v>
+        <v>-1.797559835390486</v>
       </c>
       <c r="D207" t="n">
-        <v>0.4424123216155718</v>
+        <v>1.083776709829121</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.4727164506997944</v>
+        <v>0.284674931044144</v>
       </c>
       <c r="F207" t="n">
-        <v>0.8300937438114662</v>
+        <v>-0.7066568899043584</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.6723638926890185</v>
       </c>
     </row>
     <row r="208">
@@ -5000,19 +5616,22 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-0.5238094406156939</v>
+        <v>-0.4885450537834296</v>
       </c>
       <c r="C208" t="n">
-        <v>0.2235348655568003</v>
+        <v>-0.9483744571777952</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.8425639518176057</v>
+        <v>0.07050735771623946</v>
       </c>
       <c r="E208" t="n">
-        <v>2.827067480503376</v>
+        <v>-0.4762309372574044</v>
       </c>
       <c r="F208" t="n">
-        <v>0.8075787645323061</v>
+        <v>3.401027114399576</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0.8106448722759528</v>
       </c>
     </row>
     <row r="209">
@@ -5022,19 +5641,22 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-1.728658389714809</v>
+        <v>-0.463355841693832</v>
       </c>
       <c r="C209" t="n">
-        <v>0.9490975321057979</v>
+        <v>-0.9532241036119801</v>
       </c>
       <c r="D209" t="n">
-        <v>-1.173285335547513</v>
+        <v>-1.123440848691093</v>
       </c>
       <c r="E209" t="n">
-        <v>-1.564489915844035</v>
+        <v>-1.951068743047877</v>
       </c>
       <c r="F209" t="n">
-        <v>0.7185018930126073</v>
+        <v>-1.234363368619598</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0.3956912381175047</v>
       </c>
     </row>
     <row r="210">
@@ -5044,19 +5666,22 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1.619415340982925</v>
+        <v>1.176479314197934</v>
       </c>
       <c r="C210" t="n">
-        <v>0.7927268307384119</v>
+        <v>-1.060466646512622</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.5772493284351672</v>
+        <v>1.970351570580972</v>
       </c>
       <c r="E210" t="n">
-        <v>0.1306570451974187</v>
+        <v>-0.7720513717311628</v>
       </c>
       <c r="F210" t="n">
-        <v>0.7010789395130795</v>
+        <v>0.994847906464537</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.7834952214761252</v>
       </c>
     </row>
     <row r="211">
@@ -5066,19 +5691,22 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-1.100233044972608</v>
+        <v>-0.8849090309368238</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.194572545092109</v>
+        <v>-0.7678037312598531</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.135642022231007</v>
+        <v>-0.3044140679704616</v>
       </c>
       <c r="E211" t="n">
-        <v>3.745434098763418</v>
+        <v>-0.7108477794552421</v>
       </c>
       <c r="F211" t="n">
-        <v>0.9418960625367413</v>
+        <v>4.505432620048686</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.9701106448055438</v>
       </c>
     </row>
     <row r="212">
@@ -5088,19 +5716,22 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-0.8651211302765552</v>
+        <v>-0.9261662547860855</v>
       </c>
       <c r="C212" t="n">
-        <v>2.010063459478491</v>
+        <v>-1.945269246833016</v>
       </c>
       <c r="D212" t="n">
-        <v>0.313132595743127</v>
+        <v>-0.1480501793057715</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.07390446894019619</v>
+        <v>-0.05370644564304052</v>
       </c>
       <c r="F212" t="n">
-        <v>0.8367155983650418</v>
+        <v>-0.4881631396108865</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.5179555453677822</v>
       </c>
     </row>
     <row r="213">
@@ -5110,19 +5741,22 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>1.561834928169894</v>
+        <v>2.288613205516507</v>
       </c>
       <c r="C213" t="n">
-        <v>2.310468884010151</v>
+        <v>-2.131254965408608</v>
       </c>
       <c r="D213" t="n">
-        <v>-1.286154524385542</v>
+        <v>-1.157623150863926</v>
       </c>
       <c r="E213" t="n">
-        <v>0.02735820283237086</v>
+        <v>1.402399761119688</v>
       </c>
       <c r="F213" t="n">
-        <v>0.8701870204207891</v>
+        <v>-1.064731021732285</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.6596353529857039</v>
       </c>
     </row>
     <row r="214">
@@ -5132,19 +5766,22 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-0.5965785653544365</v>
+        <v>-0.377789363844123</v>
       </c>
       <c r="C214" t="n">
-        <v>1.970516883898101</v>
+        <v>-1.892662691143875</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.1298118985115479</v>
+        <v>-0.2830828671431958</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.426760472139066</v>
+        <v>-0.2462730855053227</v>
       </c>
       <c r="F214" t="n">
-        <v>0.8323092860483637</v>
+        <v>-0.7611332000760525</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.5010293243644689</v>
       </c>
     </row>
     <row r="215">
@@ -5154,19 +5791,22 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-4.272173279655311</v>
+        <v>-3.00879311210802</v>
       </c>
       <c r="C215" t="n">
-        <v>0.9368453254536168</v>
+        <v>-1.112486222784935</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.4223685574719133</v>
+        <v>-2.259255106143435</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.2228277128488418</v>
+        <v>-1.994442125534178</v>
       </c>
       <c r="F215" t="n">
-        <v>0.7171367419651229</v>
+        <v>-0.1994343261044992</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.2907720881073051</v>
       </c>
     </row>
     <row r="216">
@@ -5176,19 +5816,22 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-1.001203671482393</v>
+        <v>-1.034098808662298</v>
       </c>
       <c r="C216" t="n">
-        <v>1.757588718730816</v>
+        <v>-1.695275676657452</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3130261522029673</v>
+        <v>-0.03465228423404937</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.3375510055770795</v>
+        <v>-0.3786287292310149</v>
       </c>
       <c r="F216" t="n">
-        <v>0.8085846529297001</v>
+        <v>-0.5698696882123782</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0.5321698653523285</v>
       </c>
     </row>
     <row r="217">
@@ -5198,19 +5841,22 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.5155219187005281</v>
+        <v>0.5605252888915568</v>
       </c>
       <c r="C217" t="n">
-        <v>2.228255267975646</v>
+        <v>-2.144881865391116</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.2903149098720041</v>
+        <v>0.04851594414568852</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.1241178024608694</v>
+        <v>0.3721227244042635</v>
       </c>
       <c r="F217" t="n">
-        <v>0.8610267109979143</v>
+        <v>-0.5992399086046063</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0.5425949249179378</v>
       </c>
     </row>
     <row r="218">
@@ -5220,19 +5866,22 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.4761041419912843</v>
+        <v>-0.1138927065529159</v>
       </c>
       <c r="C218" t="n">
-        <v>1.907112585752316</v>
+        <v>-1.80516455964978</v>
       </c>
       <c r="D218" t="n">
-        <v>0.4889230778379531</v>
+        <v>1.261240707091863</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.5499616584515694</v>
+        <v>-0.1320674594998861</v>
       </c>
       <c r="F218" t="n">
-        <v>0.8252447264562904</v>
+        <v>-0.5705665443180257</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.694608838604759</v>
       </c>
     </row>
     <row r="219">
@@ -5242,19 +5891,22 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1.399988345318702</v>
+        <v>0.6551351464711467</v>
       </c>
       <c r="C219" t="n">
-        <v>2.382275583713096</v>
+        <v>-2.20615039535934</v>
       </c>
       <c r="D219" t="n">
-        <v>0.5215630857705381</v>
+        <v>1.014088511210117</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1224624605966539</v>
+        <v>1.158062308668723</v>
       </c>
       <c r="F219" t="n">
-        <v>0.8781877825772471</v>
+        <v>-0.5125992175743909</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.6636285422339627</v>
       </c>
     </row>
     <row r="220">
@@ -5264,19 +5916,22 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2.762526208594306</v>
+        <v>1.681248115529567</v>
       </c>
       <c r="C220" t="n">
-        <v>2.129952812863038</v>
+        <v>-1.915062317774626</v>
       </c>
       <c r="D220" t="n">
-        <v>0.4545377396987005</v>
+        <v>2.256187304932737</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.5361526955741374</v>
+        <v>0.9352146163944106</v>
       </c>
       <c r="F220" t="n">
-        <v>0.8500737697541936</v>
+        <v>-0.7232564637703354</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.8193244631787512</v>
       </c>
     </row>
     <row r="221">
@@ -5286,19 +5941,22 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-0.2448917066495336</v>
+        <v>-0.4603358735962285</v>
       </c>
       <c r="C221" t="n">
-        <v>1.819866193307692</v>
+        <v>-1.717472189880001</v>
       </c>
       <c r="D221" t="n">
-        <v>0.3272835725311088</v>
+        <v>0.3417564636665514</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.3670851889945473</v>
+        <v>-0.05350960429414339</v>
       </c>
       <c r="F221" t="n">
-        <v>0.8155236609032696</v>
+        <v>-0.6345186016204004</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0.5793523495091775</v>
       </c>
     </row>
     <row r="222">
@@ -5308,19 +5966,22 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>-0.03818378238094754</v>
+        <v>-0.2237082193113891</v>
       </c>
       <c r="C222" t="n">
-        <v>0.1804812703942668</v>
+        <v>-0.9005262828528432</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.7307428509570452</v>
+        <v>0.4716834233673957</v>
       </c>
       <c r="E222" t="n">
-        <v>2.891723284214408</v>
+        <v>-0.2941155007751488</v>
       </c>
       <c r="F222" t="n">
-        <v>0.8170351109217519</v>
+        <v>3.506914441773081</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.8259340069048005</v>
       </c>
     </row>
     <row r="223">
@@ -5330,19 +5991,22 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.785400527962362</v>
+        <v>0.2456343871707618</v>
       </c>
       <c r="C223" t="n">
-        <v>1.943027157901007</v>
+        <v>-1.799271865402912</v>
       </c>
       <c r="D223" t="n">
-        <v>0.4081432920805671</v>
+        <v>1.027867671099043</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.4194181990033153</v>
+        <v>0.2988250070569679</v>
       </c>
       <c r="F223" t="n">
-        <v>0.8292463579322019</v>
+        <v>-0.66396989267919</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.6653557470260405</v>
       </c>
     </row>
     <row r="224">
@@ -5352,19 +6016,22 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>6.214654429254098</v>
+        <v>4.632837117836234</v>
       </c>
       <c r="C224" t="n">
-        <v>3.102526714819122</v>
+        <v>-2.800952806561129</v>
       </c>
       <c r="D224" t="n">
-        <v>0.09260330494193242</v>
+        <v>2.541340765698455</v>
       </c>
       <c r="E224" t="n">
-        <v>1.004280788845287</v>
+        <v>3.836944364125689</v>
       </c>
       <c r="F224" t="n">
-        <v>0.9584387621757808</v>
+        <v>-0.2293624780444026</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.9233467544093091</v>
       </c>
     </row>
     <row r="225">
@@ -5374,19 +6041,22 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.5836018663114404</v>
+        <v>0.7132316331257719</v>
       </c>
       <c r="C225" t="n">
-        <v>2.07170779449316</v>
+        <v>-1.968668932339894</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.3846225652775951</v>
+        <v>-0.02291073698669806</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.2778006925765642</v>
+        <v>0.3353141041999949</v>
       </c>
       <c r="F225" t="n">
-        <v>0.8435840614024143</v>
+        <v>-0.7328779258591519</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.5336416573073904</v>
       </c>
     </row>
     <row r="226">
@@ -5396,19 +6066,22 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>-4.62970263688642</v>
+        <v>-4.037066683823996</v>
       </c>
       <c r="C226" t="n">
-        <v>0.9130228461524095</v>
+        <v>-1.152489622644282</v>
       </c>
       <c r="D226" t="n">
-        <v>0.5677236114911943</v>
+        <v>-2.257676969707545</v>
       </c>
       <c r="E226" t="n">
-        <v>1.269098981903384</v>
+        <v>-0.9058910733103652</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7144824215235126</v>
+        <v>0.8449063941363496</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.4415650702913582</v>
       </c>
     </row>
     <row r="227">
@@ -5418,19 +6091,22 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>-3.511323147844879</v>
+        <v>-2.05024468120804</v>
       </c>
       <c r="C227" t="n">
-        <v>0.3327499592054908</v>
+        <v>-0.4674852519140658</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.7646666128075877</v>
+        <v>-2.77166621788857</v>
       </c>
       <c r="E227" t="n">
-        <v>0.07284406674901177</v>
+        <v>-1.227613562633997</v>
       </c>
       <c r="F227" t="n">
-        <v>0.649827934219272</v>
+        <v>-0.1823702291557703</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.3639595565036993</v>
       </c>
     </row>
     <row r="228">
@@ -5440,19 +6116,22 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>-1.363013261462109</v>
+        <v>0.4442004302138779</v>
       </c>
       <c r="C228" t="n">
-        <v>0.1729607762768831</v>
+        <v>-0.3923721955857762</v>
       </c>
       <c r="D228" t="n">
-        <v>-2.096142058195585</v>
+        <v>-2.304175706760932</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.1316150341039241</v>
+        <v>-1.191609837107309</v>
       </c>
       <c r="F228" t="n">
-        <v>0.6320240906632355</v>
+        <v>-0.04829441705481028</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.4796932316905573</v>
       </c>
     </row>
     <row r="229">
@@ -5462,19 +6141,22 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-2.599345918602109</v>
+        <v>-1.497909262163248</v>
       </c>
       <c r="C229" t="n">
-        <v>0.4625101275213075</v>
+        <v>-0.6326077266203221</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.7131744976547961</v>
+        <v>-1.969938924356089</v>
       </c>
       <c r="E229" t="n">
-        <v>0.2344065205281276</v>
+        <v>-1.042613554058687</v>
       </c>
       <c r="F229" t="n">
-        <v>0.6642859200112887</v>
+        <v>0.127471852641796</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.3432736113489012</v>
       </c>
     </row>
     <row r="230">
@@ -5484,19 +6166,22 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>-2.431637495021056</v>
+        <v>-1.954122033824353</v>
       </c>
       <c r="C230" t="n">
-        <v>1.149698848589898</v>
+        <v>-1.224258287880509</v>
       </c>
       <c r="D230" t="n">
-        <v>0.04304386877035915</v>
+        <v>-0.9715876254644965</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.1021827641960479</v>
+        <v>-1.045829994174287</v>
       </c>
       <c r="F230" t="n">
-        <v>0.7408530584066604</v>
+        <v>-0.1768013250240923</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0.4147258974845272</v>
       </c>
     </row>
     <row r="231">
@@ -5506,19 +6191,22 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>-3.498869981471585</v>
+        <v>-2.586058271348606</v>
       </c>
       <c r="C231" t="n">
-        <v>0.7613921370584313</v>
+        <v>-0.8911966386595963</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.07164656983382318</v>
+        <v>-2.374801355029691</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6796536207027805</v>
+        <v>-0.6574973429747083</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6975876019022981</v>
+        <v>0.1897834416218581</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.3469714747413358</v>
       </c>
     </row>
     <row r="232">
@@ -5528,19 +6216,22 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>-2.95191542329541</v>
+        <v>-2.10944502236209</v>
       </c>
       <c r="C232" t="n">
-        <v>0.5745626118381321</v>
+        <v>-1.092992964315631</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.7861221101326953</v>
+        <v>-1.334322084591475</v>
       </c>
       <c r="E232" t="n">
-        <v>1.330964691886719</v>
+        <v>-1.636743387189458</v>
       </c>
       <c r="F232" t="n">
-        <v>0.6767709009360195</v>
+        <v>1.748071073712214</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.5719735593955085</v>
       </c>
     </row>
     <row r="233">
@@ -5550,19 +6241,22 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>-1.659790965105263</v>
+        <v>-1.140733003546208</v>
       </c>
       <c r="C233" t="n">
-        <v>0.04478927850557137</v>
+        <v>-0.3304322782486365</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.5155970450434163</v>
+        <v>-0.5135570454859361</v>
       </c>
       <c r="E233" t="n">
-        <v>0.298769175508363</v>
+        <v>-1.366750535949669</v>
       </c>
       <c r="F233" t="n">
-        <v>0.6177431158635652</v>
+        <v>0.7989204142216306</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.4721396018782881</v>
       </c>
     </row>
     <row r="234">
@@ -5572,19 +6266,22 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-2.455215751762288</v>
+        <v>-1.810833682785179</v>
       </c>
       <c r="C234" t="n">
-        <v>1.198369066644868</v>
+        <v>-1.413779289802893</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.4134298649352377</v>
+        <v>-0.7055494872204299</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.1726234199697174</v>
+        <v>-1.757201497129722</v>
       </c>
       <c r="F234" t="n">
-        <v>0.7462759345501352</v>
+        <v>0.174639710746373</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.4480735290494902</v>
       </c>
     </row>
     <row r="235">
@@ -5594,19 +6291,22 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>-1.13930285466547</v>
+        <v>-0.9511025005373583</v>
       </c>
       <c r="C235" t="n">
-        <v>1.067510245682325</v>
+        <v>-1.107677169365275</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0003715130068328458</v>
+        <v>-0.2959946121627348</v>
       </c>
       <c r="E235" t="n">
-        <v>-0.1098422007640584</v>
+        <v>-0.5965645437171194</v>
       </c>
       <c r="F235" t="n">
-        <v>0.7316955359671756</v>
+        <v>-0.1459671067180655</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.499410849214198</v>
       </c>
     </row>
     <row r="236">
@@ -5616,19 +6316,22 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>-1.020767802966034</v>
+        <v>-0.7051983820885377</v>
       </c>
       <c r="C236" t="n">
-        <v>0.5919937630444926</v>
+        <v>-0.6860742451155745</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.2247798772029514</v>
+        <v>-0.4733360331442864</v>
       </c>
       <c r="E236" t="n">
-        <v>0.09473279725185561</v>
+        <v>-0.5635225173513437</v>
       </c>
       <c r="F236" t="n">
-        <v>0.6787130942897357</v>
+        <v>0.1267442646536142</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.4771812681205495</v>
       </c>
     </row>
     <row r="237">
@@ -5638,19 +6341,22 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>-3.02195733714497</v>
+        <v>-2.477215589536779</v>
       </c>
       <c r="C237" t="n">
-        <v>1.237509314623267</v>
+        <v>-1.355680373199272</v>
       </c>
       <c r="D237" t="n">
-        <v>0.1622867661311894</v>
+        <v>-1.578016466589607</v>
       </c>
       <c r="E237" t="n">
-        <v>0.543266823467789</v>
+        <v>-0.7000375397530042</v>
       </c>
       <c r="F237" t="n">
-        <v>0.7506369735077173</v>
+        <v>0.1774465539434762</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.3451901441393232</v>
       </c>
     </row>
     <row r="238">
@@ -5660,19 +6366,22 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>-3.467056296848696</v>
+        <v>-2.510257519276568</v>
       </c>
       <c r="C238" t="n">
-        <v>1.038676545065589</v>
+        <v>-1.112378983486189</v>
       </c>
       <c r="D238" t="n">
-        <v>-0.1308930960665224</v>
+        <v>-2.132325963808835</v>
       </c>
       <c r="E238" t="n">
-        <v>0.07115557514056967</v>
+        <v>-1.040384549310335</v>
       </c>
       <c r="F238" t="n">
-        <v>0.728482861081972</v>
+        <v>-0.2872357557200886</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.2831696071905873</v>
       </c>
     </row>
     <row r="239">
@@ -5682,19 +6391,22 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>-2.649492888465336</v>
+        <v>-1.933636728646463</v>
       </c>
       <c r="C239" t="n">
-        <v>1.147432979532142</v>
+        <v>-1.196420963234491</v>
       </c>
       <c r="D239" t="n">
-        <v>-0.1085582862324054</v>
+        <v>-1.541790175640664</v>
       </c>
       <c r="E239" t="n">
-        <v>-0.02669172301913275</v>
+        <v>-0.85677428263164</v>
       </c>
       <c r="F239" t="n">
-        <v>0.7406005933931757</v>
+        <v>-0.3152360893314482</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.3432515416414838</v>
       </c>
     </row>
     <row r="240">
@@ -5704,19 +6416,22 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>-1.805857109642677</v>
+        <v>-1.238587461566149</v>
       </c>
       <c r="C240" t="n">
-        <v>1.173870204039078</v>
+        <v>-1.31905711391444</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.517921526320681</v>
+        <v>-0.03220438754684499</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.9741729448246979</v>
+        <v>-2.134089675743659</v>
       </c>
       <c r="F240" t="n">
-        <v>0.7435462509186141</v>
+        <v>-0.3310079601888046</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.5324767069103575</v>
       </c>
     </row>
     <row r="241">
@@ -5726,19 +6441,22 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>-3.854058490804474</v>
+        <v>-2.715104065464675</v>
       </c>
       <c r="C241" t="n">
-        <v>0.9354009934145838</v>
+        <v>-1.144353772641533</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.4629884658667399</v>
+        <v>-1.96238689478498</v>
       </c>
       <c r="E241" t="n">
-        <v>-0.06965189608832852</v>
+        <v>-1.895309711771568</v>
       </c>
       <c r="F241" t="n">
-        <v>0.7169758132890097</v>
+        <v>0.02269407034616221</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.3228453403317631</v>
       </c>
     </row>
     <row r="242">
@@ -5748,19 +6466,22 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>-3.23987682778871</v>
+        <v>-2.121977055158131</v>
       </c>
       <c r="C242" t="n">
-        <v>0.6854493388898131</v>
+        <v>-1.164808812938479</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.9915304076965075</v>
+        <v>-1.702375868051883</v>
       </c>
       <c r="E242" t="n">
-        <v>0.998207389660082</v>
+        <v>-1.840085773332784</v>
       </c>
       <c r="F242" t="n">
-        <v>0.6891259922174557</v>
+        <v>1.370315976629894</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0.5174292746422217</v>
       </c>
     </row>
     <row r="243">
@@ -5770,19 +6491,22 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>-5.173894209295031</v>
+        <v>-3.595937130850427</v>
       </c>
       <c r="C243" t="n">
-        <v>0.2264565923323711</v>
+        <v>-0.739926025377418</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.8249250890772976</v>
+        <v>-3.203323145270004</v>
       </c>
       <c r="E243" t="n">
-        <v>1.459352958989468</v>
+        <v>-1.929903518305854</v>
       </c>
       <c r="F243" t="n">
-        <v>0.6379846389462813</v>
+        <v>1.517824698973427</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0.5387281474231385</v>
       </c>
     </row>
     <row r="244">
@@ -5792,19 +6516,22 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>-4.465852180009911</v>
+        <v>-2.830159732099669</v>
       </c>
       <c r="C244" t="n">
-        <v>0.5873728734484994</v>
+        <v>-0.7508174227080325</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.7682289550827323</v>
+        <v>-2.805293734731813</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.4135340671560574</v>
+        <v>-2.118444562264055</v>
       </c>
       <c r="F244" t="n">
-        <v>0.6781982309307213</v>
+        <v>-0.4074951422763921</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0.3284647290669116</v>
       </c>
     </row>
     <row r="245">
@@ -5814,19 +6541,22 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>-3.249722486182395</v>
+        <v>-2.39761331116675</v>
       </c>
       <c r="C245" t="n">
-        <v>0.9139976913189309</v>
+        <v>-1.20534036622558</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.4488018384884581</v>
+        <v>-1.290627302593347</v>
       </c>
       <c r="E245" t="n">
-        <v>0.1982762708236258</v>
+        <v>-1.882843186518457</v>
       </c>
       <c r="F245" t="n">
-        <v>0.7145910395821197</v>
+        <v>0.5111638192549059</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0.3933757799833529</v>
       </c>
     </row>
     <row r="246">
@@ -5836,19 +6566,22 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>-5.039056712941724</v>
+        <v>-3.714258531502107</v>
       </c>
       <c r="C246" t="n">
-        <v>0.8270846046628783</v>
+        <v>-1.133867820314717</v>
       </c>
       <c r="D246" t="n">
-        <v>-0.3705167967033559</v>
+        <v>-2.652318505200791</v>
       </c>
       <c r="E246" t="n">
-        <v>0.4580806219370792</v>
+        <v>-2.066944057909212</v>
       </c>
       <c r="F246" t="n">
-        <v>0.7049071112370577</v>
+        <v>0.4690259127649648</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0.387291462423519</v>
       </c>
     </row>
     <row r="247">
@@ -5858,19 +6591,22 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>-0.05981270169661775</v>
+        <v>0.2783490722424479</v>
       </c>
       <c r="C247" t="n">
-        <v>1.45488801763666</v>
+        <v>-1.54603298453123</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.7893763256172698</v>
+        <v>0.6434470470909679</v>
       </c>
       <c r="E247" t="n">
-        <v>-0.9964049292567002</v>
+        <v>-1.478705147258798</v>
       </c>
       <c r="F247" t="n">
-        <v>0.7748574892518508</v>
+        <v>-0.4243956520541622</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0.6171689816998087</v>
       </c>
     </row>
     <row r="248">
@@ -5880,19 +6616,22 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.5645019904788555</v>
+        <v>0.180926228018243</v>
       </c>
       <c r="C248" t="n">
-        <v>0.1287596160138144</v>
+        <v>-1.005144125442882</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.9099729134324883</v>
+        <v>0.9800523071488108</v>
       </c>
       <c r="E248" t="n">
-        <v>3.511448199642524</v>
+        <v>-0.2300459091348286</v>
       </c>
       <c r="F248" t="n">
-        <v>0.9076740501985733</v>
+        <v>4.346443080376822</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0.9471540499332677</v>
       </c>
     </row>
     <row r="249">
@@ -5902,19 +6641,22 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>-3.730390409471035</v>
+        <v>-2.788077348932913</v>
       </c>
       <c r="C249" t="n">
-        <v>0.6944673243543357</v>
+        <v>-0.9589227647552678</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.37260602900962</v>
+        <v>-1.324313794329136</v>
       </c>
       <c r="E249" t="n">
-        <v>-0.2423165054203742</v>
+        <v>-2.343802366336727</v>
       </c>
       <c r="F249" t="n">
-        <v>0.6901307836523848</v>
+        <v>0.2297093440869603</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0.3705120024382922</v>
       </c>
     </row>
     <row r="250">
@@ -5924,19 +6666,22 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>-3.154733127482138</v>
+        <v>-2.20585319745642</v>
       </c>
       <c r="C250" t="n">
-        <v>0.7549962118703405</v>
+        <v>-1.097128481099044</v>
       </c>
       <c r="D250" t="n">
-        <v>-0.673830188715586</v>
+        <v>-1.265342687417845</v>
       </c>
       <c r="E250" t="n">
-        <v>0.2100363714999769</v>
+        <v>-2.061140810919568</v>
       </c>
       <c r="F250" t="n">
-        <v>0.6968749626024541</v>
+        <v>0.6650576284537519</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0.4155965992801489</v>
       </c>
     </row>
     <row r="251">
@@ -5946,19 +6691,22 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>-2.70909465881337</v>
+        <v>-2.270746471207497</v>
       </c>
       <c r="C251" t="n">
-        <v>0.1134190811904869</v>
+        <v>-1.048868923812201</v>
       </c>
       <c r="D251" t="n">
-        <v>-0.9141796705347159</v>
+        <v>-0.4909622468477491</v>
       </c>
       <c r="E251" t="n">
-        <v>2.897901802236343</v>
+        <v>-1.901296003571759</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8179387607603645</v>
+        <v>3.916607747242822</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0.8850898686990019</v>
       </c>
     </row>
     <row r="252">
@@ -5968,19 +6716,22 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>-3.808790122225191</v>
+        <v>-2.194030207435434</v>
       </c>
       <c r="C252" t="n">
-        <v>0.5382462123667301</v>
+        <v>-0.7599775945075069</v>
       </c>
       <c r="D252" t="n">
-        <v>-1.048626453559671</v>
+        <v>-2.578263354123925</v>
       </c>
       <c r="E252" t="n">
-        <v>-0.1905604561715231</v>
+        <v>-1.974875936076779</v>
       </c>
       <c r="F252" t="n">
-        <v>0.6727244975258698</v>
+        <v>-0.1022619408203935</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0.3273171759443609</v>
       </c>
     </row>
     <row r="253">
@@ -5990,19 +6741,22 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>-4.230024531836465</v>
+        <v>-3.080951988966337</v>
       </c>
       <c r="C253" t="n">
-        <v>0.9250078293642245</v>
+        <v>-1.177747107848146</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.3947097165667597</v>
+        <v>-2.098814895931967</v>
       </c>
       <c r="E253" t="n">
-        <v>0.1463230578926363</v>
+        <v>-1.966883597696403</v>
       </c>
       <c r="F253" t="n">
-        <v>0.7158177983131931</v>
+        <v>0.2386763927233743</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0.3540311572390903</v>
       </c>
     </row>
     <row r="254">
@@ -6012,19 +6766,22 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-6.260438536937455</v>
+        <v>-4.47267127491107</v>
       </c>
       <c r="C254" t="n">
-        <v>0.7048338685797162</v>
+        <v>-0.9855786534903288</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.4155570868964452</v>
+        <v>-3.907948963621751</v>
       </c>
       <c r="E254" t="n">
-        <v>0.6124014749285084</v>
+        <v>-2.017617854462964</v>
       </c>
       <c r="F254" t="n">
-        <v>0.6912858326251796</v>
+        <v>0.2738040392604443</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0.3591032591649929</v>
       </c>
     </row>
     <row r="255">
@@ -6034,19 +6791,22 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>-3.950649874981666</v>
+        <v>-2.745170603448072</v>
       </c>
       <c r="C255" t="n">
-        <v>1.127546528977918</v>
+        <v>-1.25902323708032</v>
       </c>
       <c r="D255" t="n">
-        <v>-0.4304863513732734</v>
+        <v>-2.044282492170532</v>
       </c>
       <c r="E255" t="n">
-        <v>-0.4481666143483198</v>
+        <v>-1.958105195458297</v>
       </c>
       <c r="F255" t="n">
-        <v>0.7383848285456238</v>
+        <v>-0.4277408424225567</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0.2802646001959314</v>
       </c>
     </row>
     <row r="256">
@@ -6056,19 +6816,22 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>-2.975888596583809</v>
+        <v>-2.374755675523147</v>
       </c>
       <c r="C256" t="n">
-        <v>0.8079862796088143</v>
+        <v>-0.8855835297722516</v>
       </c>
       <c r="D256" t="n">
-        <v>0.1495224775476858</v>
+        <v>-1.568251191355288</v>
       </c>
       <c r="E256" t="n">
-        <v>0.2163518433612984</v>
+        <v>-0.8338286227107881</v>
       </c>
       <c r="F256" t="n">
-        <v>0.7027791599877119</v>
+        <v>-0.04966978184519966</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0.3399346780943617</v>
       </c>
     </row>
     <row r="257">
@@ -6078,19 +6841,22 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>-3.18356973263882</v>
+        <v>-2.378615574206759</v>
       </c>
       <c r="C257" t="n">
-        <v>0.4493831963097559</v>
+        <v>-0.8295450098913717</v>
       </c>
       <c r="D257" t="n">
-        <v>-0.408731559216727</v>
+        <v>-1.756300781555636</v>
       </c>
       <c r="E257" t="n">
-        <v>1.260417380339256</v>
+        <v>-1.133188181387821</v>
       </c>
       <c r="F257" t="n">
-        <v>0.6628233064264522</v>
+        <v>1.305067622134433</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0.5080080256510843</v>
       </c>
     </row>
     <row r="258">
@@ -6100,19 +6866,22 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>-2.461362252371716</v>
+        <v>-1.969741394114799</v>
       </c>
       <c r="C258" t="n">
-        <v>0.9432191495343691</v>
+        <v>-1.182315667846781</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.139911463910389</v>
+        <v>-1.120751618421555</v>
       </c>
       <c r="E258" t="n">
-        <v>0.7476117636804875</v>
+        <v>-0.8992597974112556</v>
       </c>
       <c r="F258" t="n">
-        <v>0.7178469187412199</v>
+        <v>0.713103773313817</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0.4225340109174404</v>
       </c>
     </row>
     <row r="259">
@@ -6122,19 +6891,22 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>-1.784180081746878</v>
+        <v>-1.13852668209745</v>
       </c>
       <c r="C259" t="n">
-        <v>1.186930712569526</v>
+        <v>-1.221949699920615</v>
       </c>
       <c r="D259" t="n">
-        <v>-0.3453752080183399</v>
+        <v>-1.005659925743142</v>
       </c>
       <c r="E259" t="n">
-        <v>-0.339209161842105</v>
+        <v>-0.9086551946408596</v>
       </c>
       <c r="F259" t="n">
-        <v>0.7450014636331211</v>
+        <v>-0.4474134935106736</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0.4104549665429617</v>
       </c>
     </row>
     <row r="260">
@@ -6144,19 +6916,22 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>-2.125213412370318</v>
+        <v>-1.557032549133992</v>
       </c>
       <c r="C260" t="n">
-        <v>1.190143176885641</v>
+        <v>-1.319404042149574</v>
       </c>
       <c r="D260" t="n">
-        <v>-0.2364293504140548</v>
+        <v>-1.089481231484716</v>
       </c>
       <c r="E260" t="n">
-        <v>0.2164140620376151</v>
+        <v>-0.8567979802603289</v>
       </c>
       <c r="F260" t="n">
-        <v>0.7453593990769678</v>
+        <v>0.09752008112364817</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0.3999480443414548</v>
       </c>
     </row>
     <row r="261">
@@ -6166,19 +6941,22 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>-2.058128911010413</v>
+        <v>-1.406035004448756</v>
       </c>
       <c r="C261" t="n">
-        <v>1.015748107038029</v>
+        <v>-1.072883754313048</v>
       </c>
       <c r="D261" t="n">
-        <v>-0.2541673004485992</v>
+        <v>-1.204662811688373</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.1090523010645774</v>
+        <v>-0.8337880498270392</v>
       </c>
       <c r="F261" t="n">
-        <v>0.7259281554620718</v>
+        <v>-0.2701511817989529</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0.3855101410955</v>
       </c>
     </row>
     <row r="262">
@@ -6188,19 +6966,22 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>-1.127532941266129</v>
+        <v>-0.6677756298488668</v>
       </c>
       <c r="C262" t="n">
-        <v>1.02866376433917</v>
+        <v>-1.073527194036075</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.3514613644611166</v>
+        <v>-0.5743319925165007</v>
       </c>
       <c r="E262" t="n">
-        <v>-0.2718510500015714</v>
+        <v>-0.7371820503086172</v>
       </c>
       <c r="F262" t="n">
-        <v>0.7273672287322295</v>
+        <v>-0.2877179720904269</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0.4645215191652897</v>
       </c>
     </row>
     <row r="263">
@@ -6210,19 +6991,22 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>-0.447260896912589</v>
+        <v>-0.320083390215724</v>
       </c>
       <c r="C263" t="n">
-        <v>1.245254867704089</v>
+        <v>-1.290162524931961</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.1952078689527682</v>
+        <v>0.01691623654529823</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.1167616963765829</v>
+        <v>-0.4526135367033841</v>
       </c>
       <c r="F263" t="n">
-        <v>0.7514999894689889</v>
+        <v>-0.1182601707510638</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0.5386339311537593</v>
       </c>
     </row>
     <row r="264">
@@ -6232,19 +7016,22 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>-1.770782663607636</v>
+        <v>-1.291926587235441</v>
       </c>
       <c r="C264" t="n">
-        <v>1.207203803177111</v>
+        <v>-1.282703825238251</v>
       </c>
       <c r="D264" t="n">
-        <v>-0.1756161438308365</v>
+        <v>-0.9329189974538843</v>
       </c>
       <c r="E264" t="n">
-        <v>0.08274667247076961</v>
+        <v>-0.6707440076997588</v>
       </c>
       <c r="F264" t="n">
-        <v>0.7472603082367389</v>
+        <v>-0.0897887186596774</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0.4195729738042295</v>
       </c>
     </row>
     <row r="265">
@@ -6254,19 +7041,22 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>-2.675606028488324</v>
+        <v>-1.837845201843689</v>
       </c>
       <c r="C265" t="n">
-        <v>0.2314871418994844</v>
+        <v>-0.5819989232685541</v>
       </c>
       <c r="D265" t="n">
-        <v>-0.5113232952127529</v>
+        <v>-2.065188478247556</v>
       </c>
       <c r="E265" t="n">
-        <v>1.62083478993023</v>
+        <v>-0.4558678203369061</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6385451469597292</v>
+        <v>1.387407100944436</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0.5198970723200464</v>
       </c>
     </row>
     <row r="266">
@@ -6276,19 +7066,22 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>-1.962282326404922</v>
+        <v>-1.4536071496101</v>
       </c>
       <c r="C266" t="n">
-        <v>1.448744140744714</v>
+        <v>-1.473342106064855</v>
       </c>
       <c r="D266" t="n">
-        <v>-0.09904214762497064</v>
+        <v>-1.013248201457013</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.1369481568067895</v>
+        <v>-0.7198845460721559</v>
       </c>
       <c r="F266" t="n">
-        <v>0.7741729333826303</v>
+        <v>-0.3865564449771663</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0.4095037832863439</v>
       </c>
     </row>
     <row r="267">
@@ -6298,19 +7091,22 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>-0.1354394200912833</v>
+        <v>-0.2561274882277532</v>
       </c>
       <c r="C267" t="n">
-        <v>1.144021326616527</v>
+        <v>-1.104098128837413</v>
       </c>
       <c r="D267" t="n">
-        <v>0.1680438245842788</v>
+        <v>0.0835819466069925</v>
       </c>
       <c r="E267" t="n">
-        <v>0.02241000453859363</v>
+        <v>0.1338566420871422</v>
       </c>
       <c r="F267" t="n">
-        <v>0.7402204641900354</v>
+        <v>-0.2223043894190778</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0.5469904154977991</v>
       </c>
     </row>
     <row r="268">
@@ -6320,19 +7116,22 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>-2.977715732610144</v>
+        <v>-1.928983436260349</v>
       </c>
       <c r="C268" t="n">
-        <v>0.6597834750548953</v>
+        <v>-0.7052044933717676</v>
       </c>
       <c r="D268" t="n">
-        <v>-0.3876578444097494</v>
+        <v>-1.890986100061833</v>
       </c>
       <c r="E268" t="n">
-        <v>-0.4157619678678652</v>
+        <v>-1.278338246932555</v>
       </c>
       <c r="F268" t="n">
-        <v>0.6862662803391393</v>
+        <v>-0.5494145559287114</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0.3341789515328611</v>
       </c>
     </row>
     <row r="269">
@@ -6342,19 +7141,22 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>-4.34219636769542</v>
+        <v>-3.014420050143995</v>
       </c>
       <c r="C269" t="n">
-        <v>0.4333401667917701</v>
+        <v>-0.6068793136348084</v>
       </c>
       <c r="D269" t="n">
-        <v>-0.3455108566334074</v>
+        <v>-2.94876546906558</v>
       </c>
       <c r="E269" t="n">
-        <v>0.4604935699409975</v>
+        <v>-1.243352318371567</v>
       </c>
       <c r="F269" t="n">
-        <v>0.6610357787448649</v>
+        <v>0.1137729895613062</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0.3464967736766528</v>
       </c>
     </row>
     <row r="270">
@@ -6364,19 +7166,22 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>-4.983089446402844</v>
+        <v>-3.514677900632309</v>
       </c>
       <c r="C270" t="n">
-        <v>0.7330681202228442</v>
+        <v>-0.791603561698646</v>
       </c>
       <c r="D270" t="n">
-        <v>-0.1836236023255893</v>
+        <v>-3.199456284218175</v>
       </c>
       <c r="E270" t="n">
-        <v>-0.188213314355524</v>
+        <v>-1.558018135369066</v>
       </c>
       <c r="F270" t="n">
-        <v>0.6944317164075668</v>
+        <v>-0.6189391625481778</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0.3233551894010563</v>
       </c>
     </row>
     <row r="271">
@@ -6386,19 +7191,22 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>-5.255192683341892</v>
+        <v>-3.634202141873978</v>
       </c>
       <c r="C271" t="n">
-        <v>0.678512488283892</v>
+        <v>-0.710863706975153</v>
       </c>
       <c r="D271" t="n">
-        <v>-0.2005508693523821</v>
+        <v>-3.708761968185895</v>
       </c>
       <c r="E271" t="n">
-        <v>-0.04639112507425582</v>
+        <v>-1.324985736286508</v>
       </c>
       <c r="F271" t="n">
-        <v>0.6883530825580165</v>
+        <v>-0.6966913742965646</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0.3334699857641057</v>
       </c>
     </row>
     <row r="272">
@@ -6408,19 +7216,22 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>-5.258557942033432</v>
+        <v>-3.674444467459702</v>
       </c>
       <c r="C272" t="n">
-        <v>0.7724885520747607</v>
+        <v>-0.7298265632833619</v>
       </c>
       <c r="D272" t="n">
-        <v>-0.06504643861933093</v>
+        <v>-3.661905877597156</v>
       </c>
       <c r="E272" t="n">
-        <v>-0.3513264810001051</v>
+        <v>-1.31301422005516</v>
       </c>
       <c r="F272" t="n">
-        <v>0.6988239736851856</v>
+        <v>-1.058232276828577</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.3310943878555366</v>
       </c>
     </row>
     <row r="273">
@@ -6430,19 +7241,22 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>-2.23295099413106</v>
+        <v>-1.833304447008574</v>
       </c>
       <c r="C273" t="n">
-        <v>1.193565204031727</v>
+        <v>-1.175465764051112</v>
       </c>
       <c r="D273" t="n">
-        <v>0.1850802332667692</v>
+        <v>-0.8243459068881294</v>
       </c>
       <c r="E273" t="n">
-        <v>-0.4668650029635156</v>
+        <v>-0.9681078376041211</v>
       </c>
       <c r="F273" t="n">
-        <v>0.7457406841854888</v>
+        <v>-0.5931673216839706</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.4331825090609171</v>
       </c>
     </row>
     <row r="274">
@@ -6452,19 +7266,22 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>-1.273477955402622</v>
+        <v>-1.217141285970134</v>
       </c>
       <c r="C274" t="n">
-        <v>1.208803569669527</v>
+        <v>-1.269739331992219</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0984034671725032</v>
+        <v>0.3160224967303729</v>
       </c>
       <c r="E274" t="n">
-        <v>-0.5817338618507549</v>
+        <v>-1.269495880671875</v>
       </c>
       <c r="F274" t="n">
-        <v>0.7474385555488232</v>
+        <v>-0.248825409253199</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.576126620845773</v>
       </c>
     </row>
     <row r="275">
@@ -6474,19 +7291,22 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>-2.857736939959126</v>
+        <v>-1.837292476408168</v>
       </c>
       <c r="C275" t="n">
-        <v>0.7535010606212074</v>
+        <v>-0.8510660223054819</v>
       </c>
       <c r="D275" t="n">
-        <v>-0.4736965300338551</v>
+        <v>-1.79083191515955</v>
       </c>
       <c r="E275" t="n">
-        <v>-0.2120739673440545</v>
+        <v>-1.276558749986194</v>
       </c>
       <c r="F275" t="n">
-        <v>0.6967083716077178</v>
+        <v>-0.2998270044339949</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.3159059478543164</v>
       </c>
     </row>
     <row r="276">
@@ -6496,19 +7316,22 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>-2.728455266198474</v>
+        <v>-2.074868149506449</v>
       </c>
       <c r="C276" t="n">
-        <v>0.6838381329204385</v>
+        <v>-1.008868660467412</v>
       </c>
       <c r="D276" t="n">
-        <v>-0.3513281911078237</v>
+        <v>-1.300627344191534</v>
       </c>
       <c r="E276" t="n">
-        <v>0.9128468418275266</v>
+        <v>-1.160397855168715</v>
       </c>
       <c r="F276" t="n">
-        <v>0.688946470309342</v>
+        <v>1.022334565523992</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.467184030242317</v>
       </c>
     </row>
     <row r="277">
@@ -6518,19 +7341,22 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>-2.610045703297214</v>
+        <v>-2.064078613199373</v>
       </c>
       <c r="C277" t="n">
-        <v>0.936086730561705</v>
+        <v>-1.159766088236191</v>
       </c>
       <c r="D277" t="n">
-        <v>-0.1717194319776718</v>
+        <v>-0.9887668156172892</v>
       </c>
       <c r="E277" t="n">
-        <v>0.3488040538994954</v>
+        <v>-1.288634432408054</v>
       </c>
       <c r="F277" t="n">
-        <v>0.7170522186918294</v>
+        <v>0.4788305626307384</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.4125725020819695</v>
       </c>
     </row>
     <row r="278">
@@ -6540,19 +7366,22 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>-2.272615343981437</v>
+        <v>-1.865799295830473</v>
       </c>
       <c r="C278" t="n">
-        <v>1.123702501238291</v>
+        <v>-1.273636229262006</v>
       </c>
       <c r="D278" t="n">
-        <v>-0.03812256555809299</v>
+        <v>-0.7248804372085029</v>
       </c>
       <c r="E278" t="n">
-        <v>0.09938912556795759</v>
+        <v>-1.151157751103969</v>
       </c>
       <c r="F278" t="n">
-        <v>0.7379565237802633</v>
+        <v>0.1763224374713957</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0.4456504125660498</v>
       </c>
     </row>
     <row r="279">
@@ -6562,19 +7391,22 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>-0.1010851206346155</v>
+        <v>-0.1962232689960736</v>
       </c>
       <c r="C279" t="n">
-        <v>1.275657715648611</v>
+        <v>-1.339270675353406</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.1286600441437122</v>
+        <v>0.7734710959945772</v>
       </c>
       <c r="E279" t="n">
-        <v>-0.4486824492585763</v>
+        <v>-0.8495920144793188</v>
       </c>
       <c r="F279" t="n">
-        <v>0.7548875000535075</v>
+        <v>-0.1129528022156162</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0.6334673745018378</v>
       </c>
     </row>
     <row r="280">
@@ -6584,19 +7416,22 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>-0.7811033389397288</v>
+        <v>-0.7078987310465598</v>
       </c>
       <c r="C280" t="n">
-        <v>1.190228435922254</v>
+        <v>-1.385014411908679</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.2396986766062024</v>
+        <v>0.2592938936827578</v>
       </c>
       <c r="E280" t="n">
-        <v>0.2076423741184451</v>
+        <v>-0.9046904185648916</v>
       </c>
       <c r="F280" t="n">
-        <v>0.7453688987096825</v>
+        <v>0.5070108662242763</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0.569015743562865</v>
       </c>
     </row>
     <row r="281">
@@ -6606,19 +7441,22 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>-1.822142780852433</v>
+        <v>-1.387201824505907</v>
       </c>
       <c r="C281" t="n">
-        <v>0.7853622560091688</v>
+        <v>-0.9132357024873418</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.15458946800359</v>
+        <v>-0.7917840423418538</v>
       </c>
       <c r="E281" t="n">
-        <v>0.1571593320635368</v>
+        <v>-0.8519826735235445</v>
       </c>
       <c r="F281" t="n">
-        <v>0.7002583724763561</v>
+        <v>0.1738460044059937</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0.4372641082974943</v>
       </c>
     </row>
     <row r="282">
@@ -6628,19 +7466,22 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>-1.834753444714825</v>
+        <v>-1.635564946435245</v>
       </c>
       <c r="C282" t="n">
-        <v>0.6747362370785603</v>
+        <v>-0.8216630987280893</v>
       </c>
       <c r="D282" t="n">
-        <v>0.1696227054733157</v>
+        <v>-0.7876128623310079</v>
       </c>
       <c r="E282" t="n">
-        <v>0.6914255821269084</v>
+        <v>-0.4105256391583322</v>
       </c>
       <c r="F282" t="n">
-        <v>0.6879323295104336</v>
+        <v>0.5498791837800484</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0.4377869618068105</v>
       </c>
     </row>
     <row r="283">
@@ -6650,19 +7491,22 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>-5.459893497230455</v>
+        <v>-3.374028558848409</v>
       </c>
       <c r="C283" t="n">
-        <v>0.3288105038127123</v>
+        <v>-0.237402064632141</v>
       </c>
       <c r="D283" t="n">
-        <v>-0.5286646308731479</v>
+        <v>-4.28015559478036</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.8779170313603332</v>
+        <v>-1.604767821082568</v>
       </c>
       <c r="F283" t="n">
-        <v>0.6493889968254914</v>
+        <v>-1.553567758812118</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.3927835442838117</v>
       </c>
     </row>
     <row r="284">
@@ -6672,19 +7516,22 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>-1.234980210304892</v>
+        <v>-0.9222268260707868</v>
       </c>
       <c r="C284" t="n">
-        <v>0.9543893512755505</v>
+        <v>-1.067434823652116</v>
       </c>
       <c r="D284" t="n">
-        <v>-0.2572152157039554</v>
+        <v>-0.1395609242289533</v>
       </c>
       <c r="E284" t="n">
-        <v>-0.2891515731090268</v>
+        <v>-1.132538202626234</v>
       </c>
       <c r="F284" t="n">
-        <v>0.7190915119023116</v>
+        <v>-0.02075206327503364</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0.5190196655440519</v>
       </c>
     </row>
     <row r="285">
@@ -6694,19 +7541,22 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>-2.055397515839618</v>
+        <v>-1.402044219118453</v>
       </c>
       <c r="C285" t="n">
-        <v>1.27921288766607</v>
+        <v>-1.311279371340193</v>
       </c>
       <c r="D285" t="n">
-        <v>-0.2773750869957498</v>
+        <v>-0.991655762574716</v>
       </c>
       <c r="E285" t="n">
-        <v>-0.4704052724813267</v>
+        <v>-1.11058204864411</v>
       </c>
       <c r="F285" t="n">
-        <v>0.755283620274248</v>
+        <v>-0.5314636350394255</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0.4122103752854776</v>
       </c>
     </row>
     <row r="286">
@@ -6716,19 +7566,22 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>-2.707558485811043</v>
+        <v>-1.743538805984869</v>
       </c>
       <c r="C286" t="n">
-        <v>0.6997780371843045</v>
+        <v>-0.8557169550239285</v>
       </c>
       <c r="D286" t="n">
-        <v>-0.5431710737003669</v>
+        <v>-1.579849987787132</v>
       </c>
       <c r="E286" t="n">
-        <v>-0.07231791765577331</v>
+        <v>-1.368311481519769</v>
       </c>
       <c r="F286" t="n">
-        <v>0.6907225076894121</v>
+        <v>-0.02759411766167407</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0.3384807798203809</v>
       </c>
     </row>
     <row r="287">
@@ -6738,19 +7591,22 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>-2.797545198660823</v>
+        <v>-1.826635896461455</v>
       </c>
       <c r="C287" t="n">
-        <v>1.04485236592022</v>
+        <v>-1.049105690447509</v>
       </c>
       <c r="D287" t="n">
-        <v>-0.3588174296857256</v>
+        <v>-1.565324323884767</v>
       </c>
       <c r="E287" t="n">
-        <v>-0.761890008754936</v>
+        <v>-1.432159176273037</v>
       </c>
       <c r="F287" t="n">
-        <v>0.7291709761740622</v>
+        <v>-0.838755259426792</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.3403015581916689</v>
       </c>
     </row>
     <row r="288">
@@ -6760,19 +7616,22 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>-4.0724318559651</v>
+        <v>-2.720712220692206</v>
       </c>
       <c r="C288" t="n">
-        <v>0.7566566487847108</v>
+        <v>-0.6676037896906306</v>
       </c>
       <c r="D288" t="n">
-        <v>-0.1615308495751573</v>
+        <v>-2.884455465301061</v>
       </c>
       <c r="E288" t="n">
-        <v>-0.6873616931694922</v>
+        <v>-1.181915411421987</v>
       </c>
       <c r="F288" t="n">
-        <v>0.6970599698633732</v>
+        <v>-1.231087590997136</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0.3388894314085624</v>
       </c>
     </row>
     <row r="289">
@@ -6782,19 +7641,22 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>-3.373691234851529</v>
+        <v>-2.079761534524051</v>
       </c>
       <c r="C289" t="n">
-        <v>0.7123640069375422</v>
+        <v>-0.6071368325620103</v>
       </c>
       <c r="D289" t="n">
-        <v>-0.3393322175205061</v>
+        <v>-2.451223173523796</v>
       </c>
       <c r="E289" t="n">
-        <v>-0.9664560949241243</v>
+        <v>-1.22888475440681</v>
       </c>
       <c r="F289" t="n">
-        <v>0.6921248468989928</v>
+        <v>-1.354288756689752</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0.3464645126388147</v>
       </c>
     </row>
     <row r="290">
@@ -6804,19 +7666,22 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>-2.890519108099808</v>
+        <v>-1.725379606476505</v>
       </c>
       <c r="C290" t="n">
-        <v>0.8996379329196724</v>
+        <v>-0.8820364464005724</v>
       </c>
       <c r="D290" t="n">
-        <v>-0.5093070070410948</v>
+        <v>-1.949032655713855</v>
       </c>
       <c r="E290" t="n">
-        <v>-0.7942298083774729</v>
+        <v>-1.349827553621422</v>
       </c>
       <c r="F290" t="n">
-        <v>0.7129910633674774</v>
+        <v>-0.9732208732463716</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0.3120260853741085</v>
       </c>
     </row>
     <row r="291">
@@ -6826,19 +7691,22 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>-0.8931059994317299</v>
+        <v>-0.4899790657081659</v>
       </c>
       <c r="C291" t="n">
-        <v>0.9255220537451305</v>
+        <v>-1.073664401720077</v>
       </c>
       <c r="D291" t="n">
-        <v>-0.5144031911310509</v>
+        <v>-0.2746038914443119</v>
       </c>
       <c r="E291" t="n">
-        <v>-0.0272880469649251</v>
+        <v>-0.902385029420997</v>
       </c>
       <c r="F291" t="n">
-        <v>0.7158750936210641</v>
+        <v>0.1779418778750896</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0.502092156030338</v>
       </c>
     </row>
     <row r="292">
@@ -6848,19 +7716,22 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>-3.012723104767252</v>
+        <v>-1.926427567971239</v>
       </c>
       <c r="C292" t="n">
-        <v>1.121469759239776</v>
+        <v>-1.118685030151112</v>
       </c>
       <c r="D292" t="n">
-        <v>-0.3716801091607134</v>
+        <v>-2.092407882904311</v>
       </c>
       <c r="E292" t="n">
-        <v>-0.4072315566283327</v>
+        <v>-1.05214607550919</v>
       </c>
       <c r="F292" t="n">
-        <v>0.7377077498112499</v>
+        <v>-0.7706671698103101</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0.2823796085202896</v>
       </c>
     </row>
     <row r="293">
@@ -6870,19 +7741,22 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>-3.504297920953044</v>
+        <v>-2.3269295432369</v>
       </c>
       <c r="C293" t="n">
-        <v>1.173390456652512</v>
+        <v>-1.29594210793399</v>
       </c>
       <c r="D293" t="n">
-        <v>-0.5335566970187681</v>
+        <v>-1.962929303163265</v>
       </c>
       <c r="E293" t="n">
-        <v>-0.3776346605938442</v>
+        <v>-1.72460139291462</v>
       </c>
       <c r="F293" t="n">
-        <v>0.7434927970661049</v>
+        <v>-0.4122504131288429</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0.2904621462754347</v>
       </c>
     </row>
     <row r="294">
@@ -6892,19 +7766,22 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>-1.151887719532901</v>
+        <v>-0.8846217312673468</v>
       </c>
       <c r="C294" t="n">
-        <v>1.088115270376494</v>
+        <v>-1.289557125332918</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.3306175173594422</v>
+        <v>-0.2061015060443452</v>
       </c>
       <c r="E294" t="n">
-        <v>0.3135651755424254</v>
+        <v>-0.8825757047147507</v>
       </c>
       <c r="F294" t="n">
-        <v>0.7339913649425773</v>
+        <v>0.507496766216283</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0.5106788659085415</v>
       </c>
     </row>
     <row r="295">
@@ -6914,19 +7791,22 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>-3.802716613849701</v>
+        <v>-2.428379205106356</v>
       </c>
       <c r="C295" t="n">
-        <v>0.6265167050723826</v>
+        <v>-0.6622681315021971</v>
       </c>
       <c r="D295" t="n">
-        <v>-0.505062653571306</v>
+        <v>-2.38692328469231</v>
       </c>
       <c r="E295" t="n">
-        <v>-0.7546696379855981</v>
+        <v>-1.760360513316829</v>
       </c>
       <c r="F295" t="n">
-        <v>0.6825596691810616</v>
+        <v>-0.8489514625736032</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0.3395578633276396</v>
       </c>
     </row>
     <row r="296">
@@ -6936,19 +7816,22 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>-3.040538585431052</v>
+        <v>-2.168369674574948</v>
       </c>
       <c r="C296" t="n">
-        <v>0.5915706669706835</v>
+        <v>-0.8161435214838116</v>
       </c>
       <c r="D296" t="n">
-        <v>-0.3709680257504173</v>
+        <v>-1.690599339220201</v>
       </c>
       <c r="E296" t="n">
-        <v>0.4278778759705151</v>
+        <v>-1.255339309378491</v>
       </c>
       <c r="F296" t="n">
-        <v>0.6786659525735743</v>
+        <v>0.4328523064175476</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0.3820683337340421</v>
       </c>
     </row>
     <row r="297">
@@ -6958,19 +7841,22 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-0.01695830297002857</v>
+        <v>0.1594648812469686</v>
       </c>
       <c r="C297" t="n">
-        <v>1.543715777961806</v>
+        <v>-1.601161494385268</v>
       </c>
       <c r="D297" t="n">
-        <v>-0.3836888747850766</v>
+        <v>-0.3285840919481173</v>
       </c>
       <c r="E297" t="n">
-        <v>0.4640089813880651</v>
+        <v>0.2398473348987881</v>
       </c>
       <c r="F297" t="n">
-        <v>0.7847547521283286</v>
+        <v>0.1152850398956362</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0.495325788433252</v>
       </c>
     </row>
     <row r="298">
@@ -6980,19 +7866,22 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>1.881196701250679</v>
+        <v>1.458501974446695</v>
       </c>
       <c r="C298" t="n">
-        <v>1.11844411673705</v>
+        <v>-1.181804226117204</v>
       </c>
       <c r="D298" t="n">
-        <v>-0.4105284528035879</v>
+        <v>1.715613312672539</v>
       </c>
       <c r="E298" t="n">
-        <v>-0.3459554168350867</v>
+        <v>-0.2595076376814144</v>
       </c>
       <c r="F298" t="n">
-        <v>0.7373706302091109</v>
+        <v>0.1106109659593797</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0.7515640193323273</v>
       </c>
     </row>
     <row r="299">
@@ -7002,19 +7891,22 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>1.658344778547687</v>
+        <v>3.504393064403792</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.2395416891651967</v>
+        <v>0.1642826891228474</v>
       </c>
       <c r="D299" t="n">
-        <v>-2.876346506440858</v>
+        <v>-2.296713970536604</v>
       </c>
       <c r="E299" t="n">
-        <v>0.1584615001189423</v>
+        <v>0.6344304861559096</v>
       </c>
       <c r="F299" t="n">
-        <v>0.6001254785412375</v>
+        <v>-0.2745028928465916</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0.7782476342307176</v>
       </c>
     </row>
     <row r="300">
@@ -7024,19 +7916,22 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.05541187345811087</v>
+        <v>0.2124786071814424</v>
       </c>
       <c r="C300" t="n">
-        <v>1.527133610923499</v>
+        <v>-1.57234895208822</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.4022649854515579</v>
+        <v>-0.06719464009479167</v>
       </c>
       <c r="E300" t="n">
-        <v>0.1342492416350868</v>
+        <v>-0.04381229601124285</v>
       </c>
       <c r="F300" t="n">
-        <v>0.7829071532961724</v>
+        <v>-0.04821396864479745</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0.5280907115112188</v>
       </c>
     </row>
     <row r="301">
@@ -7046,19 +7941,22 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>2.359998788144756</v>
+        <v>2.104444300507343</v>
       </c>
       <c r="C301" t="n">
-        <v>0.4207408094510188</v>
+        <v>-0.5371258882586135</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.8332471718002877</v>
+        <v>1.836465154176777</v>
       </c>
       <c r="E301" t="n">
-        <v>-0.5081775281113734</v>
+        <v>-0.5104516590112469</v>
       </c>
       <c r="F301" t="n">
-        <v>0.6596319478791576</v>
+        <v>0.2525777190076863</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0.766712684523832</v>
       </c>
     </row>
     <row r="302">
@@ -7068,19 +7966,22 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>-2.730325601694054</v>
+        <v>-1.846299179356101</v>
       </c>
       <c r="C302" t="n">
-        <v>0.863241126542053</v>
+        <v>-1.060308831651296</v>
       </c>
       <c r="D302" t="n">
-        <v>-0.4585346740604574</v>
+        <v>-1.759192070766664</v>
       </c>
       <c r="E302" t="n">
-        <v>0.5066360194582279</v>
+        <v>-0.9584085061334623</v>
       </c>
       <c r="F302" t="n">
-        <v>0.7089357009530139</v>
+        <v>0.3471765642612318</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0.3696975620019934</v>
       </c>
     </row>
     <row r="303">
@@ -7090,19 +7991,22 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1.722558191583889</v>
+        <v>3.28067968898203</v>
       </c>
       <c r="C303" t="n">
-        <v>1.290829599614069</v>
+        <v>-1.44484038034864</v>
       </c>
       <c r="D303" t="n">
-        <v>-2.830602904955286</v>
+        <v>-1.447878686406521</v>
       </c>
       <c r="E303" t="n">
-        <v>0.1451270562873289</v>
+        <v>0.1888247146853438</v>
       </c>
       <c r="F303" t="n">
-        <v>0.7565779639736593</v>
+        <v>-0.12132325693134</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0.7564220104470806</v>
       </c>
     </row>
     <row r="304">
@@ -7112,19 +8016,22 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>1.207779489171728</v>
+        <v>1.4977573805565</v>
       </c>
       <c r="C304" t="n">
-        <v>0.8493036122681661</v>
+        <v>-0.5841205739926907</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.6480390128193239</v>
+        <v>0.8655126034150501</v>
       </c>
       <c r="E304" t="n">
-        <v>-2.355843363682218</v>
+        <v>-0.9355006684033167</v>
       </c>
       <c r="F304" t="n">
-        <v>0.7073827715297302</v>
+        <v>-1.986348260443524</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0.6450046912880718</v>
       </c>
     </row>
     <row r="305">
@@ -7134,19 +8041,22 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1.586848931228099</v>
+        <v>1.116852563841123</v>
       </c>
       <c r="C305" t="n">
-        <v>1.30630760933136</v>
+        <v>-1.29660983614481</v>
       </c>
       <c r="D305" t="n">
-        <v>-0.1722678509470927</v>
+        <v>1.71798572552378</v>
       </c>
       <c r="E305" t="n">
-        <v>-0.6553609293265076</v>
+        <v>-0.3441648279004954</v>
       </c>
       <c r="F305" t="n">
-        <v>0.7583025366794888</v>
+        <v>-0.2617293968288033</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0.7518613990621861</v>
       </c>
     </row>
     <row r="306">
@@ -7156,19 +8066,22 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>-1.164918355700126</v>
+        <v>-0.5568348159465291</v>
       </c>
       <c r="C306" t="n">
-        <v>0.6220843808710093</v>
+        <v>-0.7139053464811281</v>
       </c>
       <c r="D306" t="n">
-        <v>-0.5444793880297477</v>
+        <v>-0.8151752235400488</v>
       </c>
       <c r="E306" t="n">
-        <v>-0.1043717042432985</v>
+        <v>-0.7510568715892882</v>
       </c>
       <c r="F306" t="n">
-        <v>0.6820658159350247</v>
+        <v>-0.07202557193213975</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0.4343320456330388</v>
       </c>
     </row>
     <row r="307">
@@ -7178,19 +8091,22 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>-1.954749115420489</v>
+        <v>-1.420318567252579</v>
       </c>
       <c r="C307" t="n">
-        <v>0.9858433700821316</v>
+        <v>-0.9774514816161854</v>
       </c>
       <c r="D307" t="n">
-        <v>-0.06166758125836752</v>
+        <v>-1.013714206928368</v>
       </c>
       <c r="E307" t="n">
-        <v>-0.3728397223880259</v>
+        <v>-0.8066254662938734</v>
       </c>
       <c r="F307" t="n">
-        <v>0.722596144817865</v>
+        <v>-0.5382652762276253</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0.4094453699367821</v>
       </c>
     </row>
     <row r="308">
@@ -7200,19 +8116,22 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>-2.333812552157907</v>
+        <v>-0.6768132624451538</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.2359006730777042</v>
+        <v>0.1202471832141646</v>
       </c>
       <c r="D308" t="n">
-        <v>-1.372091887622283</v>
+        <v>-2.591532940543928</v>
       </c>
       <c r="E308" t="n">
-        <v>-0.2834713962902262</v>
+        <v>-1.156837962013782</v>
       </c>
       <c r="F308" t="n">
-        <v>0.586468408188435</v>
+        <v>-0.3578836943299054</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0.4375885457759749</v>
       </c>
     </row>
     <row r="309">
@@ -7222,19 +8141,22 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2.857169868348622</v>
+        <v>2.944103065090052</v>
       </c>
       <c r="C309" t="n">
-        <v>1.267580062755614</v>
+        <v>-1.326156973435461</v>
       </c>
       <c r="D309" t="n">
-        <v>-1.321966805699422</v>
+        <v>0.9092413183956607</v>
       </c>
       <c r="E309" t="n">
-        <v>0.009580397996419448</v>
+        <v>0.5109515450293779</v>
       </c>
       <c r="F309" t="n">
-        <v>0.753987481255169</v>
+        <v>0.06725870665633819</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0.7235853740430934</v>
       </c>
     </row>
     <row r="310">
@@ -7244,19 +8166,22 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>-2.369450462815782</v>
+        <v>-0.9639191716043329</v>
       </c>
       <c r="C310" t="n">
-        <v>0.7821030859085812</v>
+        <v>-0.8208932856693708</v>
       </c>
       <c r="D310" t="n">
-        <v>-1.050332943520218</v>
+        <v>-2.129281668224412</v>
       </c>
       <c r="E310" t="n">
-        <v>-0.6281402700608707</v>
+        <v>-1.243857876549949</v>
       </c>
       <c r="F310" t="n">
-        <v>0.6998952330351882</v>
+        <v>-0.7836400657325036</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0.3423161588458564</v>
       </c>
     </row>
     <row r="311">
@@ -7266,19 +8191,22 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>-0.8091826052897799</v>
+        <v>-0.6990742303798</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.01569098101561253</v>
+        <v>-0.8260864888384172</v>
       </c>
       <c r="D311" t="n">
-        <v>-0.9902853851059499</v>
+        <v>0.05403305599479905</v>
       </c>
       <c r="E311" t="n">
-        <v>3.085181578722729</v>
+        <v>-0.8044815613021372</v>
       </c>
       <c r="F311" t="n">
-        <v>0.8453296883576514</v>
+        <v>3.874068080797537</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0.8789475407785508</v>
       </c>
     </row>
     <row r="312">
@@ -7288,19 +8216,22 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>-0.7341143282664876</v>
+        <v>-0.7117961748835723</v>
       </c>
       <c r="C312" t="n">
-        <v>0.4607462496565576</v>
+        <v>-0.9908830940435156</v>
       </c>
       <c r="D312" t="n">
-        <v>-0.5345048586600695</v>
+        <v>0.1175115328123086</v>
       </c>
       <c r="E312" t="n">
-        <v>1.896398933197314</v>
+        <v>-0.634467971109635</v>
       </c>
       <c r="F312" t="n">
-        <v>0.6714622266199197</v>
+        <v>2.372447858530236</v>
+      </c>
+      <c r="G312" t="n">
+        <v>0.6621276973740476</v>
       </c>
     </row>
     <row r="313">
@@ -7310,19 +8241,22 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>-0.2911920455233964</v>
+        <v>-0.6260621188016077</v>
       </c>
       <c r="C313" t="n">
-        <v>1.00324571424862</v>
+        <v>-1.274509191490546</v>
       </c>
       <c r="D313" t="n">
-        <v>0.0748173880378141</v>
+        <v>0.4706278479685406</v>
       </c>
       <c r="E313" t="n">
-        <v>1.233923013441728</v>
+        <v>-0.095451061727618</v>
       </c>
       <c r="F313" t="n">
-        <v>0.7245351284672582</v>
+        <v>1.348874525821145</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0.5955062568825138</v>
       </c>
     </row>
     <row r="314">
@@ -7332,25 +8266,28 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>-0.8329315152524704</v>
+        <v>-0.7383397121277763</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.120564835081262</v>
+        <v>-0.8018085820123865</v>
       </c>
       <c r="D314" t="n">
-        <v>-1.016159161665096</v>
+        <v>-0.2025710715836809</v>
       </c>
       <c r="E314" t="n">
-        <v>3.780669878417088</v>
+        <v>-0.437074419644815</v>
       </c>
       <c r="F314" t="n">
-        <v>0.9470495324278043</v>
+        <v>4.432760999313611</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0.9596175459553301</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
